--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Liga_Portu" displayName="AveragesTable_Liga_Portu" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>87.2</v>
+        <v>84.33</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>35.6</v>
+        <v>35</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>14.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.8</v>
+        <v>10.83</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,73 +1526,73 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>41.2</v>
+        <v>43.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BD2" t="n">
-        <v>22.2</v>
+        <v>21.67</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>5.36</v>
@@ -1610,52 +1610,52 @@
         <v>5.45</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC2" t="n">
-        <v>6.33</v>
+        <v>6.09</v>
       </c>
       <c r="CD2" t="n">
-        <v>6.79</v>
+        <v>6.48</v>
       </c>
       <c r="CE2" t="n">
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH2" t="n">
         <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.88</v>
@@ -1673,10 +1673,10 @@
         <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX2" t="n">
         <v>1.63</v>
@@ -1691,55 +1691,55 @@
         <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.55</v>
+        <v>87</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM2" t="n">
-        <v>36.27</v>
+        <v>35.92</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.82</v>
+        <v>15.66</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>44.36</v>
+        <v>45.16</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.55</v>
+        <v>10.42</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.27</v>
+        <v>22.92</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -8242,82 +8242,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>92.8</v>
+        <v>90.83</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>39.4</v>
+        <v>38.83</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.8</v>
+        <v>13.83</v>
       </c>
       <c r="R19" t="n">
-        <v>7.6</v>
+        <v>7.17</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.6</v>
+        <v>12.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.6</v>
+        <v>8.33</v>
       </c>
       <c r="AB19" t="n">
         <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,67 +8401,67 @@
         <v>1.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="BH19" t="n">
-        <v>7.91</v>
+        <v>8.08</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CB19" t="n">
         <v>3.53</v>
@@ -8476,7 +8476,7 @@
         <v>1.43</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CG19" t="n">
         <v>2.67</v>
@@ -8488,19 +8488,19 @@
         <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CK19" t="n">
         <v>1.53</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CO19" t="n">
         <v>1.39</v>
@@ -8554,76 +8554,76 @@
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="DH19" t="n">
-        <v>94</v>
+        <v>92.92</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.18</v>
+        <v>4.42</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.46</v>
+        <v>41</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.09</v>
+        <v>13.84</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.73</v>
+        <v>14.66</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.45</v>
+        <v>7.25</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>48.36</v>
+        <v>48.16</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.82</v>
+        <v>12.66</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.18</v>
+        <v>9</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="EA19" t="n">
-        <v>23.27</v>
+        <v>22.67</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,127 +1875,127 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>74.8</v>
+        <v>80.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.8</v>
+        <v>31.33</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.2</v>
+        <v>13.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.6</v>
+        <v>13.67</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43</v>
+        <v>43.83</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.73</v>
+        <v>7.92</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>4.69</v>
@@ -2013,67 +2013,67 @@
         <v>4.58</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.37</v>
+        <v>4.26</v>
       </c>
       <c r="CC3" t="n">
-        <v>6.72</v>
+        <v>6.09</v>
       </c>
       <c r="CD3" t="n">
-        <v>8.41</v>
+        <v>7.53</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.04</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN3" t="n">
         <v>1.61</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS3" t="n">
         <v>3.32</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV3" t="n">
         <v>1.8</v>
@@ -2082,100 +2082,100 @@
         <v>2.11</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="DH3" t="n">
-        <v>74.18000000000001</v>
+        <v>77.17</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.54</v>
+        <v>38.58</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.46</v>
+        <v>13.75</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.64</v>
+        <v>14.17</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.27</v>
+        <v>7.92</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.45</v>
+        <v>45.66</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.369999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.91</v>
+        <v>5.84</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.18</v>
+        <v>19.75</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0.17</v>
@@ -2275,139 +2275,139 @@
         <v>2.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>2.83</v>
       </c>
       <c r="AI4" t="n">
-        <v>101.8</v>
+        <v>110.33</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>46.2</v>
+        <v>56.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.8</v>
+        <v>12.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.4</v>
+        <v>8.67</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>57.6</v>
+        <v>59.67</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>13.4</v>
+        <v>16.33</v>
       </c>
       <c r="BB4" t="n">
-        <v>9</v>
+        <v>11.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.4</v>
+        <v>19.17</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.73</v>
+        <v>9.08</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.2</v>
@@ -2416,43 +2416,43 @@
         <v>1.21</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.08</v>
+        <v>5.98</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.89</v>
+        <v>6.76</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
         <v>1.92</v>
@@ -2461,10 +2461,10 @@
         <v>1.19</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2482,13 +2482,13 @@
         <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CX4" t="n">
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.47</v>
@@ -2497,88 +2497,88 @@
         <v>2</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.91</v>
+        <v>3.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>116.27</v>
+        <v>119.33</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.37</v>
+        <v>5.84</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.82</v>
+        <v>65.67</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.55</v>
+        <v>12.16</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.55</v>
+        <v>13.25</v>
       </c>
       <c r="DR4" t="n">
-        <v>7</v>
+        <v>6.84</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>60.64</v>
+        <v>61.42</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.64</v>
+        <v>16.92</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.640000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6</v>
+        <v>6.16</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.82</v>
+        <v>20</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>86.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>41.6</v>
+        <v>38.83</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>15.2</v>
+        <v>14.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.2</v>
+        <v>13.17</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6</v>
+        <v>9.17</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.2</v>
+        <v>46</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.2</v>
+        <v>6.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.6</v>
+        <v>20.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2759,70 +2759,70 @@
         <v>3.17</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.73</v>
+        <v>10.92</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.82</v>
+        <v>6.08</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.94</v>
+        <v>4.45</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.63</v>
+        <v>5.23</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.92</v>
+        <v>4.01</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.07</v>
+        <v>4.18</v>
       </c>
       <c r="CC5" t="n">
         <v>6.03</v>
@@ -2831,13 +2831,13 @@
         <v>6.59</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH5" t="n">
         <v>1.41</v>
@@ -2861,13 +2861,13 @@
         <v>1.99</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.51</v>
+        <v>3.46</v>
       </c>
       <c r="CR5" t="n">
         <v>1.47</v>
@@ -2882,106 +2882,106 @@
         <v>1.43</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY5" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.18000000000001</v>
+        <v>86.75</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.09</v>
+        <v>36.08</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.18</v>
+        <v>14.75</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.27</v>
+        <v>11.92</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.09</v>
+        <v>8.83</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.91</v>
+        <v>41.84</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.27</v>
+        <v>10.84</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.36</v>
+        <v>7.08</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.82</v>
+        <v>20.67</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,127 +3084,127 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI6" t="n">
-        <v>89.33</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.67</v>
+        <v>3.14</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>37</v>
+        <v>33.71</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.5</v>
+        <v>16.14</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.67</v>
+        <v>12.14</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.33</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AU6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>0.67</v>
       </c>
-      <c r="AV6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>43.67</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>18.67</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.73</v>
-      </c>
       <c r="BK6" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BO6" t="n">
         <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="n">
         <v>4.12</v>
@@ -3222,16 +3222,16 @@
         <v>4.81</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.52</v>
+        <v>6.34</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.41</v>
+        <v>6.3</v>
       </c>
       <c r="CE6" t="n">
         <v>1.41</v>
@@ -3252,16 +3252,16 @@
         <v>2.01</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO6" t="n">
         <v>1.34</v>
@@ -3270,121 +3270,121 @@
         <v>2.11</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="CR6" t="n">
         <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV6" t="n">
         <v>1.88</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="DG6" t="n">
         <v>1.91</v>
       </c>
       <c r="DH6" t="n">
-        <v>92</v>
+        <v>89.25</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.18</v>
+        <v>38</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.55</v>
+        <v>15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.09</v>
+        <v>8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.46</v>
+        <v>44.58</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.27</v>
+        <v>11.67</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.09</v>
+        <v>7.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.46</v>
+        <v>18.92</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="H7" t="n">
-        <v>92.59999999999999</v>
+        <v>91.83</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="N7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P7" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51</v>
+        <v>51.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.4</v>
+        <v>8.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.2</v>
+        <v>20.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,37 +3565,37 @@
         <v>3.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.55</v>
+        <v>4.08</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.27</v>
+        <v>3.83</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
@@ -3604,31 +3604,31 @@
         <v>100</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.93</v>
+        <v>3.7</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.32</v>
+        <v>4.21</v>
       </c>
       <c r="CC7" t="n">
         <v>7.06</v>
@@ -3637,157 +3637,157 @@
         <v>8.029999999999999</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ7" t="n">
         <v>2.04</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV7" t="n">
         <v>1.75</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.63</v>
+        <v>80.33</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.18</v>
+        <v>32.66</v>
       </c>
       <c r="DN7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.18</v>
+        <v>14.67</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.55</v>
+        <v>15.67</v>
       </c>
       <c r="DR7" t="n">
         <v>8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>44.73</v>
+        <v>45.34</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>9.359999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.27</v>
+        <v>17.75</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2</v>
       </c>
-      <c r="AI8" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AL8" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU8" t="n">
         <v>1</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AV8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.2</v>
+        <v>43.83</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.4</v>
+        <v>8.67</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="BE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN8" t="n">
         <v>1.08</v>
       </c>
-      <c r="BF8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BO8" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY8" t="n">
         <v>4.32</v>
@@ -4028,169 +4028,169 @@
         <v>4.66</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.61</v>
+        <v>4.12</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.21</v>
+        <v>6.34</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CK8" t="n">
         <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.12</v>
+        <v>3.95</v>
       </c>
       <c r="CR8" t="n">
         <v>1.5</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.17</v>
+        <v>3.01</v>
       </c>
       <c r="CT8" t="n">
         <v>2.67</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CX8" t="n">
         <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.23</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.29</v>
+        <v>4.11</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>70.36</v>
+        <v>69</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM8" t="n">
-        <v>33.37</v>
+        <v>32.34</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.27</v>
+        <v>14.08</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.73</v>
+        <v>16.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.18</v>
+        <v>8.08</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.82</v>
+        <v>49.66</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>11.42</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.369999999999999</v>
+        <v>7.84</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.45</v>
+        <v>18.92</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0.17</v>
@@ -4696,127 +4696,127 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>82.59999999999999</v>
+        <v>86.33</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AL10" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.6</v>
+        <v>18.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AU10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1</v>
       </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>0.82</v>
-      </c>
       <c r="BO10" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="BR10" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
         <v>3.3</v>
@@ -4834,40 +4834,40 @@
         <v>3.36</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM10" t="n">
         <v>2.27</v>
@@ -4876,19 +4876,19 @@
         <v>1.75</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CT10" t="n">
         <v>2.84</v>
@@ -4897,22 +4897,22 @@
         <v>1.38</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW10" t="n">
         <v>1.96</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
         <v>1.38</v>
@@ -4921,49 +4921,49 @@
         <v>2.22</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.18000000000001</v>
+        <v>85.92</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="DK10" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.45</v>
+        <v>49.16</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>19.09</v>
+        <v>19.33</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.36</v>
+        <v>16.42</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.18</v>
+        <v>7.75</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.09</v>
+        <v>50.16</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.36</v>
+        <v>13.66</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.91</v>
+        <v>4.25</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.73</v>
+        <v>21.16</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0.17</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.6</v>
+        <v>47.83</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>6.83</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.2</v>
+        <v>50.33</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>24.8</v>
+        <v>24.33</v>
       </c>
       <c r="BE11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1.58</v>
       </c>
-      <c r="BF11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BP11" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.36</v>
+        <v>4.58</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY11" t="n">
         <v>3.55</v>
@@ -5237,166 +5237,166 @@
         <v>3.72</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.58</v>
+        <v>3.87</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.72</v>
+        <v>3.97</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.33</v>
+        <v>5.44</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.51</v>
+        <v>5.48</v>
       </c>
       <c r="CE11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CH11" t="n">
         <v>1.4</v>
       </c>
-      <c r="CF11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>1.38</v>
-      </c>
       <c r="CI11" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CM11" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="CR11" t="n">
         <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="CT11" t="n">
         <v>2.92</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.77</v>
+        <v>3.66</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DH11" t="n">
-        <v>97.63</v>
+        <v>98.66</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
         <v>3</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.73</v>
+        <v>46</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.91</v>
+        <v>12.75</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.91</v>
+        <v>13</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.27</v>
+        <v>8.75</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.82</v>
+        <v>51.75</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.63</v>
+        <v>13.42</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.369999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.55</v>
+        <v>22.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC11" t="n">
         <v>3</v>
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>84.2</v>
+        <v>92</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="M12" t="n">
-        <v>46.4</v>
+        <v>51.33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="P12" t="n">
-        <v>14.4</v>
+        <v>13.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.2</v>
+        <v>15.17</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>6.83</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>43.8</v>
+        <v>47.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
         <v>0.33</v>
@@ -5580,49 +5580,49 @@
         <v>3.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.27</v>
+        <v>8.83</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>4.42</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.27</v>
+        <v>3.01</v>
       </c>
       <c r="CA12" t="n">
         <v>3.5</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
         <v>4.26</v>
@@ -5652,13 +5652,13 @@
         <v>4.8</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CH12" t="n">
         <v>1.32</v>
@@ -5667,28 +5667,28 @@
         <v>1.7</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN12" t="n">
         <v>1.7</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="CR12" t="n">
         <v>1.51</v>
@@ -5697,16 +5697,16 @@
         <v>3.18</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CU12" t="n">
         <v>1.39</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CX12" t="n">
         <v>1.69</v>
@@ -5718,91 +5718,91 @@
         <v>2.16</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.18000000000001</v>
+        <v>88.08</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.82</v>
+        <v>5.42</v>
       </c>
       <c r="DL12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.36</v>
+        <v>43.33</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.91</v>
+        <v>15.42</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.91</v>
+        <v>14.42</v>
       </c>
       <c r="DR12" t="n">
-        <v>8</v>
+        <v>7.42</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.64</v>
+        <v>47.25</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="DY12" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.63</v>
+        <v>4.42</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.73</v>
+        <v>21.16</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="13">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -5824,46 +5824,46 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="H13" t="n">
-        <v>82.40000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>36.6</v>
+        <v>34.83</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="P13" t="n">
-        <v>14.4</v>
+        <v>14.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.6</v>
+        <v>14.17</v>
       </c>
       <c r="R13" t="n">
-        <v>8.4</v>
+        <v>8.67</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.6</v>
+        <v>50.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
         <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.2</v>
+        <v>22.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AF13" t="n">
         <v>0.33</v>
@@ -5983,70 +5983,70 @@
         <v>2.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.359999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="CC13" t="n">
         <v>5.93</v>
@@ -6055,70 +6055,70 @@
         <v>6.22</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
         <v>3.12</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN13" t="n">
         <v>1.66</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="CR13" t="n">
         <v>1.49</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CU13" t="n">
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DA13" t="n">
         <v>1.68</v>
@@ -6127,52 +6127,52 @@
         <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DH13" t="n">
-        <v>74.37</v>
+        <v>72.92</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.73</v>
+        <v>31.25</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.73</v>
+        <v>14.92</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.91</v>
+        <v>14.58</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.09</v>
+        <v>47.25</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.27</v>
+        <v>9.42</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.27</v>
+        <v>6.17</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.09</v>
+        <v>20.75</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="H14" t="n">
-        <v>103.8</v>
+        <v>101.83</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M14" t="n">
-        <v>49.4</v>
+        <v>46.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>53.2</v>
+        <v>52.5</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0.17</v>
@@ -6386,49 +6386,49 @@
         <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.45</v>
+        <v>4.67</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.91</v>
+        <v>5.09</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="CC14" t="n">
         <v>1.72</v>
@@ -6458,157 +6458,157 @@
         <v>1.85</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CM14" t="n">
         <v>2.32</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO14" t="n">
         <v>1.24</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="CT14" t="n">
         <v>3.16</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA14" t="n">
         <v>1.85</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="DH14" t="n">
-        <v>100.46</v>
+        <v>99.75</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.73</v>
+        <v>46.42</v>
       </c>
       <c r="DN14" t="n">
         <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.82</v>
+        <v>13.84</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.64</v>
+        <v>11.58</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.73</v>
+        <v>5.92</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.27</v>
+        <v>52.92</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.91</v>
+        <v>14.66</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.18</v>
+        <v>8.92</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.64</v>
+        <v>18.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -6633,79 +6633,79 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="H15" t="n">
-        <v>70.2</v>
+        <v>73</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M15" t="n">
-        <v>20.4</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.2</v>
+        <v>47.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.2</v>
+        <v>14.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.33</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.73</v>
+        <v>10.33</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BP15" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.81</v>
+        <v>3.66</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.14</v>
+        <v>3.94</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CC15" t="n">
         <v>4.9</v>
@@ -6861,157 +6861,157 @@
         <v>6.65</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="CH15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CR15" t="n">
         <v>1.43</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1.42</v>
       </c>
       <c r="CS15" t="n">
         <v>2.89</v>
       </c>
       <c r="CT15" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="CU15" t="n">
         <v>1.47</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
         <v>1.56</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.37</v>
+        <v>3.52</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.73</v>
+        <v>69.33</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM15" t="n">
-        <v>24.18</v>
+        <v>24.67</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.82</v>
+        <v>14.42</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.18</v>
+        <v>15.08</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.18</v>
+        <v>44.42</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.550000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.18</v>
+        <v>15.34</v>
       </c>
       <c r="EB15" t="n">
         <v>1.06</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0.33</v>
@@ -7111,127 +7111,127 @@
         <v>3.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>82.40000000000001</v>
+        <v>80.83</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>34.17</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.4</v>
+        <v>12.83</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.2</v>
+        <v>14.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.2</v>
+        <v>44.67</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="BC16" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.4</v>
+        <v>18.83</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
         <v>2</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.27</v>
+        <v>8.08</v>
       </c>
       <c r="BI16" t="n">
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="BR16" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS16" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>2.8</v>
@@ -7252,52 +7252,52 @@
         <v>2.98</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.72</v>
+        <v>4.36</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.19</v>
+        <v>4.78</v>
       </c>
       <c r="CE16" t="n">
         <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CL16" t="n">
         <v>2.36</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO16" t="n">
         <v>1.48</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CQ16" t="n">
         <v>4.73</v>
@@ -7309,28 +7309,28 @@
         <v>3.24</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB16" t="n">
         <v>1.53</v>
@@ -7339,82 +7339,82 @@
         <v>2.64</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DH16" t="n">
-        <v>92.91</v>
+        <v>91.25</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>39.18</v>
+        <v>39.67</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.18</v>
+        <v>13.33</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.91</v>
+        <v>15.34</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.27</v>
+        <v>8.08</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.46</v>
+        <v>47.92</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.27</v>
+        <v>12</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.27</v>
+        <v>8.08</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.91</v>
+        <v>21.42</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="17">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>120.6</v>
+        <v>119.83</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="K18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>61</v>
+        <v>57.67</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>11.8</v>
+        <v>11.83</v>
       </c>
       <c r="Q18" t="n">
         <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>57.6</v>
+        <v>58.5</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.2</v>
+        <v>13.17</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>18</v>
+        <v>18.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.17</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.36</v>
+        <v>10</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.64</v>
+        <v>5.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.79</v>
+        <v>6.06</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
       <c r="CC18" t="n">
         <v>1.32</v>
@@ -8076,151 +8076,151 @@
         <v>2.14</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CK18" t="n">
         <v>1.44</v>
       </c>
-      <c r="CI18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>1.43</v>
-      </c>
       <c r="CL18" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CT18" t="n">
         <v>3.28</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CX18" t="n">
         <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.26</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="DB18" t="n">
         <v>1.21</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="DH18" t="n">
-        <v>117.37</v>
+        <v>117.25</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="DK18" t="n">
-        <v>7.63</v>
+        <v>7.42</v>
       </c>
       <c r="DL18" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="DM18" t="n">
-        <v>61.91</v>
+        <v>60.17</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.82</v>
+        <v>11.83</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.64</v>
+        <v>13.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.91</v>
+        <v>4.66</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.55</v>
+        <v>62.58</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>20.54</v>
+        <v>20.42</v>
       </c>
       <c r="DY18" t="n">
-        <v>12.82</v>
+        <v>12.84</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.73</v>
+        <v>7.58</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.82</v>
+        <v>18.25</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -2338,10 +2338,10 @@
         <v>0.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.33</v>
+        <v>16.17</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.33</v>
+        <v>11.17</v>
       </c>
       <c r="BC4" t="n">
         <v>5</v>
@@ -2350,7 +2350,7 @@
         <v>19.17</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BF4" t="n">
         <v>2.67</v>
@@ -2563,10 +2563,10 @@
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.92</v>
+        <v>16.84</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.75</v>
+        <v>10.67</v>
       </c>
       <c r="DZ4" t="n">
         <v>6.16</v>
@@ -2575,7 +2575,7 @@
         <v>20</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="EC4" t="n">
         <v>2.42</v>
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="H9" t="n">
-        <v>90.33</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="K9" t="n">
-        <v>4.83</v>
+        <v>4.14</v>
       </c>
       <c r="L9" t="n">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="M9" t="n">
-        <v>33.5</v>
+        <v>28.71</v>
       </c>
       <c r="N9" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>14.43</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.33</v>
+        <v>13.57</v>
       </c>
       <c r="R9" t="n">
-        <v>7.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="T9" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>54.5</v>
+        <v>49</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>9.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>7</v>
+        <v>6.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.17</v>
+        <v>19.43</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>0.99</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AF9" t="n">
         <v>0.2</v>
@@ -4371,37 +4371,37 @@
         <v>1.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.449999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.91</v>
+        <v>4.42</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.55</v>
+        <v>4.08</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
@@ -4410,28 +4410,28 @@
         <v>100</v>
       </c>
       <c r="BT9" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.38</v>
+        <v>3.74</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.13</v>
+        <v>4.54</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="n">
         <v>4.52</v>
@@ -4446,7 +4446,7 @@
         <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CG9" t="n">
         <v>3.01</v>
@@ -4455,19 +4455,19 @@
         <v>1.46</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN9" t="n">
         <v>1.84</v>
@@ -4476,10 +4476,10 @@
         <v>1.29</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
@@ -4497,19 +4497,19 @@
         <v>1.93</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB9" t="n">
         <v>1.31</v>
@@ -4521,46 +4521,46 @@
         <v>3.47</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.91</v>
+        <v>74.17</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.63</v>
+        <v>3.33</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>30.09</v>
+        <v>27.58</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.82</v>
+        <v>14.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.73</v>
+        <v>12.42</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.27</v>
+        <v>9.5</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.82</v>
+        <v>47.92</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.449999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.55</v>
+        <v>6.17</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.37</v>
+        <v>20.33</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="10">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52.33</v>
+        <v>52.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.17</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.16</v>
+        <v>50.25</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.33</v>
+        <v>50.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.75</v>
+        <v>51.84</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.33</v>
+        <v>50.17</v>
       </c>
       <c r="Y13" t="n">
         <v>0.17</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.25</v>
+        <v>47.17</v>
       </c>
       <c r="DW13" t="n">
         <v>0.17</v>
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.5</v>
+        <v>52.33</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.92</v>
+        <v>52.83</v>
       </c>
       <c r="DW14" t="n">
         <v>0.08</v>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0.33</v>
@@ -7517,127 +7517,127 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" t="n">
-        <v>125.6</v>
+        <v>104.67</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN17" t="n">
-        <v>62.6</v>
+        <v>52.17</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.8</v>
+        <v>11.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.6</v>
+        <v>5.17</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>65.2</v>
+        <v>68.33</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>14.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>23.6</v>
+        <v>21.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="BJ17" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BK17" t="n">
         <v>1</v>
       </c>
-      <c r="BK17" t="n">
-        <v>0.82</v>
-      </c>
       <c r="BL17" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BP17" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.09</v>
+        <v>3.67</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.44</v>
@@ -7655,55 +7655,55 @@
         <v>1.46</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.76</v>
+        <v>3.38</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CN17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP17" t="n">
         <v>1.9</v>
       </c>
-      <c r="CO17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="CQ17" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7724,16 +7724,16 @@
         <v>2.05</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB17" t="n">
         <v>1.31</v>
@@ -7745,79 +7745,79 @@
         <v>3.36</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="DH17" t="n">
-        <v>119.73</v>
+        <v>109.75</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.55</v>
+        <v>5.58</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="DM17" t="n">
-        <v>59.45</v>
+        <v>54.5</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.82</v>
+        <v>12.58</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>64.37</v>
+        <v>66</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.18</v>
+        <v>13.58</v>
       </c>
       <c r="DY17" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="EA17" t="n">
-        <v>24.09</v>
+        <v>23.08</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="H4" t="n">
-        <v>128.33</v>
+        <v>122.14</v>
       </c>
       <c r="I4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="K4" t="n">
-        <v>7.17</v>
+        <v>6.57</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>74.83</v>
+        <v>69.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O4" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.5</v>
+        <v>14.43</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="S4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T4" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="V4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>63.17</v>
+        <v>60</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>16.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.17</v>
+        <v>9.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.33</v>
+        <v>6.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.83</v>
+        <v>20.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF4" t="n">
         <v>0.17</v>
@@ -2356,70 +2356,70 @@
         <v>2.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.08</v>
+        <v>8.77</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.77</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.98</v>
+        <v>5.77</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.76</v>
+        <v>6.49</v>
       </c>
       <c r="CC4" t="n">
         <v>1.72</v>
@@ -2428,22 +2428,22 @@
         <v>1.75</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
@@ -2452,19 +2452,19 @@
         <v>1.94</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2479,106 +2479,106 @@
         <v>1.61</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="DA4" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>119.33</v>
+        <v>116.69</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.84</v>
+        <v>5.61</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>65.67</v>
+        <v>63.69</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.16</v>
+        <v>12.38</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.25</v>
+        <v>13.77</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.84</v>
+        <v>6.54</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>61.42</v>
+        <v>59.85</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.84</v>
+        <v>16.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.67</v>
+        <v>10.31</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="EA4" t="n">
-        <v>20</v>
+        <v>19.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="5">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0.17</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AI18" t="n">
-        <v>114.67</v>
+        <v>110.86</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="AL18" t="n">
-        <v>9.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>62.67</v>
+        <v>58.43</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>4.43</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.83</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>66.67</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA18" t="n">
-        <v>20.33</v>
+        <v>18.14</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>11.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.83</v>
+        <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.67</v>
+        <v>17.57</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM18" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.33</v>
+        <v>5.15</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX18" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY18" t="n">
         <v>1.35</v>
@@ -8058,55 +8058,55 @@
         <v>1.33</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.06</v>
+        <v>5.84</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.67</v>
+        <v>6.4</v>
       </c>
       <c r="CC18" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8121,106 +8121,106 @@
         <v>1.64</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="DH18" t="n">
-        <v>117.25</v>
+        <v>115</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="DK18" t="n">
-        <v>7.42</v>
+        <v>7</v>
       </c>
       <c r="DL18" t="n">
         <v>1.16</v>
       </c>
       <c r="DM18" t="n">
-        <v>60.17</v>
+        <v>58.08</v>
       </c>
       <c r="DN18" t="n">
         <v>0.92</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.83</v>
+        <v>12.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.5</v>
+        <v>13.62</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.58</v>
+        <v>62.31</v>
       </c>
       <c r="DW18" t="n">
         <v>0.08</v>
       </c>
       <c r="DX18" t="n">
-        <v>20.42</v>
+        <v>19.23</v>
       </c>
       <c r="DY18" t="n">
-        <v>12.84</v>
+        <v>12.08</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.58</v>
+        <v>7.15</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.25</v>
+        <v>18.15</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="EC18" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="H2" t="n">
-        <v>89.67</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="L2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>36.83</v>
+        <v>33.86</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="P2" t="n">
-        <v>16.5</v>
+        <v>16.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.83</v>
+        <v>15</v>
       </c>
       <c r="R2" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47</v>
+        <v>45.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.17</v>
+        <v>10.86</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.17</v>
+        <v>22.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1553,46 +1553,46 @@
         <v>3.08</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.5</v>
+        <v>8.92</v>
       </c>
       <c r="BI2" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.17</v>
+        <v>3.46</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.36</v>
+        <v>5.03</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5.45</v>
+        <v>5.13</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="CC2" t="n">
         <v>6.09</v>
@@ -1625,7 +1625,7 @@
         <v>1.43</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG2" t="n">
         <v>2.74</v>
@@ -1634,13 +1634,13 @@
         <v>1.36</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL2" t="n">
         <v>2.06</v>
@@ -1649,16 +1649,16 @@
         <v>1.99</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1667,79 +1667,79 @@
         <v>3.15</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CU2" t="n">
         <v>1.39</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="DG2" t="n">
         <v>1.92</v>
       </c>
       <c r="DH2" t="n">
-        <v>87</v>
+        <v>84.38</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.92</v>
+        <v>34.39</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO2" t="n">
         <v>0.84</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.66</v>
+        <v>15.69</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.83</v>
+        <v>13.08</v>
       </c>
       <c r="DR2" t="n">
-        <v>9</v>
+        <v>8.77</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.16</v>
+        <v>44.39</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.42</v>
+        <v>10.31</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.92</v>
+        <v>22.31</v>
       </c>
       <c r="EB2" t="n">
         <v>1.12</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="H3" t="n">
-        <v>73.67</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="K3" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="L3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M3" t="n">
-        <v>45.83</v>
+        <v>44.29</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="P3" t="n">
-        <v>13.67</v>
+        <v>13.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.67</v>
+        <v>15.14</v>
       </c>
       <c r="R3" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.5</v>
+        <v>47.86</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.5</v>
+        <v>20.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,49 +1953,49 @@
         <v>2.67</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.92</v>
+        <v>7.62</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.69</v>
+        <v>4.33</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.58</v>
+        <v>4.24</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.26</v>
+        <v>4.17</v>
       </c>
       <c r="CC3" t="n">
         <v>6.09</v>
@@ -2025,43 +2025,43 @@
         <v>7.53</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG3" t="n">
         <v>2.73</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK3" t="n">
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO3" t="n">
         <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CR3" t="n">
         <v>1.51</v>
@@ -2076,106 +2076,106 @@
         <v>1.34</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC3" t="n">
         <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DH3" t="n">
-        <v>77.17</v>
+        <v>77.23</v>
       </c>
       <c r="DI3" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.58</v>
+        <v>38.31</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
         <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.75</v>
+        <v>13.46</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.17</v>
+        <v>14.46</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.92</v>
+        <v>7.69</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.66</v>
+        <v>46</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.84</v>
+        <v>5.85</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.75</v>
+        <v>19.85</v>
       </c>
       <c r="EB3" t="n">
         <v>1.13</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -2413,13 +2413,13 @@
         <v>1.43</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CA4" t="n">
         <v>5.77</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.49</v>
+        <v>6.48</v>
       </c>
       <c r="CC4" t="n">
         <v>1.72</v>
@@ -2467,16 +2467,16 @@
         <v>2.69</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="CV4" t="n">
         <v>1.7</v>
@@ -2485,22 +2485,22 @@
         <v>2.25</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="n">
         <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD4" t="n">
         <v>2.84</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.17</v>
@@ -2678,139 +2678,139 @@
         <v>2.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>89.5</v>
+        <v>92.14</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN5" t="n">
-        <v>33.33</v>
+        <v>36.71</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.17</v>
+        <v>15.71</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.67</v>
+        <v>10.57</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AU5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1</v>
       </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>21.17</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BP5" t="n">
-        <v>4.83</v>
+        <v>4.54</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.08</v>
+        <v>5.85</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY5" t="n">
         <v>4.45</v>
@@ -2819,31 +2819,31 @@
         <v>5.23</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.03</v>
+        <v>5.7</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.59</v>
+        <v>6.21</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.9</v>
@@ -2852,22 +2852,22 @@
         <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CO5" t="n">
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="CR5" t="n">
         <v>1.47</v>
@@ -2882,106 +2882,106 @@
         <v>1.43</v>
       </c>
       <c r="CV5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CY5" t="n">
         <v>1.87</v>
       </c>
-      <c r="CW5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>1.84</v>
-      </c>
       <c r="CZ5" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DH5" t="n">
-        <v>86.75</v>
+        <v>88.38</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.58</v>
+        <v>4.39</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
-        <v>36.08</v>
+        <v>37.69</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.75</v>
+        <v>15.07</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.92</v>
+        <v>11.77</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.83</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>41.84</v>
+        <v>42.46</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.84</v>
+        <v>11.31</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.08</v>
+        <v>7.62</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.67</v>
+        <v>20.85</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>95.2</v>
+        <v>88.83</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>40.83</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>13.4</v>
+        <v>12.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>47.6</v>
+        <v>43.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.4</v>
+        <v>19.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.83</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.92</v>
+        <v>4.77</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS6" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.12</v>
+        <v>5.1</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.81</v>
+        <v>5.87</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.98</v>
+        <v>4.09</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.11</v>
+        <v>4.24</v>
       </c>
       <c r="CC6" t="n">
         <v>6.34</v>
@@ -3237,154 +3237,154 @@
         <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
         <v>1.89</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.67</v>
+        <v>3.59</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CW6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CX6" t="n">
         <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.76</v>
+        <v>3.69</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.25</v>
+        <v>86.77</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
         <v>1.08</v>
       </c>
       <c r="DP6" t="n">
-        <v>15</v>
+        <v>14.54</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.5</v>
+        <v>12.31</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.58</v>
+        <v>43.08</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.67</v>
+        <v>11.62</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.67</v>
+        <v>7.77</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.92</v>
+        <v>18.62</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,52 +3484,52 @@
         <v>2.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="AI7" t="n">
-        <v>68.83</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.33</v>
+        <v>25.86</v>
       </c>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.67</v>
+        <v>14.29</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.17</v>
+        <v>15.43</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>39.5</v>
+        <v>42</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.33</v>
+        <v>5.86</v>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BD7" t="n">
-        <v>14.83</v>
+        <v>15.71</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="BH7" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BP7" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>4.08</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>3.83</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU7" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX7" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY7" t="n">
         <v>3.7</v>
@@ -3625,136 +3625,136 @@
         <v>3.9</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.88</v>
+        <v>3.81</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.21</v>
+        <v>4.12</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.06</v>
+        <v>6.67</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.029999999999999</v>
+        <v>7.55</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CH7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CO7" t="n">
         <v>1.37</v>
       </c>
-      <c r="CI7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CP7" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CS7" t="n">
         <v>2.96</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="CU7" t="n">
         <v>1.43</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY7" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.04</v>
+        <v>4.21</v>
       </c>
       <c r="DE7" t="n">
         <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.33</v>
+        <v>79.77</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.08</v>
+        <v>4.31</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.66</v>
+        <v>31.92</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.67</v>
+        <v>14.47</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.67</v>
+        <v>16.23</v>
       </c>
       <c r="DR7" t="n">
-        <v>8</v>
+        <v>8.31</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.34</v>
+        <v>46.23</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>9</v>
+        <v>8.69</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.08</v>
+        <v>5.85</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>77.5</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="L8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>36.17</v>
+        <v>36.57</v>
       </c>
       <c r="N8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>13.5</v>
+        <v>13.29</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.5</v>
+        <v>17.86</v>
       </c>
       <c r="R8" t="n">
-        <v>7.83</v>
+        <v>7.57</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.5</v>
+        <v>56.57</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.17</v>
+        <v>15.57</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.67</v>
+        <v>11.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.5</v>
+        <v>4.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.33</v>
+        <v>20.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.25</v>
+        <v>8.23</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.32</v>
+        <v>3.99</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.66</v>
+        <v>4.27</v>
       </c>
       <c r="CA8" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="CC8" t="n">
         <v>6.34</v>
@@ -4052,49 +4052,49 @@
         <v>1.36</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CK8" t="n">
         <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP8" t="n">
         <v>2.16</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CX8" t="n">
         <v>1.64</v>
@@ -4112,85 +4112,85 @@
         <v>1.39</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="DH8" t="n">
-        <v>69</v>
+        <v>70.62</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="DL8" t="n">
         <v>0.08</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.34</v>
+        <v>32.85</v>
       </c>
       <c r="DN8" t="n">
         <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.08</v>
+        <v>13.93</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.33</v>
+        <v>16.16</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.08</v>
+        <v>7.92</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.66</v>
+        <v>50.69</v>
       </c>
       <c r="DW8" t="n">
         <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.42</v>
+        <v>12.39</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.84</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.92</v>
+        <v>19.08</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0.14</v>
@@ -4290,52 +4290,52 @@
         <v>3.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>69.59999999999999</v>
+        <v>70.33</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,43 +4347,43 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.4</v>
+        <v>44.83</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BD9" t="n">
-        <v>21.6</v>
+        <v>22.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="BG9" t="n">
         <v>3.92</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.17</v>
+        <v>9.08</v>
       </c>
       <c r="BI9" t="n">
         <v>3.92</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL9" t="n">
         <v>1.08</v>
@@ -4392,13 +4392,13 @@
         <v>1.08</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="BQ9" t="n">
         <v>4.08</v>
@@ -4410,19 +4410,19 @@
         <v>100</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU9" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV9" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW9" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY9" t="n">
         <v>3.74</v>
@@ -4431,31 +4431,31 @@
         <v>4.54</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.43</v>
+        <v>6.84</v>
       </c>
       <c r="CD9" t="n">
-        <v>8</v>
+        <v>7.36</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.92</v>
@@ -4464,40 +4464,40 @@
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CO9" t="n">
         <v>1.29</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV9" t="n">
         <v>1.93</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX9" t="n">
         <v>1.55</v>
@@ -4512,55 +4512,55 @@
         <v>1.87</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DH9" t="n">
-        <v>74.17</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.83</v>
+        <v>3.23</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM9" t="n">
-        <v>27.58</v>
+        <v>27.92</v>
       </c>
       <c r="DN9" t="n">
         <v>1.08</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.5</v>
+        <v>14.46</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.42</v>
+        <v>12.38</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.5</v>
+        <v>9.77</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.92</v>
+        <v>47.08</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="DX9" t="n">
         <v>8.92</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.17</v>
+        <v>6.23</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.33</v>
+        <v>20.77</v>
       </c>
       <c r="EB9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -4603,58 +4603,58 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="H10" t="n">
-        <v>85.5</v>
+        <v>84.14</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="L10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>43.33</v>
+        <v>42.14</v>
       </c>
       <c r="N10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="P10" t="n">
-        <v>20.33</v>
+        <v>18.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.33</v>
+        <v>15.86</v>
       </c>
       <c r="R10" t="n">
-        <v>7.33</v>
+        <v>7.86</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>48</v>
+        <v>47.29</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.83</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.83</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.33</v>
+        <v>20</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,49 +4774,49 @@
         <v>3.17</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.42</v>
+        <v>10.54</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN10" t="n">
         <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="BR10" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT10" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BU10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BZ10" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CA10" t="n">
         <v>3.36</v>
       </c>
-      <c r="CA10" t="n">
-        <v>3.39</v>
-      </c>
       <c r="CB10" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC10" t="n">
         <v>2.16</v>
@@ -4852,25 +4852,25 @@
         <v>2.81</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN10" t="n">
         <v>1.75</v>
@@ -4879,13 +4879,13 @@
         <v>1.25</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.62</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS10" t="n">
         <v>3.17</v>
@@ -4897,73 +4897,73 @@
         <v>1.38</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="DB10" t="n">
         <v>1.38</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.92</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.92</v>
+        <v>5.69</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>49.16</v>
+        <v>48.08</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="DP10" t="n">
-        <v>19.33</v>
+        <v>18.62</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.42</v>
+        <v>16.62</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.25</v>
+        <v>49.69</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.66</v>
+        <v>13.15</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.42</v>
+        <v>8.92</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.16</v>
+        <v>21.38</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="H11" t="n">
-        <v>101.83</v>
+        <v>103.29</v>
       </c>
       <c r="I11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="K11" t="n">
-        <v>4.83</v>
+        <v>4.29</v>
       </c>
       <c r="L11" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M11" t="n">
-        <v>44.17</v>
+        <v>41.86</v>
       </c>
       <c r="N11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O11" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="P11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.83</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>10.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>53.17</v>
+        <v>52</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.83</v>
+        <v>12.29</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.67</v>
+        <v>20.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.83</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BX11" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.72</v>
+        <v>3.51</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="CC11" t="n">
         <v>5.44</v>
@@ -5252,13 +5252,13 @@
         <v>1.39</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI11" t="n">
         <v>1.85</v>
@@ -5267,10 +5267,10 @@
         <v>1.9</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM11" t="n">
         <v>2.03</v>
@@ -5279,13 +5279,13 @@
         <v>1.62</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CR11" t="n">
         <v>1.43</v>
@@ -5300,106 +5300,106 @@
         <v>1.44</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DB11" t="n">
         <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DH11" t="n">
-        <v>98.66</v>
+        <v>99.69</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>46</v>
+        <v>44.62</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13</v>
+        <v>13.08</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.75</v>
+        <v>8.15</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.84</v>
+        <v>51.31</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.42</v>
+        <v>13.08</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.33</v>
+        <v>8.92</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="EA11" t="n">
-        <v>22.5</v>
+        <v>22.38</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,52 +5902,52 @@
         <v>3.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>67.67</v>
+        <v>71.86</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>27.67</v>
+        <v>28.71</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14.86</v>
       </c>
       <c r="AR13" t="n">
-        <v>15</v>
+        <v>15.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.17</v>
+        <v>8.57</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>44.17</v>
+        <v>45.71</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.17</v>
+        <v>20.29</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.42</v>
+        <v>8.23</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.67</v>
+        <v>4.54</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY13" t="n">
         <v>3.85</v>
@@ -6043,34 +6043,34 @@
         <v>4.07</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.93</v>
+        <v>5.55</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.22</v>
+        <v>5.83</v>
       </c>
       <c r="CE13" t="n">
         <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK13" t="n">
         <v>1.68</v>
@@ -6088,10 +6088,10 @@
         <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="CR13" t="n">
         <v>1.49</v>
@@ -6106,19 +6106,19 @@
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CX13" t="n">
         <v>1.72</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA13" t="n">
         <v>1.68</v>
@@ -6127,22 +6127,22 @@
         <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="DH13" t="n">
-        <v>72.92</v>
+        <v>74.77</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
@@ -6151,28 +6151,28 @@
         <v>3.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.25</v>
+        <v>31.53</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.92</v>
+        <v>14.85</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.58</v>
+        <v>14.69</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.92</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.17</v>
+        <v>47.77</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.42</v>
+        <v>9.31</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.17</v>
+        <v>5.93</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.75</v>
+        <v>21.23</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.17</v>
@@ -6305,130 +6305,130 @@
         <v>2.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AI14" t="n">
-        <v>97.67</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.33</v>
+        <v>47.29</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>13.86</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.17</v>
+        <v>12.57</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>53.33</v>
+        <v>56.43</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA14" t="n">
-        <v>16.5</v>
+        <v>15.71</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BC14" t="n">
         <v>6</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.5</v>
+        <v>18.14</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.67</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.67</v>
+        <v>4.54</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT14" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY14" t="n">
         <v>1.41</v>
@@ -6446,22 +6446,22 @@
         <v>1.43</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="CE14" t="n">
         <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CG14" t="n">
         <v>3.08</v>
@@ -6470,49 +6470,49 @@
         <v>1.47</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CK14" t="n">
         <v>1.55</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM14" t="n">
         <v>2.32</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO14" t="n">
         <v>1.24</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
@@ -6524,7 +6524,7 @@
         <v>2.35</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB14" t="n">
         <v>1.26</v>
@@ -6533,82 +6533,82 @@
         <v>1.82</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="DH14" t="n">
-        <v>99.75</v>
+        <v>100.61</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.42</v>
+        <v>46.93</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.84</v>
+        <v>13.54</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.58</v>
+        <v>11.38</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.92</v>
+        <v>6</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.83</v>
+        <v>54.54</v>
       </c>
       <c r="DW14" t="n">
         <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.66</v>
+        <v>14.38</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.92</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.5</v>
+        <v>18.77</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AI15" t="n">
-        <v>65.67</v>
+        <v>67.14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.5</v>
+        <v>4.57</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN15" t="n">
-        <v>27.33</v>
+        <v>31.43</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.33</v>
+        <v>16.29</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.17</v>
+        <v>15.14</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.33</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>41.5</v>
+        <v>44.86</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.67</v>
+        <v>10.71</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>6.43</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.67</v>
+        <v>4.29</v>
       </c>
       <c r="BD15" t="n">
-        <v>16</v>
+        <v>17.71</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="BG15" t="n">
         <v>2.92</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.33</v>
+        <v>10.62</v>
       </c>
       <c r="BI15" t="n">
         <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM15" t="n">
         <v>1</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.92</v>
+        <v>6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.33</v>
+        <v>4.54</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS15" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY15" t="n">
         <v>3.66</v>
@@ -6849,28 +6849,28 @@
         <v>3.94</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.9</v>
+        <v>4.54</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.65</v>
+        <v>6.04</v>
       </c>
       <c r="CE15" t="n">
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI15" t="n">
         <v>1.87</v>
@@ -6879,16 +6879,16 @@
         <v>1.86</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO15" t="n">
         <v>1.31</v>
@@ -6897,121 +6897,121 @@
         <v>2.01</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV15" t="n">
         <v>1.99</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="DH15" t="n">
-        <v>69.33</v>
+        <v>69.84</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.08</v>
+        <v>3.69</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DM15" t="n">
-        <v>24.67</v>
+        <v>27.08</v>
       </c>
       <c r="DN15" t="n">
         <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.42</v>
+        <v>14.54</v>
       </c>
       <c r="DQ15" t="n">
         <v>15.08</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.5</v>
+        <v>9.85</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.42</v>
+        <v>46</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.5</v>
+        <v>10.07</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.92</v>
+        <v>4.23</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.34</v>
+        <v>16.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F16" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>101.67</v>
+        <v>99</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J16" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="K16" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M16" t="n">
-        <v>45.17</v>
+        <v>45.43</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1.67</v>
+        <v>2.29</v>
       </c>
       <c r="P16" t="n">
-        <v>13.83</v>
+        <v>15.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.5</v>
+        <v>15.86</v>
       </c>
       <c r="R16" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51.17</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.5</v>
+        <v>12.29</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.5</v>
+        <v>8.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AC16" t="n">
-        <v>24</v>
+        <v>23.71</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="AF16" t="n">
         <v>0.17</v>
@@ -7192,46 +7192,46 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.08</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BO16" t="n">
         <v>0.92</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT16" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CC16" t="n">
         <v>4.36</v>
@@ -7264,13 +7264,13 @@
         <v>4.78</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CH16" t="n">
         <v>1.27</v>
@@ -7279,37 +7279,37 @@
         <v>1.61</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CK16" t="n">
         <v>1.72</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM16" t="n">
         <v>2.05</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.73</v>
+        <v>4.79</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CS16" t="n">
         <v>3.24</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CU16" t="n">
         <v>1.36</v>
@@ -7327,94 +7327,94 @@
         <v>2.25</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DA16" t="n">
         <v>1.63</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.29</v>
+        <v>5.36</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="DH16" t="n">
-        <v>91.25</v>
+        <v>90.61</v>
       </c>
       <c r="DI16" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM16" t="n">
-        <v>39.67</v>
+        <v>40.23</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="DP16" t="n">
-        <v>13.33</v>
+        <v>14.07</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.34</v>
+        <v>15.08</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.08</v>
+        <v>7.92</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.92</v>
+        <v>47.54</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX16" t="n">
-        <v>12</v>
+        <v>11.93</v>
       </c>
       <c r="DY16" t="n">
         <v>8.08</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.42</v>
+        <v>21.46</v>
       </c>
       <c r="EB16" t="n">
         <v>1.32</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.33</v>
@@ -7517,43 +7517,43 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>104.67</v>
+        <v>104.14</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.17</v>
+        <v>5.71</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>52.17</v>
+        <v>53.43</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.33</v>
+        <v>12.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>14</v>
+        <v>13.43</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.17</v>
+        <v>5.57</v>
       </c>
       <c r="AT17" t="n">
         <v>1</v>
@@ -7562,46 +7562,46 @@
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>68.33</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.67</v>
+        <v>15.57</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.67</v>
+        <v>20.57</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BH17" t="n">
-        <v>8</v>
+        <v>8.31</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BJ17" t="n">
         <v>0.92</v>
@@ -7610,10 +7610,10 @@
         <v>1</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BN17" t="n">
         <v>0.92</v>
@@ -7622,22 +7622,22 @@
         <v>1.92</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY17" t="n">
         <v>1.44</v>
@@ -7655,169 +7655,169 @@
         <v>1.46</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CO17" t="n">
         <v>1.25</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="DB17" t="n">
         <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.75</v>
+        <v>109.07</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.58</v>
+        <v>5.84</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.58</v>
+        <v>11.23</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.58</v>
+        <v>12.39</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>66</v>
+        <v>65.31</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.58</v>
+        <v>14.15</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.33</v>
+        <v>8.85</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="EA17" t="n">
-        <v>23.08</v>
+        <v>22.38</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -8067,7 +8067,7 @@
         <v>1.51</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CE18" t="n">
         <v>1.19</v>
@@ -8109,16 +8109,16 @@
         <v>2.4</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="CV18" t="n">
         <v>1.79</v>
@@ -8127,22 +8127,22 @@
         <v>2.13</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DB18" t="n">
         <v>1.23</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD18" t="n">
         <v>2.75</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.83</v>
+        <v>44</v>
       </c>
       <c r="Y6" t="n">
         <v>0.17</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.08</v>
+        <v>43.15</v>
       </c>
       <c r="DW6" t="n">
         <v>0.15</v>
@@ -3517,7 +3517,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.29</v>
+        <v>14.43</v>
       </c>
       <c r="AR7" t="n">
         <v>15.43</v>
@@ -3748,7 +3748,7 @@
         <v>1.54</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.47</v>
+        <v>14.54</v>
       </c>
       <c r="DQ7" t="n">
         <v>16.23</v>
@@ -3839,7 +3839,7 @@
         <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>13.29</v>
+        <v>13.14</v>
       </c>
       <c r="Q8" t="n">
         <v>17.86</v>
@@ -4151,7 +4151,7 @@
         <v>1.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.93</v>
+        <v>13.85</v>
       </c>
       <c r="DQ8" t="n">
         <v>16.16</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52</v>
+        <v>51.86</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.31</v>
+        <v>51.23</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5499,52 +5499,52 @@
         <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>84.17</v>
+        <v>82.14</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.17</v>
+        <v>5.86</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.33</v>
+        <v>34.71</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.67</v>
+        <v>13.86</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>7.29</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47.17</v>
+        <v>47.29</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>12.86</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.33</v>
+        <v>4.71</v>
       </c>
       <c r="BD12" t="n">
-        <v>20.33</v>
+        <v>20.29</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.83</v>
+        <v>9.08</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.42</v>
+        <v>4.62</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BU12" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BY12" t="n">
         <v>2.98</v>
@@ -5640,28 +5640,28 @@
         <v>3.01</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.26</v>
+        <v>4.02</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.8</v>
+        <v>4.51</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI12" t="n">
         <v>1.7</v>
@@ -5673,7 +5673,7 @@
         <v>1.65</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM12" t="n">
         <v>2.14</v>
@@ -5682,13 +5682,13 @@
         <v>1.7</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="CR12" t="n">
         <v>1.51</v>
@@ -5697,7 +5697,7 @@
         <v>3.18</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CU12" t="n">
         <v>1.39</v>
@@ -5709,100 +5709,100 @@
         <v>2.17</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DA12" t="n">
         <v>1.72</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.08</v>
+        <v>86.69</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.42</v>
+        <v>5.31</v>
       </c>
       <c r="DL12" t="n">
         <v>0.92</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.33</v>
+        <v>42.38</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.42</v>
+        <v>15.54</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.42</v>
+        <v>14.46</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.42</v>
+        <v>7.08</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.25</v>
+        <v>47.31</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.75</v>
+        <v>13.16</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.42</v>
+        <v>4.15</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.16</v>
+        <v>21.08</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="13">
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.71</v>
+        <v>45.86</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.14</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.77</v>
+        <v>47.85</v>
       </c>
       <c r="DW13" t="n">
         <v>0.15</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.43</v>
+        <v>56.29</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.14</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.54</v>
+        <v>54.46</v>
       </c>
       <c r="DW14" t="n">
         <v>0.08</v>
@@ -7063,7 +7063,7 @@
         <v>2.29</v>
       </c>
       <c r="P16" t="n">
-        <v>15.14</v>
+        <v>15</v>
       </c>
       <c r="Q16" t="n">
         <v>15.86</v>
@@ -7375,7 +7375,7 @@
         <v>2.39</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.07</v>
+        <v>14</v>
       </c>
       <c r="DQ16" t="n">
         <v>15.08</v>
@@ -7577,19 +7577,19 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.57</v>
+        <v>15.71</v>
       </c>
       <c r="BB17" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.71</v>
+        <v>5.86</v>
       </c>
       <c r="BD17" t="n">
         <v>20.57</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
         <v>2.43</v>
@@ -7802,19 +7802,19 @@
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.15</v>
+        <v>14.23</v>
       </c>
       <c r="DY17" t="n">
         <v>8.85</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="EA17" t="n">
         <v>22.38</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC17" t="n">
         <v>2</v>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -8242,82 +8242,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="H19" t="n">
-        <v>90.83</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="K19" t="n">
-        <v>4.67</v>
+        <v>5.14</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M19" t="n">
-        <v>38.83</v>
+        <v>39.29</v>
       </c>
       <c r="N19" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="P19" t="n">
-        <v>14.5</v>
+        <v>14.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.83</v>
+        <v>14.29</v>
       </c>
       <c r="R19" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="U19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>46.5</v>
+        <v>47.29</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>21</v>
+        <v>21.29</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>1.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.08</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="BR19" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS19" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU19" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="CC19" t="n">
         <v>3.47</v>
@@ -8473,157 +8473,157 @@
         <v>3.86</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CN19" t="n">
         <v>1.84</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS19" t="n">
         <v>3.12</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CU19" t="n">
         <v>1.4</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.92</v>
+        <v>92</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>41</v>
+        <v>41.08</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.84</v>
+        <v>13.92</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.66</v>
+        <v>14.85</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.25</v>
+        <v>7.23</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>48.16</v>
+        <v>48.46</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.66</v>
+        <v>12.46</v>
       </c>
       <c r="DY19" t="n">
-        <v>9</v>
+        <v>8.85</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.67</v>
+        <v>22.69</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -3839,7 +3839,7 @@
         <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>13.14</v>
+        <v>13.29</v>
       </c>
       <c r="Q8" t="n">
         <v>17.86</v>
@@ -4151,7 +4151,7 @@
         <v>1.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.85</v>
+        <v>13.93</v>
       </c>
       <c r="DQ8" t="n">
         <v>16.16</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.33</v>
+        <v>82.86</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP2" t="n">
         <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.83</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.83</v>
+        <v>10.86</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.33</v>
+        <v>41.86</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.67</v>
+        <v>20.14</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT2" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>5.03</v>
@@ -1610,136 +1610,136 @@
         <v>5.13</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.79</v>
+        <v>4.24</v>
       </c>
       <c r="CB2" t="n">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="CC2" t="n">
-        <v>6.09</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="CD2" t="n">
-        <v>6.48</v>
+        <v>10.42</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="CK2" t="n">
         <v>1.53</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.87</v>
+        <v>3.72</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="CT2" t="n">
         <v>2.81</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="CX2" t="n">
         <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.24</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.38</v>
+        <v>83.64</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.39</v>
+        <v>33.93</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.69</v>
+        <v>15.22</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.08</v>
+        <v>12.93</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.77</v>
+        <v>8.93</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>44.39</v>
+        <v>43.58</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.31</v>
+        <v>10.08</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.23</v>
+        <v>7</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.08</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.31</v>
+        <v>21.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,127 +1875,127 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>80.67</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.33</v>
+        <v>-0.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.33</v>
+        <v>29.71</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.83</v>
+        <v>13.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.67</v>
+        <v>13.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.83</v>
+        <v>42</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.67</v>
+        <v>7.29</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="BC3" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>20.14</v>
       </c>
       <c r="BE3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK3" t="n">
         <v>0.93</v>
       </c>
-      <c r="BF3" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1</v>
-      </c>
       <c r="BL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY3" t="n">
         <v>4.33</v>
@@ -2013,16 +2013,16 @@
         <v>4.24</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="CC3" t="n">
-        <v>6.09</v>
+        <v>5.58</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.53</v>
+        <v>6.81</v>
       </c>
       <c r="CE3" t="n">
         <v>1.44</v>
@@ -2031,25 +2031,25 @@
         <v>3.06</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN3" t="n">
         <v>1.62</v>
@@ -2058,16 +2058,16 @@
         <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CT3" t="n">
         <v>2.67</v>
@@ -2076,22 +2076,22 @@
         <v>1.34</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB3" t="n">
         <v>1.41</v>
@@ -2100,82 +2100,82 @@
         <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.62</v>
+        <v>0.93</v>
       </c>
       <c r="DH3" t="n">
-        <v>77.23</v>
+        <v>76.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.54</v>
+        <v>2.79</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.31</v>
+        <v>37</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.46</v>
+        <v>13.28</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.46</v>
+        <v>14.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.69</v>
+        <v>8</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46</v>
+        <v>44.93</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.85</v>
+        <v>5.72</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.85</v>
+        <v>20.36</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0.14</v>
@@ -2275,139 +2275,139 @@
         <v>2.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AI4" t="n">
-        <v>110.33</v>
+        <v>110.57</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.5</v>
+        <v>52.29</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.83</v>
+        <v>13.14</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>13.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.67</v>
+        <v>7.86</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>59.67</v>
+        <v>57.86</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.17</v>
+        <v>15.29</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.17</v>
+        <v>10.29</v>
       </c>
       <c r="BC4" t="n">
         <v>5</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.17</v>
+        <v>18.29</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.77</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP4" t="n">
         <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS4" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.43</v>
@@ -2416,28 +2416,28 @@
         <v>1.45</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.77</v>
+        <v>5.67</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.48</v>
+        <v>6.38</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI4" t="n">
         <v>1.7</v>
@@ -2446,139 +2446,139 @@
         <v>2.12</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL4" t="n">
         <v>1.94</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV4" t="n">
         <v>1.7</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB4" t="n">
         <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="DH4" t="n">
-        <v>116.69</v>
+        <v>116.36</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.61</v>
+        <v>5.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.69</v>
+        <v>61.08</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.38</v>
+        <v>12.57</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.77</v>
+        <v>14.14</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.54</v>
+        <v>6.29</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59.85</v>
+        <v>58.93</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.31</v>
+        <v>15.86</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.31</v>
+        <v>9.93</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.69</v>
+        <v>19.22</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="5">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>91.83</v>
+        <v>87</v>
       </c>
       <c r="I7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>34.71</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>14.67</v>
+        <v>15.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.17</v>
+        <v>15.86</v>
       </c>
       <c r="R7" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.17</v>
+        <v>48.57</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.67</v>
+        <v>7.86</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.67</v>
+        <v>19.71</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AF7" t="n">
         <v>0.14</v>
@@ -3565,70 +3565,70 @@
         <v>3.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.380000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX7" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="CC7" t="n">
         <v>6.67</v>
@@ -3637,13 +3637,13 @@
         <v>7.55</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CH7" t="n">
         <v>1.36</v>
@@ -3658,136 +3658,136 @@
         <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
         <v>1.79</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.94</v>
+        <v>4.03</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW7" t="n">
         <v>2.18</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF7" t="n">
         <v>2.07</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.77</v>
+        <v>78.22</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.31</v>
+        <v>4.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.92</v>
+        <v>30.28</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.54</v>
+        <v>14.86</v>
       </c>
       <c r="DQ7" t="n">
-        <v>16.23</v>
+        <v>15.64</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.31</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.23</v>
+        <v>45.28</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.85</v>
+        <v>5.58</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="EA7" t="n">
-        <v>18</v>
+        <v>17.71</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="8">
@@ -4200,58 +4200,58 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H9" t="n">
-        <v>77.43000000000001</v>
+        <v>85.62</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="K9" t="n">
-        <v>4.14</v>
+        <v>4.62</v>
       </c>
       <c r="L9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M9" t="n">
-        <v>28.71</v>
+        <v>34.38</v>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="O9" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.57</v>
+        <v>13.25</v>
       </c>
       <c r="R9" t="n">
-        <v>8.289999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49</v>
+        <v>51.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.43</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.29</v>
+        <v>7.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.43</v>
+        <v>19.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4371,70 +4371,70 @@
         <v>1.83</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.92</v>
+        <v>3.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.08</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.92</v>
+        <v>3.71</v>
       </c>
       <c r="BJ9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BM9" t="n">
         <v>1</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BN9" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.08</v>
+        <v>4.29</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BT9" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV9" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW9" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.54</v>
+        <v>4.37</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.45</v>
+        <v>4.36</v>
       </c>
       <c r="CC9" t="n">
         <v>6.84</v>
@@ -4446,16 +4446,16 @@
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CG9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.92</v>
@@ -4464,34 +4464,34 @@
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CM9" t="n">
         <v>2.29</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="CR9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CU9" t="n">
         <v>1.44</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>1.45</v>
       </c>
       <c r="CV9" t="n">
         <v>1.93</v>
@@ -4500,67 +4500,67 @@
         <v>1.93</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CY9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO9" t="n">
         <v>1.93</v>
       </c>
-      <c r="CZ9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>74.15000000000001</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>1.62</v>
-      </c>
       <c r="DP9" t="n">
-        <v>14.46</v>
+        <v>14.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.38</v>
+        <v>12.29</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.77</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.08</v>
+        <v>48.64</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.92</v>
+        <v>9.57</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.23</v>
+        <v>6.79</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.77</v>
+        <v>20.64</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H10" t="n">
-        <v>84.14</v>
+        <v>85.12</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="K10" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M10" t="n">
-        <v>42.14</v>
+        <v>42.38</v>
       </c>
       <c r="N10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>18.86</v>
+        <v>17.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.86</v>
+        <v>16.12</v>
       </c>
       <c r="R10" t="n">
-        <v>7.86</v>
+        <v>7.88</v>
       </c>
       <c r="S10" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>47.29</v>
+        <v>48.12</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA10" t="n">
         <v>8</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>19.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,49 +4774,49 @@
         <v>3.17</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.54</v>
+        <v>10.71</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT10" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,19 +4825,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.37</v>
+        <v>3.16</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="CC10" t="n">
         <v>2.16</v>
@@ -4846,121 +4846,121 @@
         <v>2.14</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CN10" t="n">
         <v>1.76</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1.75</v>
       </c>
       <c r="CO10" t="n">
         <v>1.25</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CR10" t="n">
         <v>1.45</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA10" t="n">
         <v>1.89</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF10" t="n">
         <v>2.21</v>
       </c>
-      <c r="DD10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>2.23</v>
-      </c>
       <c r="DG10" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.15000000000001</v>
+        <v>85.64</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.08</v>
+        <v>47.79</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="DP10" t="n">
-        <v>18.62</v>
+        <v>18</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.62</v>
+        <v>16.71</v>
       </c>
       <c r="DR10" t="n">
         <v>8</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.69</v>
+        <v>50</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.15</v>
+        <v>13.64</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.92</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.23</v>
+        <v>4.79</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.38</v>
+        <v>20.86</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.14</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="AI11" t="n">
-        <v>95.5</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.83</v>
+        <v>4.57</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.83</v>
+        <v>46.86</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>13.71</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.17</v>
+        <v>12.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.5</v>
+        <v>49.86</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>13.43</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="BC11" t="n">
         <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>24.33</v>
+        <v>22.86</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.619999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.46</v>
+        <v>4.64</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW11" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY11" t="n">
         <v>3.35</v>
@@ -5237,169 +5237,169 @@
         <v>3.51</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.44</v>
+        <v>5.37</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.48</v>
+        <v>5.4</v>
       </c>
       <c r="CE11" t="n">
         <v>1.39</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK11" t="n">
         <v>1.48</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CO11" t="n">
         <v>1.32</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CR11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="EB11" t="n">
         <v>1.43</v>
       </c>
-      <c r="CS11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CZ11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>99.69</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>2</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>13</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>51.23</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>22.38</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1.45</v>
-      </c>
       <c r="EC11" t="n">
-        <v>2.93</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5499,130 +5499,130 @@
         <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AI12" t="n">
-        <v>82.14</v>
+        <v>86.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="AM12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1.14</v>
       </c>
-      <c r="AN12" t="n">
-        <v>34.71</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BP12" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BU12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BY12" t="n">
         <v>2.98</v>
@@ -5640,34 +5640,34 @@
         <v>3.01</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.02</v>
+        <v>3.79</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.51</v>
+        <v>4.21</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CH12" t="n">
         <v>1.31</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK12" t="n">
         <v>1.65</v>
@@ -5676,133 +5676,133 @@
         <v>2.08</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN12" t="n">
         <v>1.7</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.28</v>
+        <v>4.34</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CX12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DA12" t="n">
         <v>1.7</v>
       </c>
-      <c r="CY12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.72</v>
-      </c>
       <c r="DB12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.39</v>
+        <v>4.48</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="DG12" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.69</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.38</v>
+        <v>44.57</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.54</v>
+        <v>15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.46</v>
+        <v>14.79</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.08</v>
+        <v>6.71</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.31</v>
+        <v>48.71</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.16</v>
+        <v>13</v>
       </c>
       <c r="DY12" t="n">
         <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.08</v>
+        <v>21.71</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="13">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
@@ -5824,49 +5824,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>78.17</v>
+        <v>76.86</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="K13" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M13" t="n">
-        <v>34.83</v>
+        <v>33.86</v>
       </c>
       <c r="N13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="O13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="P13" t="n">
-        <v>14.83</v>
+        <v>15.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.17</v>
+        <v>14.29</v>
       </c>
       <c r="R13" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.17</v>
+        <v>50.57</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.67</v>
+        <v>6.86</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.33</v>
+        <v>20.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>0.43</v>
@@ -5983,70 +5983,70 @@
         <v>2.57</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.23</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT13" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV13" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.85</v>
+        <v>4.46</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.07</v>
+        <v>4.74</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="CC13" t="n">
         <v>5.55</v>
@@ -6055,19 +6055,19 @@
         <v>5.83</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.03</v>
@@ -6076,7 +6076,7 @@
         <v>1.68</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM13" t="n">
         <v>2.09</v>
@@ -6085,28 +6085,28 @@
         <v>1.66</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CU13" t="n">
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW13" t="n">
         <v>2.1</v>
@@ -6115,64 +6115,64 @@
         <v>1.72</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.11</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.11</v>
+        <v>4.04</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DH13" t="n">
-        <v>74.77</v>
+        <v>74.36</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.53</v>
+        <v>31.28</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.85</v>
+        <v>15.14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.69</v>
+        <v>14.72</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.85</v>
+        <v>48.22</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.93</v>
+        <v>6.08</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.23</v>
+        <v>20.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="14">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G15" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="H15" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="K15" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="L15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>21.57</v>
       </c>
       <c r="N15" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="P15" t="n">
-        <v>12.5</v>
+        <v>12.86</v>
       </c>
       <c r="Q15" t="n">
         <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>9.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="T15" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.33</v>
+        <v>46.71</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.67</v>
+        <v>14.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.86</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.62</v>
+        <v>10.71</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="CC15" t="n">
         <v>4.54</v>
@@ -6861,31 +6861,31 @@
         <v>6.04</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH15" t="n">
         <v>1.41</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN15" t="n">
         <v>1.86</v>
@@ -6894,10 +6894,10 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
@@ -6918,100 +6918,100 @@
         <v>1.88</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY15" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DH15" t="n">
-        <v>69.84</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.69</v>
+        <v>3.86</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM15" t="n">
-        <v>27.08</v>
+        <v>26.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.54</v>
+        <v>14.58</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.08</v>
+        <v>15.07</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.85</v>
+        <v>9.93</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46</v>
+        <v>45.78</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.07</v>
+        <v>9.92</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.23</v>
+        <v>4.08</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.31</v>
+        <v>16.07</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="16">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F18" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="H18" t="n">
-        <v>119.83</v>
+        <v>120.14</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>57.67</v>
+        <v>59</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="P18" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T18" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>58.5</v>
+        <v>59.71</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>13.17</v>
+        <v>12.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.83</v>
+        <v>18.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.57</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.619999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.15</v>
+        <v>5.07</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="CA18" t="n">
-        <v>5.84</v>
+        <v>6.13</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.4</v>
+        <v>7.07</v>
       </c>
       <c r="CC18" t="n">
         <v>1.51</v>
@@ -8073,154 +8073,154 @@
         <v>1.19</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CO18" t="n">
         <v>1.09</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="CT18" t="n">
         <v>3.15</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="CX18" t="n">
         <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.26</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="DH18" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="DK18" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="DL18" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DM18" t="n">
-        <v>58.08</v>
+        <v>58.72</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.46</v>
+        <v>12.36</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.62</v>
+        <v>13.28</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.61</v>
+        <v>4.35</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.31</v>
+        <v>62.64</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX18" t="n">
-        <v>19.23</v>
+        <v>19.57</v>
       </c>
       <c r="DY18" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.15</v>
+        <v>7.64</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.15</v>
+        <v>18</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>98.86</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>43.17</v>
+        <v>45</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.17</v>
+        <v>13.43</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.5</v>
+        <v>15.43</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.33</v>
+        <v>7.14</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>49.83</v>
+        <v>50.86</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13</v>
+        <v>13.43</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.67</v>
+        <v>10.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BD19" t="n">
-        <v>24.33</v>
+        <v>23.57</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS19" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU19" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY19" t="n">
         <v>2.89</v>
@@ -8461,25 +8461,25 @@
         <v>3.46</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.86</v>
+        <v>3.65</v>
       </c>
       <c r="CE19" t="n">
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
@@ -8488,13 +8488,13 @@
         <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM19" t="n">
         <v>2.36</v>
@@ -8527,7 +8527,7 @@
         <v>1.86</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX19" t="n">
         <v>1.57</v>
@@ -8539,91 +8539,91 @@
         <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="DH19" t="n">
-        <v>92</v>
+        <v>94.14</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.69</v>
+        <v>4.78</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.08</v>
+        <v>42.14</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.92</v>
+        <v>14</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.85</v>
+        <v>14.86</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.23</v>
+        <v>7.14</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>48.46</v>
+        <v>49.08</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.46</v>
+        <v>12.72</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.85</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.69</v>
+        <v>22.43</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -2022,7 +2022,7 @@
         <v>5.58</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="CE3" t="n">
         <v>1.44</v>
@@ -2100,7 +2100,7 @@
         <v>2.29</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>5.67</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.38</v>
+        <v>6.37</v>
       </c>
       <c r="CC4" t="n">
         <v>1.66</v>
@@ -2473,7 +2473,7 @@
         <v>2.56</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CU4" t="n">
         <v>1.57</v>
@@ -2488,7 +2488,7 @@
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.41</v>
@@ -2497,13 +2497,13 @@
         <v>1.96</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC4" t="n">
         <v>1.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE4" t="n">
         <v>0.14</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="H5" t="n">
-        <v>84</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>38.83</v>
+        <v>37.86</v>
       </c>
       <c r="N5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>14.33</v>
+        <v>13.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.17</v>
+        <v>13.57</v>
       </c>
       <c r="R5" t="n">
-        <v>9.17</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>46</v>
+        <v>45.71</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.67</v>
+        <v>6.29</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.17</v>
+        <v>19.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AF5" t="n">
         <v>0.14</v>
@@ -2759,70 +2759,70 @@
         <v>2.86</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.38</v>
+        <v>10.57</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.54</v>
+        <v>4.86</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.85</v>
+        <v>5.71</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.45</v>
+        <v>4.12</v>
       </c>
       <c r="BZ5" t="n">
-        <v>5.23</v>
+        <v>4.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="CC5" t="n">
         <v>5.7</v>
@@ -2834,7 +2834,7 @@
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG5" t="n">
         <v>2.84</v>
@@ -2846,16 +2846,16 @@
         <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK5" t="n">
         <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN5" t="n">
         <v>1.97</v>
@@ -2864,10 +2864,10 @@
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CR5" t="n">
         <v>1.47</v>
@@ -2882,106 +2882,106 @@
         <v>1.43</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
         <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.38</v>
+        <v>87.22</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.69</v>
+        <v>37.29</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.07</v>
+        <v>14.78</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.77</v>
+        <v>12.07</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.46</v>
+        <v>42.57</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.31</v>
+        <v>11.07</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.62</v>
+        <v>7.36</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.85</v>
+        <v>20.43</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,127 +3084,127 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>85.62</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>33.71</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BL6" t="n">
         <v>0.71</v>
       </c>
-      <c r="AP6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>16.14</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>17.86</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BM6" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.77</v>
+        <v>4.14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BY6" t="n">
         <v>5.1</v>
@@ -3222,22 +3222,22 @@
         <v>5.87</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.24</v>
+        <v>4.16</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.34</v>
+        <v>5.94</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.3</v>
+        <v>5.91</v>
       </c>
       <c r="CE6" t="n">
         <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG6" t="n">
         <v>2.83</v>
@@ -3246,22 +3246,22 @@
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CK6" t="n">
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CO6" t="n">
         <v>1.33</v>
@@ -3270,7 +3270,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
@@ -3285,19 +3285,19 @@
         <v>1.43</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA6" t="n">
         <v>1.84</v>
@@ -3306,85 +3306,85 @@
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.77</v>
+        <v>87</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM6" t="n">
-        <v>37</v>
+        <v>38.07</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.54</v>
+        <v>14.72</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.31</v>
+        <v>12.07</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.08</v>
+        <v>7.93</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.15</v>
+        <v>44.07</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.62</v>
+        <v>12.29</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.77</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.84</v>
+        <v>3.93</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.62</v>
+        <v>18.21</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>60.5</v>
+        <v>63.14</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.5</v>
+        <v>25.71</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>43.83</v>
+        <v>42.43</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.5</v>
+        <v>18.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.23</v>
+        <v>7.93</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>3.99</v>
@@ -4028,55 +4028,55 @@
         <v>4.27</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.93</v>
+        <v>4.13</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="CC8" t="n">
-        <v>6.34</v>
+        <v>7.58</v>
       </c>
       <c r="CD8" t="n">
-        <v>7.15</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="CH8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CO8" t="n">
         <v>1.36</v>
       </c>
-      <c r="CI8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1.37</v>
-      </c>
       <c r="CP8" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.92</v>
+        <v>3.81</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
@@ -4091,106 +4091,106 @@
         <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="CX8" t="n">
         <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.23</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DC8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG8" t="n">
         <v>2.22</v>
       </c>
-      <c r="DD8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>2.38</v>
-      </c>
       <c r="DH8" t="n">
-        <v>70.62</v>
+        <v>71.22</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.62</v>
+        <v>3.36</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.85</v>
+        <v>31.14</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.93</v>
+        <v>14.14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.16</v>
+        <v>15.93</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.92</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.69</v>
+        <v>49.5</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.39</v>
+        <v>11.93</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.390000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.08</v>
+        <v>19.36</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -4428,7 +4428,7 @@
         <v>3.64</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="CA9" t="n">
         <v>4.11</v>
@@ -4488,7 +4488,7 @@
         <v>3</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CU9" t="n">
         <v>1.44</v>
@@ -4515,7 +4515,7 @@
         <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DD9" t="n">
         <v>3.58</v>
@@ -4648,7 +4648,7 @@
         <v>17.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.12</v>
+        <v>16.25</v>
       </c>
       <c r="R10" t="n">
         <v>7.88</v>
@@ -4684,7 +4684,7 @@
         <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.25</v>
+        <v>19.12</v>
       </c>
       <c r="AD10" t="n">
         <v>1.48</v>
@@ -4960,7 +4960,7 @@
         <v>18</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.71</v>
+        <v>16.79</v>
       </c>
       <c r="DR10" t="n">
         <v>8</v>
@@ -4990,7 +4990,7 @@
         <v>4.79</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.86</v>
+        <v>20.78</v>
       </c>
       <c r="EB10" t="n">
         <v>1.54</v>
@@ -5129,7 +5129,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.71</v>
+        <v>13.86</v>
       </c>
       <c r="AR11" t="n">
         <v>12.71</v>
@@ -5360,7 +5360,7 @@
         <v>2.07</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.36</v>
+        <v>13.43</v>
       </c>
       <c r="DQ11" t="n">
         <v>12.86</v>
@@ -6040,13 +6040,13 @@
         <v>4.46</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.74</v>
+        <v>4.73</v>
       </c>
       <c r="CA13" t="n">
         <v>3.78</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CC13" t="n">
         <v>5.55</v>
@@ -6097,7 +6097,7 @@
         <v>1.48</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CT13" t="n">
         <v>2.79</v>
@@ -6109,13 +6109,13 @@
         <v>1.8</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX13" t="n">
         <v>1.72</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.11</v>
@@ -6130,7 +6130,7 @@
         <v>2.19</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="DE13" t="n">
         <v>0.22</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H14" t="n">
+        <v>105.71</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="H14" t="n">
-        <v>101.83</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M14" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>10</v>
-      </c>
-      <c r="R14" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U14" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V14" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.33</v>
+        <v>54.29</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.83</v>
+        <v>13.86</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.5</v>
+        <v>20.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AF14" t="n">
         <v>0.14</v>
@@ -6386,49 +6386,49 @@
         <v>2.29</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.92</v>
+        <v>3.79</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS14" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU14" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.3</v>
+        <v>5.46</v>
       </c>
       <c r="CC14" t="n">
         <v>1.65</v>
@@ -6461,40 +6461,40 @@
         <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK14" t="n">
         <v>1.55</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN14" t="n">
         <v>1.83</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6509,106 +6509,106 @@
         <v>1.51</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CX14" t="n">
         <v>1.57</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DB14" t="n">
         <v>1.26</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DH14" t="n">
-        <v>100.61</v>
+        <v>102.64</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.93</v>
+        <v>48.64</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.54</v>
+        <v>13.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.38</v>
+        <v>11.72</v>
       </c>
       <c r="DR14" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.46</v>
+        <v>55.29</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.38</v>
+        <v>14.78</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.609999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.77</v>
+        <v>5.79</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.77</v>
+        <v>19.22</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="15">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0.29</v>
@@ -7111,127 +7111,127 @@
         <v>3.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>80.83</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>34.17</v>
+        <v>31.71</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.83</v>
+        <v>13.14</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.17</v>
+        <v>13.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>8.43</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.67</v>
+        <v>42.86</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.5</v>
+        <v>10.57</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.83</v>
+        <v>18.14</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.539999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN16" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT16" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY16" t="n">
         <v>2.69</v>
@@ -7252,28 +7252,28 @@
         <v>2.85</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.36</v>
+        <v>4.81</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.78</v>
+        <v>5.3</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI16" t="n">
         <v>1.61</v>
@@ -7282,25 +7282,25 @@
         <v>2.21</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.79</v>
+        <v>4.7</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7318,7 +7318,7 @@
         <v>1.62</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CX16" t="n">
         <v>1.79</v>
@@ -7333,88 +7333,88 @@
         <v>1.63</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.61</v>
+        <v>90.22</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.69</v>
+        <v>4.43</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.23</v>
+        <v>38.57</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="DP16" t="n">
-        <v>14</v>
+        <v>14.07</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.08</v>
+        <v>14.72</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.92</v>
+        <v>7.71</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.54</v>
+        <v>46.43</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.93</v>
+        <v>11.43</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.08</v>
+        <v>7.71</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.46</v>
+        <v>20.92</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G17" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="H17" t="n">
-        <v>114.83</v>
+        <v>116.14</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="L17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M17" t="n">
-        <v>56.83</v>
+        <v>56.29</v>
       </c>
       <c r="N17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O17" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="P17" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.17</v>
+        <v>11.71</v>
       </c>
       <c r="R17" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="V17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>63.67</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.5</v>
+        <v>11.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>24.5</v>
+        <v>23.29</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,49 +7595,49 @@
         <v>2.43</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.31</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BK17" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.44</v>
@@ -7655,10 +7655,10 @@
         <v>1.46</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="CC17" t="n">
         <v>3.08</v>
@@ -7670,40 +7670,40 @@
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
         <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7718,106 +7718,106 @@
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.07</v>
+        <v>110.14</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.84</v>
+        <v>5.79</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM17" t="n">
-        <v>55</v>
+        <v>54.86</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.23</v>
+        <v>11.14</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.39</v>
+        <v>12.57</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>65.31</v>
+        <v>65.5</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.23</v>
+        <v>13.64</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.85</v>
+        <v>8.43</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="EA17" t="n">
-        <v>22.38</v>
+        <v>21.93</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -6287,19 +6287,19 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
         <v>8.289999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.57</v>
+        <v>5.71</v>
       </c>
       <c r="AC14" t="n">
         <v>20.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE14" t="n">
         <v>2.29</v>
@@ -6593,13 +6593,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.78</v>
+        <v>14.86</v>
       </c>
       <c r="DY14" t="n">
         <v>9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.79</v>
+        <v>5.86</v>
       </c>
       <c r="EA14" t="n">
         <v>19.22</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.86</v>
+        <v>43</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.14</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.43</v>
+        <v>46.5</v>
       </c>
       <c r="DW16" t="n">
         <v>0.22</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>64.29000000000001</v>
+        <v>64.14</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>65.5</v>
+        <v>65.42</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G2" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="H2" t="n">
-        <v>84.43000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>33.86</v>
+        <v>35.25</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>0.71</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>16.43</v>
+        <v>15.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="R2" t="n">
-        <v>7.29</v>
+        <v>7.88</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.29</v>
+        <v>44.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.86</v>
+        <v>11.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.86</v>
+        <v>22.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.93</v>
+        <v>9.07</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.03</v>
+        <v>4.76</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5.13</v>
+        <v>4.9</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
       <c r="CC2" t="n">
         <v>8.789999999999999</v>
@@ -1628,22 +1628,22 @@
         <v>2.94</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CM2" t="n">
         <v>2.03</v>
@@ -1655,10 +1655,10 @@
         <v>1.34</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1673,73 +1673,73 @@
         <v>1.44</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB2" t="n">
         <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.64</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.14</v>
+        <v>3.53</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DM2" t="n">
-        <v>33.93</v>
+        <v>34.67</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.85</v>
+        <v>1.13</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.22</v>
+        <v>14.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.93</v>
+        <v>12.8</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.93</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.58</v>
+        <v>43.13</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.08</v>
+        <v>10.47</v>
       </c>
       <c r="DY2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="3">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,52 +2678,52 @@
         <v>2.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>92.14</v>
+        <v>95.75</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.71</v>
+        <v>38.88</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.71</v>
+        <v>15.12</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>39.43</v>
+        <v>42.38</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>12.88</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.43</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.43</v>
+        <v>22.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.57</v>
+        <v>10.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.86</v>
+        <v>4.93</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>4.12</v>
@@ -2819,49 +2819,49 @@
         <v>4.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.7</v>
+        <v>5.32</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.21</v>
+        <v>5.73</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF5" t="n">
         <v>2.86</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.89</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP5" t="n">
         <v>2.05</v>
@@ -2885,103 +2885,103 @@
         <v>1.89</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DG5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.22</v>
+        <v>89.47</v>
       </c>
       <c r="DI5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.29</v>
+        <v>4.14</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.29</v>
+        <v>38.4</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.78</v>
+        <v>14.53</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="DR5" t="n">
-        <v>9</v>
+        <v>9.07</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.57</v>
+        <v>43.93</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.07</v>
+        <v>11.6</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.36</v>
+        <v>7.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.72</v>
+        <v>3.87</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.43</v>
+        <v>20.93</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="n">
-        <v>79.29000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>36.57</v>
+        <v>35.88</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="R8" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.57</v>
+        <v>55.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.57</v>
+        <v>15.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.29</v>
+        <v>11.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.43</v>
+        <v>20.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.43</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.93</v>
+        <v>8.07</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.99</v>
+        <v>3.84</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.27</v>
+        <v>4.09</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="CC8" t="n">
         <v>7.58</v>
@@ -4043,10 +4043,10 @@
         <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4055,142 +4055,142 @@
         <v>1.73</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CO8" t="n">
         <v>1.36</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ8" t="n">
         <v>3.81</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV8" t="n">
         <v>1.79</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="DH8" t="n">
-        <v>71.22</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.14</v>
+        <v>31.13</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.14</v>
+        <v>14.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.93</v>
+        <v>16.13</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.220000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.5</v>
+        <v>49.46</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.93</v>
+        <v>12</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.36</v>
+        <v>19.27</v>
       </c>
       <c r="EB8" t="n">
         <v>1.24</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="9">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.86</v>
-      </c>
       <c r="H11" t="n">
-        <v>103.29</v>
+        <v>100.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.29</v>
+        <v>4.88</v>
       </c>
       <c r="L11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>41.86</v>
+        <v>42.12</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>12.38</v>
       </c>
       <c r="R11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.86</v>
+        <v>49.38</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.29</v>
+        <v>4.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.71</v>
+        <v>20.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.93</v>
+        <v>9.27</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11" t="n">
         <v>0.93</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.21</v>
+        <v>4.47</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.64</v>
+        <v>4.73</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.35</v>
+        <v>3.63</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.51</v>
+        <v>3.69</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CC11" t="n">
         <v>5.37</v>
@@ -5252,10 +5252,10 @@
         <v>1.39</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH11" t="n">
         <v>1.39</v>
@@ -5267,139 +5267,139 @@
         <v>1.89</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN11" t="n">
         <v>1.64</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CU11" t="n">
         <v>1.45</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DB11" t="n">
         <v>1.33</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DH11" t="n">
-        <v>98.86</v>
+        <v>97.67</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.43</v>
+        <v>4.74</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.36</v>
+        <v>44.33</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.43</v>
+        <v>13.34</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.86</v>
+        <v>12.53</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.86</v>
+        <v>49.6</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.720000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.78</v>
+        <v>21.6</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="G12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H12" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M12" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>92</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M12" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P12" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
         <v>0.25</v>
@@ -5580,49 +5580,49 @@
         <v>3.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.07</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BU12" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,16 +5631,16 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CB12" t="n">
         <v>3.56</v>
@@ -5652,10 +5652,10 @@
         <v>4.21</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CG12" t="n">
         <v>2.54</v>
@@ -5664,31 +5664,31 @@
         <v>1.31</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK12" t="n">
         <v>1.65</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="CR12" t="n">
         <v>1.52</v>
@@ -5703,73 +5703,73 @@
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CX12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DA12" t="n">
         <v>1.71</v>
       </c>
-      <c r="CY12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.7</v>
-      </c>
       <c r="DB12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.79000000000001</v>
+        <v>89.27</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DM12" t="n">
-        <v>44.57</v>
+        <v>45.73</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="DP12" t="n">
-        <v>15</v>
+        <v>15.07</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.79</v>
+        <v>14.87</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.71</v>
+        <v>6.53</v>
       </c>
       <c r="DS12" t="n">
         <v>0.14</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.71</v>
+        <v>49.13</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>13</v>
+        <v>13.67</v>
       </c>
       <c r="DY12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.71</v>
+        <v>21.8</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,139 +5902,139 @@
         <v>3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>71.86</v>
+        <v>72.62</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AL13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG13" t="n">
         <v>3</v>
       </c>
-      <c r="AM13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>28.71</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>15.14</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.21</v>
-      </c>
       <c r="BH13" t="n">
-        <v>8.210000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY13" t="n">
         <v>4.46</v>
@@ -6043,46 +6043,46 @@
         <v>4.73</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.55</v>
+        <v>5.21</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.83</v>
+        <v>5.46</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO13" t="n">
         <v>1.38</v>
@@ -6091,16 +6091,16 @@
         <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CR13" t="n">
         <v>1.48</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CU13" t="n">
         <v>1.38</v>
@@ -6109,70 +6109,70 @@
         <v>1.8</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>74.36</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.86</v>
+        <v>4.06</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.28</v>
+        <v>32.8</v>
       </c>
       <c r="DN13" t="n">
         <v>0.93</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.14</v>
+        <v>15.4</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.72</v>
+        <v>14.73</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.43</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.22</v>
+        <v>48.4</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.08</v>
+        <v>6.27</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.28</v>
+        <v>3.53</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.57</v>
+        <v>20.47</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="14">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
       </c>
-      <c r="AH15" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AI15" t="n">
-        <v>67.14</v>
+        <v>65.62</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.57</v>
+        <v>4.12</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>31.43</v>
+        <v>30.12</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.29</v>
+        <v>16.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.14</v>
+        <v>15.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>10.88</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.86</v>
+        <v>44.88</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.71</v>
+        <v>9.75</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.43</v>
+        <v>5.75</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.71</v>
+        <v>17.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.71</v>
+        <v>10.73</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
         <v>0.93</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.93</v>
+        <v>5.87</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
         <v>3.58</v>
@@ -6849,16 +6849,16 @@
         <v>3.84</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.04</v>
+        <v>5.88</v>
       </c>
       <c r="CE15" t="n">
         <v>1.39</v>
@@ -6867,25 +6867,25 @@
         <v>2.87</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL15" t="n">
         <v>1.95</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN15" t="n">
         <v>1.86</v>
@@ -6912,10 +6912,10 @@
         <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
@@ -6927,91 +6927,91 @@
         <v>2.35</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DH15" t="n">
-        <v>69.06999999999999</v>
+        <v>68.13</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.86</v>
+        <v>3.66</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM15" t="n">
-        <v>26.5</v>
+        <v>26.13</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.58</v>
+        <v>14.67</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.07</v>
+        <v>15.13</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.93</v>
+        <v>10.4</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.78</v>
+        <v>45.73</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.92</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.86</v>
+        <v>5.54</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.08</v>
+        <v>3.93</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.07</v>
+        <v>15.93</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="16">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.29</v>
@@ -7517,127 +7517,127 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>104.14</v>
+        <v>105.88</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>53.43</v>
+        <v>56.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP17" t="n">
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.43</v>
+        <v>11.88</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.43</v>
+        <v>13.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="AT17" t="n">
         <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>66.70999999999999</v>
+        <v>66.88</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.71</v>
+        <v>15.25</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.57</v>
+        <v>20.62</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BJ17" t="n">
         <v>0.93</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.64</v>
+        <v>3.93</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY17" t="n">
         <v>1.44</v>
@@ -7655,16 +7655,16 @@
         <v>1.46</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
@@ -7679,22 +7679,22 @@
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.95</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CL17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CO17" t="n">
         <v>1.26</v>
@@ -7703,121 +7703,121 @@
         <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="DE17" t="n">
         <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DG17" t="n">
         <v>2.93</v>
       </c>
       <c r="DH17" t="n">
-        <v>110.14</v>
+        <v>110.67</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.79</v>
+        <v>5.73</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.86</v>
+        <v>56.4</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.57</v>
+        <v>12.53</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>65.42</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.64</v>
+        <v>13.53</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.43</v>
+        <v>8.33</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.93</v>
+        <v>21.87</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>44.25</v>
+        <v>44.12</v>
       </c>
       <c r="Y2" t="n">
         <v>0.25</v>
@@ -1607,13 +1607,13 @@
         <v>4.76</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.9</v>
+        <v>4.83</v>
       </c>
       <c r="CA2" t="n">
         <v>4.17</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="CC2" t="n">
         <v>8.789999999999999</v>
@@ -1661,22 +1661,22 @@
         <v>3.71</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX2" t="n">
         <v>1.65</v>
@@ -1694,10 +1694,10 @@
         <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.13</v>
+        <v>43.07</v>
       </c>
       <c r="DW2" t="n">
         <v>0.2</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>74.29000000000001</v>
+        <v>74.38</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K3" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>44.29</v>
+        <v>43.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P3" t="n">
-        <v>13.14</v>
+        <v>12.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.14</v>
+        <v>14.75</v>
       </c>
       <c r="R3" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.86</v>
+        <v>46.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>10.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.86</v>
+        <v>6.38</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.57</v>
+        <v>19.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,49 +1953,49 @@
         <v>2.86</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK3" t="n">
         <v>0.93</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.33</v>
+        <v>4.97</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.24</v>
+        <v>5.01</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="CC3" t="n">
         <v>5.58</v>
@@ -2028,28 +2028,28 @@
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN3" t="n">
         <v>1.62</v>
@@ -2058,124 +2058,124 @@
         <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DH3" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="DK3" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DL3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>37</v>
+        <v>36.93</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.28</v>
+        <v>12.93</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="DR3" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.93</v>
+        <v>44.6</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.72</v>
+        <v>5.54</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.42</v>
+        <v>3.53</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.36</v>
+        <v>19.86</v>
       </c>
       <c r="EB3" t="n">
         <v>1.09</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>122.88</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="H4" t="n">
-        <v>122.14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="M4" t="n">
-        <v>69.86</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.14</v>
-      </c>
       <c r="U4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>60</v>
+        <v>59.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.43</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.57</v>
+        <v>8.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.86</v>
+        <v>6.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.14</v>
+        <v>19.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>2.29</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO4" t="n">
         <v>1.07</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.37</v>
+        <v>6.27</v>
       </c>
       <c r="CC4" t="n">
         <v>1.66</v>
@@ -2434,7 +2434,7 @@
         <v>2.48</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="CH4" t="n">
         <v>1.54</v>
@@ -2443,61 +2443,61 @@
         <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="CO4" t="n">
         <v>1.21</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC4" t="n">
         <v>1.75</v>
@@ -2506,79 +2506,79 @@
         <v>2.88</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>116.36</v>
+        <v>117.14</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.08</v>
+        <v>60.07</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.57</v>
+        <v>12.47</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.14</v>
+        <v>14.53</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.29</v>
+        <v>6</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>58.93</v>
+        <v>58.67</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.86</v>
+        <v>15.4</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.93</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DZ4" t="n">
         <v>5.93</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.22</v>
+        <v>19.14</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="5">
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.38</v>
+        <v>42.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.12</v>
@@ -2822,13 +2822,13 @@
         <v>3.84</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="CC5" t="n">
         <v>5.32</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.73</v>
+        <v>5.77</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
@@ -2870,19 +2870,19 @@
         <v>3.52</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW5" t="n">
         <v>1.97</v>
@@ -2903,10 +2903,10 @@
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="DE5" t="n">
         <v>0.13</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.93</v>
+        <v>44</v>
       </c>
       <c r="DW5" t="n">
         <v>0.33</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="H6" t="n">
-        <v>88.83</v>
+        <v>86.86</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>40.83</v>
+        <v>40</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.67</v>
+        <v>12.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.5</v>
+        <v>12.86</v>
       </c>
       <c r="R6" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>44</v>
+        <v>44.29</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB6" t="n">
         <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.5</v>
+        <v>19.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>3.38</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.71</v>
+        <v>4.93</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.1</v>
+        <v>4.66</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.87</v>
+        <v>5.36</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="CC6" t="n">
         <v>5.94</v>
@@ -3234,28 +3234,28 @@
         <v>5.91</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
         <v>1.76</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CM6" t="n">
         <v>2.17</v>
@@ -3264,28 +3264,28 @@
         <v>1.7</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.61</v>
+        <v>3.65</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW6" t="n">
         <v>2.01</v>
@@ -3294,97 +3294,97 @@
         <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="DH6" t="n">
-        <v>87</v>
+        <v>86.2</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.07</v>
+        <v>37.87</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.72</v>
+        <v>14.4</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.07</v>
+        <v>12.27</v>
       </c>
       <c r="DR6" t="n">
         <v>7.93</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.07</v>
+        <v>44.2</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.29</v>
+        <v>12.2</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.359999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.21</v>
+        <v>18.33</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,52 +3484,52 @@
         <v>2.71</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>69.43000000000001</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>25.86</v>
+        <v>27.12</v>
       </c>
       <c r="AO7" t="n">
         <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.43</v>
+        <v>14.62</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.43</v>
+        <v>14.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42</v>
+        <v>43.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.710000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>15.71</v>
+        <v>16.12</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="BG7" t="n">
         <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BI7" t="n">
         <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.14</v>
+        <v>4.4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY7" t="n">
         <v>3.69</v>
@@ -3625,82 +3625,82 @@
         <v>3.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.67</v>
+        <v>6.3</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.55</v>
+        <v>7.04</v>
       </c>
       <c r="CE7" t="n">
         <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI7" t="n">
         <v>1.71</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK7" t="n">
         <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CM7" t="n">
         <v>2.21</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO7" t="n">
         <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="CR7" t="n">
         <v>1.51</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW7" t="n">
         <v>2.18</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY7" t="n">
         <v>2.05</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA7" t="n">
         <v>1.78</v>
@@ -3709,52 +3709,52 @@
         <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>78.22</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.28</v>
+        <v>30.66</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.86</v>
+        <v>14.93</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.64</v>
+        <v>15.27</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0.07000000000000001</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.28</v>
+        <v>45.87</v>
       </c>
       <c r="DW7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.58</v>
+        <v>5.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.71</v>
+        <v>17.8</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4290,52 +4290,52 @@
         <v>2.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.33</v>
+        <v>74.14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN9" t="n">
         <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.5</v>
+        <v>14.43</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>11.14</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.83</v>
+        <v>45.29</v>
       </c>
       <c r="AZ9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BK9" t="n">
         <v>0.67</v>
       </c>
-      <c r="BA9" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BJ9" t="n">
+      <c r="BL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM9" t="n">
         <v>0.93</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1</v>
-      </c>
       <c r="BN9" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BR9" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY9" t="n">
         <v>3.64</v>
@@ -4431,121 +4431,121 @@
         <v>4.39</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.36</v>
+        <v>4.29</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.84</v>
+        <v>6.57</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.36</v>
+        <v>7.05</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CW9" t="n">
         <v>1.95</v>
       </c>
-      <c r="CQ9" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CS9" t="n">
+      <c r="CX9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DJ9" t="n">
         <v>3</v>
       </c>
-      <c r="CT9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>79.06999999999999</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>3.07</v>
-      </c>
       <c r="DK9" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>31.22</v>
+        <v>30.94</v>
       </c>
       <c r="DN9" t="n">
         <v>1</v>
@@ -4554,13 +4554,13 @@
         <v>1.93</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.5</v>
+        <v>14.47</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.29</v>
+        <v>12.47</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.64</v>
+        <v>48.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.79</v>
+        <v>6.73</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.64</v>
+        <v>20.87</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.67</v>
+        <v>3.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.33</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="n">
-        <v>7.33</v>
+        <v>6.57</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.33</v>
+        <v>18.71</v>
       </c>
       <c r="AR10" t="n">
-        <v>17.5</v>
+        <v>16.57</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,73 +4750,73 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>52.5</v>
+        <v>51.43</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>10</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>23.43</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.71</v>
+        <v>10.47</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BR10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
         <v>3.13</v>
@@ -4834,70 +4834,70 @@
         <v>3.16</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.16</v>
+        <v>2.86</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="CE10" t="n">
         <v>1.32</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CI10" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK10" t="n">
         <v>1.38</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CO10" t="n">
         <v>1.25</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW10" t="n">
         <v>1.94</v>
@@ -4906,64 +4906,64 @@
         <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.37</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.97</v>
+        <v>3.89</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.64</v>
+        <v>85.86</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.57</v>
+        <v>5.33</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DM10" t="n">
-        <v>47.79</v>
+        <v>46.4</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DP10" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.79</v>
+        <v>16.4</v>
       </c>
       <c r="DR10" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50</v>
+        <v>49.66</v>
       </c>
       <c r="DW10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.64</v>
+        <v>13</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.78</v>
+        <v>21.13</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.43</v>
+        <v>48.29</v>
       </c>
       <c r="Y12" t="n">
         <v>0.14</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.13</v>
+        <v>49.07</v>
       </c>
       <c r="DW12" t="n">
         <v>0.2</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6305,130 +6305,130 @@
         <v>2.29</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>99.56999999999999</v>
+        <v>100.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.86</v>
+        <v>5.25</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>47.29</v>
+        <v>49.38</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.86</v>
+        <v>13.62</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.57</v>
+        <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.57</v>
+        <v>6.25</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.29</v>
+        <v>56.75</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.71</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BC14" t="n">
         <v>6</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.14</v>
+        <v>18.38</v>
       </c>
       <c r="BE14" t="n">
         <v>1.76</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.140000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BY14" t="n">
         <v>1.38</v>
@@ -6446,25 +6446,25 @@
         <v>1.39</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.46</v>
+        <v>5.42</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="CE14" t="n">
         <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CH14" t="n">
         <v>1.48</v>
@@ -6476,22 +6476,22 @@
         <v>2.08</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CO14" t="n">
         <v>1.23</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.88</v>
@@ -6500,115 +6500,115 @@
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB14" t="n">
         <v>1.26</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.64</v>
+        <v>102.8</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>48.64</v>
+        <v>49.67</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.72</v>
+        <v>11.47</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>55.29</v>
+        <v>55.6</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.86</v>
+        <v>14.8</v>
       </c>
       <c r="DY14" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="DZ14" t="n">
         <v>5.86</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.22</v>
+        <v>19.27</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.88</v>
+        <v>45</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.12</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.73</v>
+        <v>45.8</v>
       </c>
       <c r="DW15" t="n">
         <v>0.26</v>
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>99</v>
+        <v>98.62</v>
       </c>
       <c r="I16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J16" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="K16" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M16" t="n">
-        <v>45.43</v>
+        <v>43.62</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O16" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
         <v>15</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.86</v>
+        <v>15.62</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="S16" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50</v>
+        <v>50.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.29</v>
+        <v>11.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.43</v>
+        <v>7.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>23.71</v>
+        <v>23.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AF16" t="n">
         <v>0.14</v>
@@ -7192,46 +7192,46 @@
         <v>2.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.359999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BS16" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="CA16" t="n">
         <v>3.41</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CC16" t="n">
         <v>4.81</v>
@@ -7267,10 +7267,10 @@
         <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CH16" t="n">
         <v>1.28</v>
@@ -7279,13 +7279,13 @@
         <v>1.61</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CK16" t="n">
         <v>1.73</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CM16" t="n">
         <v>2.04</v>
@@ -7300,25 +7300,25 @@
         <v>2.5</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CT16" t="n">
         <v>2.51</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV16" t="n">
         <v>1.62</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CX16" t="n">
         <v>1.79</v>
@@ -7336,85 +7336,85 @@
         <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.27</v>
+        <v>5.24</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DO16" t="n">
         <v>2.14</v>
       </c>
-      <c r="DG16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>90.22</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>2.29</v>
-      </c>
       <c r="DP16" t="n">
-        <v>14.07</v>
+        <v>14.13</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.72</v>
+        <v>14.66</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.71</v>
+        <v>7.53</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.5</v>
+        <v>46.87</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.71</v>
+        <v>7.47</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.92</v>
+        <v>21.06</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="AI18" t="n">
-        <v>110.86</v>
+        <v>107.12</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AL18" t="n">
-        <v>8.289999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.43</v>
+        <v>55.12</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="AR18" t="n">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.14</v>
+        <v>5.75</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>65.56999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>18.14</v>
+        <v>17.88</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="BC18" t="n">
         <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.57</v>
+        <v>16.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.21</v>
+        <v>3.33</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.57</v>
+        <v>9.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.21</v>
+        <v>3.33</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BL18" t="n">
         <v>0.93</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY18" t="n">
         <v>1.31</v>
@@ -8058,25 +8058,25 @@
         <v>1.29</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.13</v>
+        <v>6.03</v>
       </c>
       <c r="CB18" t="n">
-        <v>7.07</v>
+        <v>6.91</v>
       </c>
       <c r="CC18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CD18" t="n">
         <v>1.51</v>
       </c>
-      <c r="CD18" t="n">
-        <v>1.52</v>
-      </c>
       <c r="CE18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH18" t="n">
         <v>1.48</v>
@@ -8091,40 +8091,40 @@
         <v>1.46</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CP18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CU18" t="n">
         <v>1.62</v>
       </c>
-      <c r="CQ18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>1.64</v>
-      </c>
       <c r="CV18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CX18" t="n">
         <v>1.61</v>
@@ -8142,85 +8142,85 @@
         <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="DE18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.58</v>
+        <v>3.47</v>
       </c>
       <c r="DH18" t="n">
-        <v>115.5</v>
+        <v>113.2</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="DK18" t="n">
-        <v>7.08</v>
+        <v>6.94</v>
       </c>
       <c r="DL18" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DM18" t="n">
-        <v>58.72</v>
+        <v>56.93</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.36</v>
+        <v>12.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.28</v>
+        <v>13.8</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.35</v>
+        <v>4.73</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.64</v>
+        <v>62.2</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX18" t="n">
-        <v>19.57</v>
+        <v>19.34</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.92</v>
+        <v>11.73</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.64</v>
+        <v>7.6</v>
       </c>
       <c r="EA18" t="n">
-        <v>18</v>
+        <v>17.27</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -8242,79 +8242,79 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="G19" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>89.43000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="L19" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M19" t="n">
-        <v>39.29</v>
+        <v>40.38</v>
       </c>
       <c r="N19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="P19" t="n">
-        <v>14.57</v>
+        <v>15.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.29</v>
+        <v>14.25</v>
       </c>
       <c r="R19" t="n">
-        <v>7.14</v>
+        <v>7.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>47.29</v>
+        <v>46.88</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>12.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.29</v>
+        <v>20.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -8401,70 +8401,70 @@
         <v>1.71</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU19" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV19" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.89</v>
+        <v>3.42</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.46</v>
+        <v>3.94</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="CC19" t="n">
         <v>3.33</v>
@@ -8473,13 +8473,13 @@
         <v>3.65</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
@@ -8491,10 +8491,10 @@
         <v>1.96</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM19" t="n">
         <v>2.36</v>
@@ -8503,22 +8503,22 @@
         <v>1.84</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CU19" t="n">
         <v>1.4</v>
@@ -8527,7 +8527,7 @@
         <v>1.86</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX19" t="n">
         <v>1.57</v>
@@ -8539,91 +8539,91 @@
         <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.14</v>
+        <v>93.2</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.14</v>
+        <v>42.54</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DP19" t="n">
-        <v>14</v>
+        <v>14.47</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.86</v>
+        <v>14.8</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.14</v>
+        <v>7.2</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.08</v>
+        <v>48.74</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.72</v>
+        <v>13</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.140000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.43</v>
+        <v>22</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>78.70999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.57</v>
+        <v>3.12</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.29</v>
+        <v>-0.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.71</v>
+        <v>30.38</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.43</v>
+        <v>13.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.86</v>
+        <v>13.62</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.140000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42</v>
+        <v>41.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.29</v>
+        <v>7.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.14</v>
+        <v>19.5</v>
       </c>
       <c r="BE3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK3" t="n">
         <v>0.88</v>
       </c>
-      <c r="BF3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.93</v>
-      </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY3" t="n">
         <v>4.97</v>
@@ -2013,22 +2013,22 @@
         <v>5.01</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.58</v>
+        <v>5.28</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.8</v>
+        <v>6.38</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG3" t="n">
         <v>2.73</v>
@@ -2037,145 +2037,145 @@
         <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
         <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="CR3" t="n">
         <v>1.49</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="DG3" t="n">
         <v>1</v>
       </c>
       <c r="DH3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.94</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.07</v>
+        <v>3.31</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.93</v>
+        <v>36.82</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.93</v>
+        <v>12.81</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.33</v>
+        <v>14.18</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.86</v>
+        <v>7.68</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.6</v>
+        <v>44.06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.07</v>
+        <v>9.18</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.54</v>
+        <v>5.44</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.53</v>
+        <v>3.75</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.86</v>
+        <v>19.56</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="4">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>63.14</v>
+        <v>62.88</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>25.71</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>15.12</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>42.43</v>
+        <v>42</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>4.62</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.29</v>
+        <v>17.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.07</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.53</v>
+        <v>3.69</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>3.84</v>
@@ -4034,16 +4034,16 @@
         <v>4.24</v>
       </c>
       <c r="CC8" t="n">
-        <v>7.58</v>
+        <v>7.38</v>
       </c>
       <c r="CD8" t="n">
-        <v>8.630000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="CE8" t="n">
         <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CG8" t="n">
         <v>2.8</v>
@@ -4052,40 +4052,40 @@
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK8" t="n">
         <v>1.57</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO8" t="n">
         <v>1.36</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS8" t="n">
         <v>3.07</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CU8" t="n">
         <v>1.43</v>
@@ -4094,103 +4094,103 @@
         <v>1.79</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB8" t="n">
         <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="DE8" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="DH8" t="n">
-        <v>73.26000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DM8" t="n">
-        <v>31.13</v>
+        <v>30.94</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.2</v>
+        <v>14.31</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.13</v>
+        <v>16.25</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.46</v>
+        <v>48.81</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>11.62</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.26</v>
+        <v>7.87</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.27</v>
+        <v>18.94</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="9">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>85.12</v>
+        <v>89.78</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="K10" t="n">
-        <v>4.25</v>
+        <v>4.78</v>
       </c>
       <c r="L10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>42.38</v>
+        <v>44.44</v>
       </c>
       <c r="N10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P10" t="n">
-        <v>17.75</v>
+        <v>17.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.25</v>
+        <v>16.22</v>
       </c>
       <c r="R10" t="n">
-        <v>7.88</v>
+        <v>7.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="T10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>48.12</v>
+        <v>49.56</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.12</v>
+        <v>19.11</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.86</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.47</v>
+        <v>10.62</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
         <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.93</v>
+        <v>5.06</v>
       </c>
       <c r="BR10" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="CC10" t="n">
         <v>2.86</v>
@@ -4849,91 +4849,91 @@
         <v>1.32</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.92</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL10" t="n">
         <v>1.77</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO10" t="n">
         <v>1.25</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CX10" t="n">
         <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.37</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.86</v>
+        <v>88.44</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
@@ -4942,28 +4942,28 @@
         <v>3.06</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.33</v>
+        <v>5.56</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.4</v>
+        <v>47.31</v>
       </c>
       <c r="DN10" t="n">
         <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DP10" t="n">
-        <v>18.2</v>
+        <v>18.19</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.4</v>
+        <v>16.37</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.94</v>
+        <v>7.68</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,25 +4975,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.66</v>
+        <v>50.38</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>13</v>
+        <v>13.56</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.4</v>
+        <v>8.94</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.13</v>
+        <v>21</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="EC10" t="n">
         <v>3</v>
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H11" t="n">
-        <v>100.5</v>
+        <v>102.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="K11" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>42.12</v>
+        <v>44.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P11" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="R11" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="U11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.38</v>
+        <v>51</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.75</v>
+        <v>7.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.5</v>
+        <v>20.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,70 +5177,70 @@
         <v>2.29</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.27</v>
+        <v>9.31</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.47</v>
+        <v>4.69</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.63</v>
+        <v>3.48</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.69</v>
+        <v>3.52</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC11" t="n">
         <v>5.37</v>
@@ -5255,28 +5255,28 @@
         <v>2.82</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO11" t="n">
         <v>1.31</v>
@@ -5285,7 +5285,7 @@
         <v>2</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5294,16 +5294,16 @@
         <v>2.92</v>
       </c>
       <c r="CT11" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CU11" t="n">
         <v>1.45</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
@@ -5324,82 +5324,82 @@
         <v>2.03</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="DH11" t="n">
-        <v>97.67</v>
+        <v>98.75</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.33</v>
+        <v>45.31</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.34</v>
+        <v>13.25</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.53</v>
+        <v>12.43</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.6</v>
+        <v>50.5</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.87</v>
+        <v>12.63</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.529999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.12</v>
@@ -1472,49 +1472,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>82.86</v>
+        <v>82.62</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>33.12</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.12</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.86</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.57</v>
+        <v>11.12</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>41.86</v>
+        <v>40.38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.14</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.07</v>
+        <v>8.94</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT2" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BU2" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>4.76</v>
@@ -1610,34 +1610,34 @@
         <v>4.83</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.17</v>
+        <v>4.53</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.75</v>
+        <v>5.12</v>
       </c>
       <c r="CC2" t="n">
-        <v>8.789999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="CD2" t="n">
-        <v>10.42</v>
+        <v>12.07</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CK2" t="n">
         <v>1.54</v>
@@ -1646,100 +1646,100 @@
         <v>2.07</v>
       </c>
       <c r="CM2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CP2" t="n">
         <v>2.03</v>
       </c>
-      <c r="CN2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>2.08</v>
-      </c>
       <c r="CQ2" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="CR2" t="n">
         <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="CT2" t="n">
         <v>2.82</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CY2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DC2" t="n">
         <v>2.04</v>
       </c>
-      <c r="CZ2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>2.09</v>
-      </c>
       <c r="DD2" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.06999999999999</v>
+        <v>82.94</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.53</v>
+        <v>3.32</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.67</v>
+        <v>34.18</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.86</v>
+        <v>14.37</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.140000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>43.07</v>
+        <v>42.25</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.47</v>
+        <v>10.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.4</v>
+        <v>7.32</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.4</v>
+        <v>21.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.12</v>
@@ -2275,139 +2275,139 @@
         <v>1.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>110.57</v>
+        <v>109.75</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>52.29</v>
+        <v>50.62</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.14</v>
+        <v>12.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.86</v>
+        <v>13.88</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.86</v>
+        <v>7.12</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>57.86</v>
+        <v>57</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>15.29</v>
+        <v>15.12</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.29</v>
+        <v>18.38</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.6</v>
+        <v>8.44</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM4" t="n">
         <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.41</v>
@@ -2416,55 +2416,55 @@
         <v>1.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.27</v>
+        <v>6.09</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="CE4" t="n">
         <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2479,10 +2479,10 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
@@ -2497,88 +2497,88 @@
         <v>1.98</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="DH4" t="n">
-        <v>117.14</v>
+        <v>116.32</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>60.07</v>
+        <v>58.75</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.47</v>
+        <v>12.25</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>58.67</v>
+        <v>58.19</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.4</v>
+        <v>15.31</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.93</v>
+        <v>5.94</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.14</v>
+        <v>19.13</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="5">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>87</v>
+        <v>83.12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K7" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>34.71</v>
+        <v>34.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>15.29</v>
+        <v>16.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.86</v>
+        <v>15.25</v>
       </c>
       <c r="R7" t="n">
-        <v>6.71</v>
+        <v>6.88</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48.57</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.86</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.71</v>
+        <v>19.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AF7" t="n">
         <v>0.12</v>
@@ -3565,70 +3565,70 @@
         <v>3.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.4</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.13</v>
+        <v>3.94</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="BZ7" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="CB7" t="n">
         <v>3.94</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>4</v>
       </c>
       <c r="CC7" t="n">
         <v>6.3</v>
@@ -3637,16 +3637,16 @@
         <v>7.04</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI7" t="n">
         <v>1.71</v>
@@ -3670,19 +3670,19 @@
         <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS7" t="n">
         <v>3.02</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3706,13 +3706,13 @@
         <v>1.78</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="DE7" t="n">
         <v>0.06</v>
@@ -3724,70 +3724,70 @@
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>77.40000000000001</v>
+        <v>76.06</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.66</v>
+        <v>30.94</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.93</v>
+        <v>15.43</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.27</v>
+        <v>15</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.460000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.87</v>
+        <v>45.75</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.8</v>
+        <v>17.81</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="8">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="G9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
-        <v>85.62</v>
+        <v>86.22</v>
       </c>
       <c r="I9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="K9" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="L9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M9" t="n">
-        <v>34.38</v>
+        <v>33.44</v>
       </c>
       <c r="N9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="P9" t="n">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.25</v>
+        <v>12.33</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.5</v>
+        <v>50.89</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.25</v>
+        <v>6.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.38</v>
+        <v>18.78</v>
       </c>
       <c r="AD9" t="n">
         <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AF9" t="n">
         <v>0.14</v>
@@ -4371,70 +4371,70 @@
         <v>1.86</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.130000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.27</v>
+        <v>4.38</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS9" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV9" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CC9" t="n">
         <v>6.57</v>
@@ -4446,19 +4446,19 @@
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK9" t="n">
         <v>1.56</v>
@@ -4467,19 +4467,19 @@
         <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN9" t="n">
         <v>1.79</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="CR9" t="n">
         <v>1.46</v>
@@ -4494,73 +4494,73 @@
         <v>1.43</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB9" t="n">
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.26000000000001</v>
+        <v>80.94</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>30.94</v>
+        <v>30.62</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.47</v>
+        <v>14.37</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.47</v>
+        <v>12</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.6</v>
+        <v>48.44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.73</v>
+        <v>6.56</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.87</v>
+        <v>20.44</v>
       </c>
       <c r="EB9" t="n">
         <v>1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.14</v>
@@ -5499,130 +5499,130 @@
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>86.38</v>
+        <v>86.22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.5</v>
+        <v>40.56</v>
       </c>
       <c r="AO12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK12" t="n">
         <v>0.75</v>
       </c>
-      <c r="AP12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.73</v>
-      </c>
       <c r="BL12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="BR12" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BY12" t="n">
         <v>2.79</v>
@@ -5640,16 +5640,16 @@
         <v>2.84</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.79</v>
+        <v>3.58</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.21</v>
+        <v>3.96</v>
       </c>
       <c r="CE12" t="n">
         <v>1.46</v>
@@ -5667,7 +5667,7 @@
         <v>1.7</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK12" t="n">
         <v>1.65</v>
@@ -5679,7 +5679,7 @@
         <v>2.14</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CO12" t="n">
         <v>1.41</v>
@@ -5688,7 +5688,7 @@
         <v>2.3</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="CR12" t="n">
         <v>1.52</v>
@@ -5715,7 +5715,7 @@
         <v>2.13</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA12" t="n">
         <v>1.71</v>
@@ -5727,82 +5727,82 @@
         <v>2.34</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.27</v>
+        <v>89</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.8</v>
+        <v>5.94</v>
       </c>
       <c r="DL12" t="n">
         <v>1</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.73</v>
+        <v>45.94</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="DP12" t="n">
-        <v>15.07</v>
+        <v>14.44</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.87</v>
+        <v>14.75</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.07</v>
+        <v>49.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.67</v>
+        <v>13.88</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.6</v>
+        <v>9.75</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>105.71</v>
+        <v>110.38</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K14" t="n">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>13.14</v>
+        <v>12.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.86</v>
+        <v>10.25</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="S14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>54.29</v>
+        <v>56.25</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.29</v>
+        <v>20.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6386,49 +6386,49 @@
         <v>2.12</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.93</v>
+        <v>7.88</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.22</v>
+        <v>5.52</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.42</v>
+        <v>5.75</v>
       </c>
       <c r="CC14" t="n">
         <v>1.61</v>
@@ -6458,28 +6458,28 @@
         <v>1.72</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CM14" t="n">
         <v>2.28</v>
@@ -6491,124 +6491,124 @@
         <v>1.23</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="CT14" t="n">
         <v>3.17</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA14" t="n">
         <v>1.83</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.8</v>
+        <v>105.32</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.67</v>
+        <v>50.94</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.4</v>
+        <v>13.06</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.47</v>
+        <v>11.12</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>55.6</v>
+        <v>56.5</v>
       </c>
       <c r="DW14" t="n">
         <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.94</v>
+        <v>9.25</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.27</v>
+        <v>19.56</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AI15" t="n">
-        <v>65.62</v>
+        <v>63.89</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN15" t="n">
-        <v>30.12</v>
+        <v>29.33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.25</v>
+        <v>15.11</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45</v>
+        <v>44.56</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BB15" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BP15" t="n">
         <v>5.75</v>
       </c>
-      <c r="BC15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>5.87</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY15" t="n">
         <v>3.58</v>
@@ -6849,55 +6849,55 @@
         <v>3.84</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.73</v>
+        <v>4.01</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.53</v>
+        <v>6.58</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.88</v>
+        <v>8.56</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CI15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CN15" t="n">
         <v>1.87</v>
       </c>
-      <c r="CJ15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>1.86</v>
-      </c>
       <c r="CO15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.39</v>
+        <v>3.31</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
@@ -6912,106 +6912,106 @@
         <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA15" t="n">
         <v>1.89</v>
       </c>
-      <c r="CX15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>1.86</v>
-      </c>
       <c r="DB15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.57</v>
+        <v>3.48</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DH15" t="n">
-        <v>68.13</v>
+        <v>67</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM15" t="n">
-        <v>26.13</v>
+        <v>25.94</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DP15" t="n">
-        <v>14.67</v>
+        <v>14.13</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.13</v>
+        <v>15</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.470000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.93</v>
+        <v>3.69</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.93</v>
+        <v>15.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="16">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F17" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>116.14</v>
+        <v>114</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M17" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.43</v>
       </c>
-      <c r="K17" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="M17" t="n">
-        <v>56.29</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P17" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="R17" t="n">
-        <v>5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,49 +7595,49 @@
         <v>2.38</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.529999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="CC17" t="n">
         <v>2.89</v>
@@ -7670,40 +7670,40 @@
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7736,88 +7736,88 @@
         <v>1.85</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="DH17" t="n">
-        <v>110.67</v>
+        <v>109.94</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.73</v>
+        <v>5.44</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.4</v>
+        <v>55</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.94</v>
+        <v>11.13</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.53</v>
+        <v>12.25</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.33</v>
+        <v>5.56</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>65.59999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.53</v>
+        <v>13.38</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.2</v>
+        <v>5.06</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.87</v>
+        <v>21.75</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="G18" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="H18" t="n">
-        <v>120.14</v>
+        <v>124.5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K18" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M18" t="n">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.57</v>
+        <v>10.88</v>
       </c>
       <c r="R18" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="T18" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="U18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>59.71</v>
+        <v>59.62</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>21.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.71</v>
+        <v>12.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.289999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.43</v>
+        <v>17.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.88</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BP18" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW18" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.03</v>
+        <v>6.17</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.91</v>
+        <v>7.26</v>
       </c>
       <c r="CC18" t="n">
         <v>1.5</v>
@@ -8073,40 +8073,40 @@
         <v>1.2</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CK18" t="n">
         <v>1.46</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CO18" t="n">
         <v>1.1</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
@@ -8121,106 +8121,106 @@
         <v>1.62</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DB18" t="n">
         <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="DH18" t="n">
-        <v>113.2</v>
+        <v>115.81</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.94</v>
+        <v>7</v>
       </c>
       <c r="DL18" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DM18" t="n">
-        <v>56.93</v>
+        <v>57.81</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.46</v>
+        <v>12.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.8</v>
+        <v>13.32</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="DW18" t="n">
         <v>0.06</v>
       </c>
       <c r="DX18" t="n">
-        <v>19.34</v>
+        <v>19.56</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.73</v>
+        <v>11.69</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.6</v>
+        <v>7.88</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.27</v>
+        <v>17</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>98.86</v>
+        <v>99.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>45</v>
+        <v>45.62</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.43</v>
+        <v>13.12</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.43</v>
+        <v>16.38</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.14</v>
+        <v>7.25</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>50.86</v>
+        <v>51.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.43</v>
+        <v>13.38</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.14</v>
+        <v>10.25</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.57</v>
+        <v>24</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.529999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.73</v>
+        <v>3.56</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV19" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY19" t="n">
         <v>3.42</v>
@@ -8461,73 +8461,73 @@
         <v>3.94</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL19" t="n">
         <v>2.03</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO19" t="n">
         <v>1.39</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS19" t="n">
         <v>3.09</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CU19" t="n">
         <v>1.4</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX19" t="n">
         <v>1.57</v>
@@ -8536,94 +8536,94 @@
         <v>1.96</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA19" t="n">
         <v>1.86</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.21</v>
+        <v>4.29</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.2</v>
+        <v>93.88</v>
       </c>
       <c r="DI19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.54</v>
+        <v>43</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.47</v>
+        <v>14.25</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.8</v>
+        <v>15.32</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>48.74</v>
+        <v>49.19</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX19" t="n">
         <v>13</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.33</v>
+        <v>9.43</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="EA19" t="n">
-        <v>22</v>
+        <v>22.31</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="G2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H2" t="n">
-        <v>83.25</v>
+        <v>84.33</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>35.25</v>
+        <v>35.22</v>
       </c>
       <c r="N2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>15.62</v>
+        <v>16.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.5</v>
+        <v>14.11</v>
       </c>
       <c r="R2" t="n">
-        <v>7.88</v>
+        <v>7.67</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>44.12</v>
+        <v>43.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.5</v>
+        <v>11.22</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.75</v>
+        <v>7.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.5</v>
+        <v>22.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.62</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.94</v>
+        <v>8.76</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.31</v>
+        <v>4.18</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT2" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.76</v>
+        <v>4.62</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.12</v>
+        <v>5.01</v>
       </c>
       <c r="CC2" t="n">
         <v>10.32</v>
@@ -1622,43 +1622,43 @@
         <v>12.07</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CH2" t="n">
         <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CP2" t="n">
         <v>2.05</v>
       </c>
-      <c r="CN2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>2.03</v>
-      </c>
       <c r="CQ2" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="CR2" t="n">
         <v>1.46</v>
@@ -1673,73 +1673,73 @@
         <v>1.47</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DH2" t="n">
-        <v>82.94</v>
+        <v>83.53</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.18</v>
+        <v>34.23</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO2" t="n">
         <v>1.06</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.37</v>
+        <v>14.88</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.5</v>
+        <v>12.41</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.25</v>
+        <v>42.12</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.25</v>
+        <v>10.18</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.32</v>
+        <v>7.18</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.25</v>
+        <v>21.36</v>
       </c>
       <c r="EB2" t="n">
         <v>1.1</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="3">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="H4" t="n">
-        <v>122.88</v>
+        <v>120.33</v>
       </c>
       <c r="I4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="K4" t="n">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>66.88</v>
+        <v>66.33</v>
       </c>
       <c r="N4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="P4" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.12</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="V4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>59.38</v>
+        <v>58.44</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.75</v>
+        <v>9.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.75</v>
+        <v>6.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.88</v>
+        <v>18.89</v>
       </c>
       <c r="AD4" t="n">
         <v>1.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,70 +2356,70 @@
         <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.44</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.69</v>
+        <v>4.59</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.5</v>
+        <v>5.59</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.09</v>
+        <v>6.12</v>
       </c>
       <c r="CC4" t="n">
         <v>1.72</v>
@@ -2431,28 +2431,28 @@
         <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CN4" t="n">
         <v>1.91</v>
@@ -2461,10 +2461,10 @@
         <v>1.22</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2482,13 +2482,13 @@
         <v>1.73</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.41</v>
@@ -2500,85 +2500,85 @@
         <v>1.25</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="DH4" t="n">
-        <v>116.32</v>
+        <v>115.35</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.44</v>
+        <v>5.53</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>58.75</v>
+        <v>58.94</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.25</v>
+        <v>12.23</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.5</v>
+        <v>14.47</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>58.19</v>
+        <v>57.76</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.31</v>
+        <v>15.59</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.94</v>
+        <v>5.76</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.13</v>
+        <v>18.65</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,49 +2678,49 @@
         <v>2.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" t="n">
-        <v>95.75</v>
+        <v>94.56</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.88</v>
+        <v>37.56</v>
       </c>
       <c r="AO5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AT5" t="n">
         <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.88</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.5</v>
+        <v>42.56</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BD5" t="n">
-        <v>22.25</v>
+        <v>20.89</v>
       </c>
       <c r="BE5" t="n">
         <v>1.37</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.6</v>
+        <v>10.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.93</v>
+        <v>4.69</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.67</v>
+        <v>5.56</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY5" t="n">
         <v>4.12</v>
@@ -2819,25 +2819,25 @@
         <v>4.83</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.32</v>
+        <v>5.17</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.77</v>
+        <v>5.62</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CH5" t="n">
         <v>1.39</v>
@@ -2852,25 +2852,25 @@
         <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
         <v>1.33</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.52</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS5" t="n">
         <v>3.01</v>
@@ -2888,100 +2888,100 @@
         <v>1.97</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DB5" t="n">
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.47</v>
+        <v>89.19</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
         <v>3.06</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.4</v>
+        <v>37.69</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.53</v>
+        <v>14.75</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.93</v>
+        <v>12.44</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44</v>
+        <v>43.94</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.6</v>
+        <v>11.75</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.74</v>
+        <v>7.88</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.93</v>
+        <v>20.25</v>
       </c>
       <c r="EB5" t="n">
         <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="H6" t="n">
-        <v>86.86</v>
+        <v>85.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>37.88</v>
       </c>
       <c r="N6" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.29</v>
+        <v>12.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.86</v>
+        <v>12.12</v>
       </c>
       <c r="R6" t="n">
-        <v>8.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>44.29</v>
+        <v>42.38</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.14</v>
+        <v>12.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.140000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.57</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>3.38</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.66</v>
+        <v>4.37</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.36</v>
+        <v>4.97</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CC6" t="n">
         <v>5.94</v>
@@ -3237,7 +3237,7 @@
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG6" t="n">
         <v>2.8</v>
@@ -3246,37 +3246,37 @@
         <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO6" t="n">
         <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CT6" t="n">
         <v>2.82</v>
@@ -3291,100 +3291,100 @@
         <v>2.01</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.2</v>
+        <v>85.56</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.87</v>
+        <v>36.94</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.4</v>
+        <v>14.25</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.27</v>
+        <v>11.93</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.93</v>
+        <v>8.43</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.2</v>
+        <v>43.25</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.2</v>
+        <v>11.75</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.27</v>
+        <v>7.88</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.33</v>
+        <v>18.62</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="7">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>82.12</v>
+        <v>83.11</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>35.88</v>
+        <v>33.44</v>
       </c>
       <c r="N8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>13.5</v>
+        <v>13.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>16.89</v>
       </c>
       <c r="R8" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="S8" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="U8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.62</v>
+        <v>54.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.25</v>
+        <v>14.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.12</v>
+        <v>10.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.12</v>
+        <v>20.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,67 +3968,67 @@
         <v>2.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
         <v>1.06</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.56</v>
+        <v>4.71</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU8" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.84</v>
+        <v>4.02</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.09</v>
+        <v>4.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="CB8" t="n">
         <v>4.24</v>
@@ -4040,7 +4040,7 @@
         <v>8.5</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF8" t="n">
         <v>2.97</v>
@@ -4052,40 +4052,40 @@
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CU8" t="n">
         <v>1.43</v>
@@ -4094,13 +4094,13 @@
         <v>1.79</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CX8" t="n">
         <v>1.66</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.21</v>
@@ -4109,55 +4109,55 @@
         <v>1.8</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD8" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="DH8" t="n">
-        <v>72.5</v>
+        <v>73.59</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DM8" t="n">
-        <v>30.94</v>
+        <v>29.94</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.31</v>
+        <v>14.29</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.25</v>
+        <v>15.77</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS8" t="n">
         <v>0.18</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.81</v>
+        <v>48.41</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.62</v>
+        <v>11.59</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.87</v>
+        <v>7.82</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.94</v>
+        <v>19.24</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.22</v>
@@ -4290,49 +4290,49 @@
         <v>3.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AI9" t="n">
-        <v>74.14</v>
+        <v>81</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.57</v>
+        <v>3.38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>31.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.43</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.29</v>
+        <v>48.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.289999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.14</v>
+        <v>6.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.57</v>
+        <v>22.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.31</v>
+        <v>9.41</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS9" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW9" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY9" t="n">
         <v>3.72</v>
@@ -4431,25 +4431,25 @@
         <v>4.41</v>
       </c>
       <c r="CA9" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.57</v>
+        <v>6.11</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.05</v>
+        <v>6.58</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4461,31 +4461,31 @@
         <v>1.94</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CO9" t="n">
         <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="CR9" t="n">
         <v>1.46</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT9" t="n">
         <v>2.84</v>
@@ -4500,67 +4500,67 @@
         <v>1.97</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CY9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.94</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.69</v>
+        <v>4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM9" t="n">
-        <v>30.62</v>
+        <v>32.35</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.37</v>
+        <v>13.94</v>
       </c>
       <c r="DQ9" t="n">
         <v>12</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.06</v>
+        <v>8.59</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.44</v>
+        <v>49.77</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.44</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.56</v>
+        <v>6.59</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.44</v>
+        <v>20.41</v>
       </c>
       <c r="EB9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="10">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5099,136 +5099,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.43000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.86</v>
+        <v>45.38</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.71</v>
+        <v>12.62</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.14</v>
+        <v>7.25</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.86</v>
+        <v>49.75</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.43</v>
+        <v>12.88</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC11" t="n">
         <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.86</v>
+        <v>21.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.31</v>
+        <v>9.35</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL11" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.69</v>
+        <v>4.82</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY11" t="n">
         <v>3.48</v>
@@ -5237,55 +5237,55 @@
         <v>3.52</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.79</v>
+        <v>3.98</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.91</v>
+        <v>4.07</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.37</v>
+        <v>6.38</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.4</v>
+        <v>6.16</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.88</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="CR11" t="n">
         <v>1.42</v>
@@ -5300,106 +5300,106 @@
         <v>1.45</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.26</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DH11" t="n">
-        <v>98.75</v>
+        <v>97.94</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.63</v>
+        <v>4.53</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.31</v>
+        <v>44.71</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.25</v>
+        <v>13.35</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.43</v>
+        <v>12.41</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.31</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.5</v>
+        <v>50.41</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.63</v>
+        <v>12.41</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.31</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.5</v>
+        <v>20.82</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F12" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>92.56999999999999</v>
+        <v>89.75</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="K12" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>52.86</v>
+        <v>51.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>14.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.29</v>
+        <v>15.12</v>
       </c>
       <c r="R12" t="n">
-        <v>6.43</v>
+        <v>7.12</v>
       </c>
       <c r="S12" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="T12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.29</v>
+        <v>46.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.86</v>
+        <v>15.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.71</v>
+        <v>4.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.14</v>
+        <v>21.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AF12" t="n">
         <v>0.22</v>
@@ -5583,46 +5583,46 @@
         <v>2</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI12" t="n">
         <v>2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.69</v>
+        <v>4.53</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.69</v>
+        <v>5.18</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT12" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.79</v>
+        <v>3.32</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.84</v>
+        <v>3.38</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="CC12" t="n">
         <v>3.58</v>
@@ -5655,10 +5655,10 @@
         <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH12" t="n">
         <v>1.31</v>
@@ -5673,34 +5673,34 @@
         <v>1.65</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CN12" t="n">
         <v>1.7</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV12" t="n">
         <v>1.74</v>
@@ -5712,7 +5712,7 @@
         <v>1.7</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.14</v>
@@ -5721,88 +5721,88 @@
         <v>1.71</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.57</v>
+        <v>2.83</v>
       </c>
       <c r="DH12" t="n">
-        <v>89</v>
+        <v>87.88</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
       <c r="DL12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.94</v>
+        <v>45.83</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.44</v>
+        <v>14.59</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.75</v>
+        <v>14.7</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.31</v>
+        <v>6.64</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.38</v>
+        <v>48.59</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.88</v>
+        <v>14.18</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.75</v>
+        <v>9.77</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.12</v>
+        <v>4.41</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.5</v>
+        <v>22.12</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,139 +5902,139 @@
         <v>3</v>
       </c>
       <c r="AF13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="BK13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BN13" t="n">
         <v>1.88</v>
       </c>
-      <c r="AH13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>72.62</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.93</v>
-      </c>
       <c r="BO13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>4.46</v>
@@ -6043,25 +6043,25 @@
         <v>4.73</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.21</v>
+        <v>4.89</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.46</v>
+        <v>5.09</v>
       </c>
       <c r="CE13" t="n">
         <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
@@ -6073,16 +6073,16 @@
         <v>2.02</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO13" t="n">
         <v>1.38</v>
@@ -6106,22 +6106,22 @@
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DB13" t="n">
         <v>1.39</v>
@@ -6133,46 +6133,46 @@
         <v>4.1</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DH13" t="n">
-        <v>74.59999999999999</v>
+        <v>76.19</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="DK13" t="n">
         <v>4.06</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.8</v>
+        <v>32.81</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.4</v>
+        <v>15.13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.73</v>
+        <v>15.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.539999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.4</v>
+        <v>49.12</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.27</v>
+        <v>6.31</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.47</v>
+        <v>20.56</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="14">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.25</v>
@@ -7517,91 +7517,91 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AI17" t="n">
-        <v>105.88</v>
+        <v>106.44</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.5</v>
+        <v>56.22</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.88</v>
+        <v>11.44</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.25</v>
+        <v>13.22</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.62</v>
+        <v>5.89</v>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>66.88</v>
+        <v>65.89</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.25</v>
+        <v>14.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.62</v>
+        <v>20.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.380000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
         <v>1</v>
@@ -7610,43 +7610,43 @@
         <v>0.88</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="BO17" t="n">
         <v>1.88</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT17" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY17" t="n">
         <v>1.67</v>
@@ -7655,22 +7655,22 @@
         <v>1.74</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="CB17" t="n">
         <v>4.22</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG17" t="n">
         <v>2.92</v>
@@ -7679,22 +7679,22 @@
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.94</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
@@ -7703,7 +7703,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7712,7 +7712,7 @@
         <v>2.9</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
@@ -7721,7 +7721,7 @@
         <v>1.85</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX17" t="n">
         <v>1.58</v>
@@ -7739,85 +7739,85 @@
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.94</v>
+        <v>110</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.44</v>
+        <v>5.53</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DM17" t="n">
-        <v>55</v>
+        <v>54.94</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.13</v>
+        <v>10.94</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.25</v>
+        <v>12.29</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.56</v>
+        <v>5.71</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>64.56</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.38</v>
+        <v>13.18</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.31</v>
+        <v>8.06</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.75</v>
+        <v>21.71</v>
       </c>
       <c r="EB17" t="n">
         <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0.12</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="AI18" t="n">
-        <v>107.12</v>
+        <v>106.11</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AN18" t="n">
-        <v>55.12</v>
+        <v>53.67</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.12</v>
+        <v>13.22</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.75</v>
+        <v>15.89</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>64.38</v>
+        <v>64.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA18" t="n">
-        <v>17.88</v>
+        <v>17.44</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="BC18" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.25</v>
+        <v>15.78</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.380000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL18" t="n">
         <v>1.06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BP18" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>4.94</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>4.44</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT18" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU18" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW18" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX18" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY18" t="n">
         <v>1.28</v>
@@ -8058,10 +8058,10 @@
         <v>1.27</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.17</v>
+        <v>6.05</v>
       </c>
       <c r="CB18" t="n">
-        <v>7.26</v>
+        <v>7.1</v>
       </c>
       <c r="CC18" t="n">
         <v>1.5</v>
@@ -8070,157 +8070,157 @@
         <v>1.51</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ18" t="n">
         <v>2.11</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DB18" t="n">
         <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="DH18" t="n">
-        <v>115.81</v>
+        <v>114.76</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="DK18" t="n">
         <v>7</v>
       </c>
       <c r="DL18" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.81</v>
+        <v>56.88</v>
       </c>
       <c r="DN18" t="n">
         <v>0.88</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.5</v>
+        <v>12.59</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.32</v>
+        <v>13.53</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62</v>
+        <v>62.11</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>19.56</v>
+        <v>19.23</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.69</v>
+        <v>11.59</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.88</v>
+        <v>7.65</v>
       </c>
       <c r="EA18" t="n">
-        <v>17</v>
+        <v>16.71</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -8242,82 +8242,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H19" t="n">
-        <v>88.25</v>
+        <v>88.56</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="K19" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="L19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>40.38</v>
+        <v>41.78</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O19" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="P19" t="n">
-        <v>15.38</v>
+        <v>15.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.25</v>
+        <v>14.67</v>
       </c>
       <c r="R19" t="n">
-        <v>7.25</v>
+        <v>7.56</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>46.88</v>
+        <v>48</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.62</v>
+        <v>12.22</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.619999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB19" t="n">
         <v>4</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.62</v>
+        <v>21.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>1.75</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.31</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.56</v>
+        <v>3.41</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BR19" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT19" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU19" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV19" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.94</v>
+        <v>3.72</v>
       </c>
       <c r="CA19" t="n">
         <v>3.47</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CC19" t="n">
         <v>3.23</v>
@@ -8476,31 +8476,31 @@
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.97</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
         <v>1.39</v>
@@ -8509,7 +8509,7 @@
         <v>2.2</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8533,97 +8533,97 @@
         <v>1.57</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.88</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM19" t="n">
-        <v>43</v>
+        <v>43.59</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.25</v>
+        <v>14.59</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.32</v>
+        <v>15.47</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.25</v>
+        <v>7.41</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.19</v>
+        <v>49.65</v>
       </c>
       <c r="DW19" t="n">
         <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>13</v>
+        <v>12.77</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.43</v>
+        <v>9.18</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.31</v>
+        <v>22.47</v>
       </c>
       <c r="EB19" t="n">
         <v>1.38</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1607,7 +1607,7 @@
         <v>4.62</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="CA2" t="n">
         <v>4.44</v>
@@ -1694,10 +1694,10 @@
         <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,79 +1794,79 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="H3" t="n">
-        <v>74.38</v>
+        <v>76.78</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="L3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>43.25</v>
+        <v>42.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.75</v>
+        <v>15.33</v>
       </c>
       <c r="R3" t="n">
-        <v>7.62</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="U3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.88</v>
+        <v>46.56</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.62</v>
+        <v>10.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.62</v>
+        <v>19.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1953,70 +1953,70 @@
         <v>2.88</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.94</v>
+        <v>7.88</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.97</v>
+        <v>4.81</v>
       </c>
       <c r="BZ3" t="n">
-        <v>5.01</v>
+        <v>4.89</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC3" t="n">
         <v>5.28</v>
@@ -2025,34 +2025,34 @@
         <v>6.38</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH3" t="n">
         <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK3" t="n">
         <v>1.52</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO3" t="n">
         <v>1.36</v>
@@ -2061,16 +2061,16 @@
         <v>2.12</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS3" t="n">
         <v>3.26</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2082,73 +2082,73 @@
         <v>2.07</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC3" t="n">
         <v>2.24</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DH3" t="n">
-        <v>76.94</v>
+        <v>78.06</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.82</v>
+        <v>36.71</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.81</v>
+        <v>12.88</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.18</v>
+        <v>14.53</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.68</v>
+        <v>7.94</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -2160,22 +2160,22 @@
         <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.18</v>
+        <v>9.24</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.56</v>
+        <v>19.29</v>
       </c>
       <c r="EB3" t="n">
         <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="4">
@@ -2413,13 +2413,13 @@
         <v>1.39</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CA4" t="n">
         <v>5.59</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.12</v>
+        <v>6.15</v>
       </c>
       <c r="CC4" t="n">
         <v>1.72</v>
@@ -2479,22 +2479,22 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="n">
         <v>1.25</v>
@@ -2503,7 +2503,7 @@
         <v>1.76</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="DE4" t="n">
         <v>0.11</v>
@@ -2600,7 +2600,7 @@
         <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="G5" t="n">
         <v>2.29</v>
@@ -2612,7 +2612,7 @@
         <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="K5" t="n">
         <v>4.29</v>
@@ -2675,7 +2675,7 @@
         <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2912,7 +2912,7 @@
         <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DG5" t="n">
         <v>1.94</v>
@@ -2924,7 +2924,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="DK5" t="n">
         <v>4.06</v>
@@ -2981,7 +2981,7 @@
         <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="6">
@@ -3219,7 +3219,7 @@
         <v>4.37</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="CA6" t="n">
         <v>3.93</v>
@@ -3285,7 +3285,7 @@
         <v>1.42</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW6" t="n">
         <v>2.01</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,52 +3484,52 @@
         <v>2.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>69</v>
+        <v>69.56</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>27.12</v>
+        <v>28</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.62</v>
+        <v>15.44</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.75</v>
+        <v>14.22</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>43.5</v>
+        <v>44.11</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>6.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.12</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="BM7" t="n">
         <v>0.88</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.94</v>
+        <v>4.18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX7" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY7" t="n">
         <v>3.61</v>
@@ -3625,25 +3625,25 @@
         <v>3.84</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.3</v>
+        <v>5.94</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.04</v>
+        <v>6.61</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH7" t="n">
         <v>1.34</v>
@@ -3652,109 +3652,109 @@
         <v>1.71</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="CR7" t="n">
         <v>1.52</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
         <v>1.74</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="DE7" t="n">
         <v>0.06</v>
       </c>
       <c r="DF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG7" t="n">
         <v>2.06</v>
       </c>
-      <c r="DG7" t="n">
-        <v>2</v>
-      </c>
       <c r="DH7" t="n">
-        <v>76.06</v>
+        <v>75.94</v>
       </c>
       <c r="DI7" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.37</v>
+        <v>3.23</v>
       </c>
       <c r="DK7" t="n">
         <v>3.94</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.94</v>
+        <v>31.18</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.43</v>
+        <v>15.82</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.44</v>
+        <v>8.42</v>
       </c>
       <c r="DS7" t="n">
         <v>0.06</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.75</v>
+        <v>45.94</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.31</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.5</v>
+        <v>5.76</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.81</v>
+        <v>17.65</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="8">
@@ -4025,13 +4025,13 @@
         <v>4.02</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="CA8" t="n">
         <v>4.07</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CC8" t="n">
         <v>7.38</v>
@@ -4082,13 +4082,13 @@
         <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV8" t="n">
         <v>1.79</v>
@@ -4097,25 +4097,25 @@
         <v>2.11</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY8" t="n">
         <v>2.04</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
@@ -4434,13 +4434,13 @@
         <v>3.96</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="CC9" t="n">
         <v>6.11</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.58</v>
+        <v>6.56</v>
       </c>
       <c r="CE9" t="n">
         <v>1.39</v>
@@ -4497,7 +4497,7 @@
         <v>1.9</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.70999999999999</v>
+        <v>89.12</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.57</v>
+        <v>6.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>51</v>
+        <v>52.25</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.71</v>
+        <v>19.12</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.57</v>
+        <v>16.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.43</v>
+        <v>52</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="BD10" t="n">
-        <v>23.43</v>
+        <v>23.25</v>
       </c>
       <c r="BE10" t="n">
         <v>1.48</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.62</v>
+        <v>10.41</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
         <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BT10" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY10" t="n">
         <v>2.95</v>
@@ -4834,25 +4834,25 @@
         <v>2.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CH10" t="n">
         <v>1.28</v>
@@ -4861,10 +4861,10 @@
         <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL10" t="n">
         <v>1.77</v>
@@ -4876,22 +4876,22 @@
         <v>1.81</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP10" t="n">
         <v>2.08</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4906,10 +4906,10 @@
         <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA10" t="n">
         <v>1.91</v>
@@ -4924,46 +4924,46 @@
         <v>3.87</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF10" t="n">
         <v>2.06</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="DH10" t="n">
-        <v>88.44</v>
+        <v>89.47</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="DM10" t="n">
-        <v>47.31</v>
+        <v>48.12</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DP10" t="n">
-        <v>18.19</v>
+        <v>18.41</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.37</v>
+        <v>16.23</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.68</v>
+        <v>7.65</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.38</v>
+        <v>50.71</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.56</v>
+        <v>13.59</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.94</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="EA10" t="n">
-        <v>21</v>
+        <v>21.06</v>
       </c>
       <c r="EB10" t="n">
         <v>1.52</v>
       </c>
       <c r="EC10" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="11">
@@ -5240,13 +5240,13 @@
         <v>3.98</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="CC11" t="n">
         <v>6.38</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.16</v>
+        <v>6.27</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
@@ -5300,7 +5300,7 @@
         <v>1.45</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW11" t="n">
         <v>1.9</v>
@@ -5309,10 +5309,10 @@
         <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DA11" t="n">
         <v>1.8</v>
@@ -5321,7 +5321,7 @@
         <v>1.32</v>
       </c>
       <c r="DC11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD11" t="n">
         <v>3.5</v>
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46.75</v>
+        <v>46.62</v>
       </c>
       <c r="Y12" t="n">
         <v>0.12</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.59</v>
+        <v>48.53</v>
       </c>
       <c r="DW12" t="n">
         <v>0.17</v>
@@ -6046,13 +6046,13 @@
         <v>3.69</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CC13" t="n">
         <v>4.89</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="CE13" t="n">
         <v>1.45</v>
@@ -6127,10 +6127,10 @@
         <v>1.39</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="DE13" t="n">
         <v>0.19</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.12</v>
@@ -6305,130 +6305,130 @@
         <v>2.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AI14" t="n">
-        <v>100.25</v>
+        <v>100.33</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN14" t="n">
-        <v>49.38</v>
+        <v>50.11</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.62</v>
+        <v>14.56</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>12.89</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.75</v>
+        <v>56.78</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.5</v>
+        <v>14.67</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.5</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.38</v>
+        <v>17.89</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM14" t="n">
         <v>0.88</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT14" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BY14" t="n">
         <v>1.35</v>
@@ -6446,73 +6446,73 @@
         <v>1.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.52</v>
+        <v>5.43</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CO14" t="n">
         <v>1.23</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CX14" t="n">
         <v>1.59</v>
@@ -6527,88 +6527,88 @@
         <v>1.83</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DH14" t="n">
-        <v>105.32</v>
+        <v>105.06</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.12</v>
+        <v>5.23</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.94</v>
+        <v>51.23</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.06</v>
+        <v>13.59</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.12</v>
+        <v>11.65</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.68</v>
+        <v>5.82</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.5</v>
+        <v>56.53</v>
       </c>
       <c r="DW14" t="n">
         <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>15</v>
+        <v>14.59</v>
       </c>
       <c r="DY14" t="n">
-        <v>9.25</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.56</v>
+        <v>19.24</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
@@ -6630,88 +6630,88 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.14</v>
+        <v>3.88</v>
       </c>
       <c r="L15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M15" t="n">
-        <v>21.57</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>12.86</v>
+        <v>12.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>9.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.71</v>
+        <v>47.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.140000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.86</v>
+        <v>4.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.43</v>
+        <v>15.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AH15" t="n">
         <v>1.89</v>
@@ -6735,7 +6735,7 @@
         <v>29.33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AP15" t="n">
         <v>1.78</v>
@@ -6789,70 +6789,70 @@
         <v>2.78</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.62</v>
+        <v>10.76</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
         <v>0.88</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU15" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.58</v>
+        <v>3.43</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.01</v>
+        <v>3.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="CC15" t="n">
         <v>6.58</v>
@@ -6861,157 +6861,157 @@
         <v>8.56</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI15" t="n">
         <v>1.84</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CL15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CV15" t="n">
         <v>1.94</v>
       </c>
-      <c r="CM15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>1.95</v>
-      </c>
       <c r="CW15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DH15" t="n">
-        <v>67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM15" t="n">
-        <v>25.94</v>
+        <v>26.82</v>
       </c>
       <c r="DN15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="EB15" t="n">
         <v>1.06</v>
       </c>
-      <c r="DO15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="EC15" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="H16" t="n">
-        <v>98.62</v>
+        <v>96.11</v>
       </c>
       <c r="I16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J16" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="L16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>43.62</v>
+        <v>42.22</v>
       </c>
       <c r="N16" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>15</v>
+        <v>15.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.62</v>
+        <v>16.33</v>
       </c>
       <c r="R16" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="S16" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.25</v>
+        <v>49.44</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.88</v>
+        <v>8.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="AC16" t="n">
-        <v>23.62</v>
+        <v>23.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AF16" t="n">
         <v>0.14</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>43</v>
+        <v>43.14</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.14</v>
@@ -7192,46 +7192,46 @@
         <v>2.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.73</v>
+        <v>3.88</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.87</v>
+        <v>3.81</v>
       </c>
       <c r="BR16" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
@@ -7243,19 +7243,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.58</v>
+        <v>3.12</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.72</v>
+        <v>3.28</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CC16" t="n">
         <v>4.81</v>
@@ -7267,58 +7267,58 @@
         <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CH16" t="n">
         <v>1.28</v>
       </c>
       <c r="CI16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CN16" t="n">
         <v>1.61</v>
       </c>
-      <c r="CJ16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.63</v>
-      </c>
       <c r="CO16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV16" t="n">
         <v>1.62</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CX16" t="n">
         <v>1.79</v>
@@ -7333,85 +7333,85 @@
         <v>1.63</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.59999999999999</v>
+        <v>89.69</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.27</v>
+        <v>4.13</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.06</v>
+        <v>37.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.13</v>
+        <v>14.56</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.66</v>
+        <v>15.12</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.53</v>
+        <v>7.5</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.87</v>
+        <v>46.68</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.27</v>
+        <v>11.31</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.47</v>
+        <v>7.75</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="EA16" t="n">
         <v>21.06</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
         <v>3</v>
@@ -7580,16 +7580,16 @@
         <v>14.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.78</v>
+        <v>5.67</v>
       </c>
       <c r="BD17" t="n">
         <v>20.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BF17" t="n">
         <v>2.22</v>
@@ -7658,13 +7658,13 @@
         <v>4.11</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="CC17" t="n">
         <v>2.74</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
@@ -7709,10 +7709,10 @@
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
@@ -7724,25 +7724,25 @@
         <v>2.03</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
@@ -7805,10 +7805,10 @@
         <v>13.18</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="EA17" t="n">
         <v>21.71</v>
@@ -7920,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AH18" t="n">
         <v>3.89</v>
@@ -7932,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="AL18" t="n">
         <v>7.78</v>
@@ -7995,7 +7995,7 @@
         <v>1.96</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="BG18" t="n">
         <v>3.29</v>
@@ -8151,7 +8151,7 @@
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="DG18" t="n">
         <v>3.65</v>
@@ -8163,7 +8163,7 @@
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="DK18" t="n">
         <v>7</v>
@@ -8220,7 +8220,7 @@
         <v>2.16</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.67</v>
+        <v>43.78</v>
       </c>
       <c r="Y2" t="n">
         <v>0.22</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.12</v>
+        <v>42.18</v>
       </c>
       <c r="DW2" t="n">
         <v>0.17</v>
@@ -2010,7 +2010,7 @@
         <v>4.81</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="CA3" t="n">
         <v>3.89</v>
@@ -2076,22 +2076,22 @@
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW3" t="n">
         <v>2.07</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB3" t="n">
         <v>1.39</v>
@@ -3694,16 +3694,16 @@
         <v>2.17</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
@@ -3712,7 +3712,7 @@
         <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="DE7" t="n">
         <v>0.06</v>
@@ -4888,7 +4888,7 @@
         <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT10" t="n">
         <v>2.92</v>
@@ -4903,16 +4903,16 @@
         <v>1.96</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB10" t="n">
         <v>1.36</v>
@@ -4921,7 +4921,7 @@
         <v>2.14</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="DE10" t="n">
         <v>0.17</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48</v>
+        <v>47.89</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.11</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.12</v>
+        <v>49.06</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
@@ -6449,13 +6449,13 @@
         <v>5.43</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="CC14" t="n">
         <v>1.59</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CE14" t="n">
         <v>1.33</v>
@@ -6503,7 +6503,7 @@
         <v>2.7</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CU14" t="n">
         <v>1.51</v>
@@ -6515,25 +6515,25 @@
         <v>2.23</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="DA14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DC14" t="n">
         <v>1.83</v>
       </c>
-      <c r="DB14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1.82</v>
-      </c>
       <c r="DD14" t="n">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="DE14" t="n">
         <v>0.11</v>
@@ -6846,13 +6846,13 @@
         <v>3.43</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CA15" t="n">
         <v>3.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="CC15" t="n">
         <v>6.58</v>
@@ -6921,22 +6921,22 @@
         <v>1.58</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -7249,13 +7249,13 @@
         <v>3.12</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CA16" t="n">
         <v>3.44</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC16" t="n">
         <v>4.81</v>
@@ -7303,13 +7303,13 @@
         <v>4.7</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CS16" t="n">
         <v>3.3</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CU16" t="n">
         <v>1.34</v>
@@ -7318,28 +7318,28 @@
         <v>1.62</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.2</v>
+        <v>5.23</v>
       </c>
       <c r="DE16" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="H5" t="n">
-        <v>82.29000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="J5" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>37.86</v>
+        <v>39.88</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P5" t="n">
-        <v>13.86</v>
+        <v>13.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.57</v>
+        <v>13.12</v>
       </c>
       <c r="R5" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45.71</v>
+        <v>45.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.29</v>
+        <v>6.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.43</v>
+        <v>19.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>2.56</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM5" t="n">
         <v>0.88</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.69</v>
+        <v>4.47</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.56</v>
+        <v>5.76</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT5" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.12</v>
+        <v>3.95</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.83</v>
+        <v>4.58</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="CC5" t="n">
         <v>5.17</v>
@@ -2831,46 +2831,46 @@
         <v>5.62</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.52</v>
+        <v>3.64</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS5" t="n">
         <v>3.01</v>
@@ -2882,106 +2882,106 @@
         <v>1.42</v>
       </c>
       <c r="CV5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY5" t="n">
         <v>1.9</v>
       </c>
-      <c r="CW5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CZ5" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DG5" t="n">
         <v>1.94</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.19</v>
+        <v>89.36</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.69</v>
+        <v>38.65</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.75</v>
+        <v>14.71</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.44</v>
+        <v>12.29</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.06</v>
+        <v>9.17</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.94</v>
+        <v>44.06</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.75</v>
+        <v>11.82</v>
       </c>
       <c r="DY5" t="n">
         <v>7.88</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.25</v>
+        <v>20.35</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,127 +3084,127 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AI6" t="n">
-        <v>85.62</v>
+        <v>79.67</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>34.11</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16.25</v>
+        <v>15.89</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.75</v>
+        <v>11.22</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.12</v>
+        <v>43.89</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.25</v>
+        <v>17.44</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.880000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY6" t="n">
         <v>4.37</v>
@@ -3222,25 +3222,25 @@
         <v>4.99</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.94</v>
+        <v>5.69</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.91</v>
+        <v>5.63</v>
       </c>
       <c r="CE6" t="n">
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
@@ -3252,13 +3252,13 @@
         <v>2.01</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN6" t="n">
         <v>1.69</v>
@@ -3270,121 +3270,121 @@
         <v>2.11</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV6" t="n">
         <v>1.87</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX6" t="n">
         <v>1.61</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="DG6" t="n">
         <v>2.06</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.56</v>
+        <v>82.41</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.94</v>
+        <v>35.88</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.25</v>
+        <v>14.18</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.93</v>
+        <v>11.64</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.43</v>
+        <v>8.35</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.25</v>
+        <v>43.18</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.75</v>
+        <v>11.53</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.88</v>
+        <v>7.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.62</v>
+        <v>18.64</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="7">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -5824,49 +5824,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H13" t="n">
-        <v>76.86</v>
+        <v>71.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="L13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>33.86</v>
+        <v>31.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="P13" t="n">
-        <v>15.43</v>
+        <v>14.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.29</v>
+        <v>14.12</v>
       </c>
       <c r="R13" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.57</v>
+        <v>51.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.86</v>
+        <v>10.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.86</v>
+        <v>20.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0.33</v>
@@ -5983,70 +5983,70 @@
         <v>2.44</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.19</v>
+        <v>8.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS13" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU13" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.46</v>
+        <v>4.16</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.73</v>
+        <v>4.43</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="CC13" t="n">
         <v>4.89</v>
@@ -6061,16 +6061,16 @@
         <v>3.09</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH13" t="n">
         <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
         <v>1.71</v>
@@ -6091,34 +6091,34 @@
         <v>2.22</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY13" t="n">
         <v>2.2</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA13" t="n">
         <v>1.65</v>
@@ -6130,49 +6130,49 @@
         <v>2.22</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DH13" t="n">
-        <v>76.19</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="DK13" t="n">
         <v>4.06</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.81</v>
+        <v>31.76</v>
       </c>
       <c r="DN13" t="n">
         <v>0.88</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.13</v>
+        <v>14.65</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.25</v>
+        <v>15.12</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.5</v>
+        <v>8.35</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.06</v>
+        <v>49.59</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.94</v>
+        <v>9.77</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.31</v>
+        <v>6.23</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.56</v>
+        <v>20.41</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="14">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0.22</v>
@@ -7111,139 +7111,139 @@
         <v>3.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>1.88</v>
       </c>
       <c r="AI16" t="n">
-        <v>81.43000000000001</v>
+        <v>84</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.71</v>
+        <v>34.5</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.14</v>
+        <v>12.88</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.57</v>
+        <v>13.62</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.43</v>
+        <v>8.25</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>43.14</v>
+        <v>44.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.57</v>
+        <v>12</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.14</v>
+        <v>19.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.25</v>
+        <v>8.35</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.81</v>
+        <v>4.12</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY16" t="n">
         <v>3.12</v>
@@ -7252,22 +7252,22 @@
         <v>3.26</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.81</v>
+        <v>4.56</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.3</v>
+        <v>5.01</v>
       </c>
       <c r="CE16" t="n">
         <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="CG16" t="n">
         <v>2.46</v>
@@ -7276,16 +7276,16 @@
         <v>1.28</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CK16" t="n">
         <v>1.75</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CM16" t="n">
         <v>2.02</v>
@@ -7294,13 +7294,13 @@
         <v>1.61</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7315,13 +7315,13 @@
         <v>1.34</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CY16" t="n">
         <v>2.27</v>
@@ -7336,85 +7336,85 @@
         <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="DH16" t="n">
-        <v>89.69</v>
+        <v>90.41</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.13</v>
+        <v>4.35</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.62</v>
+        <v>38.59</v>
       </c>
       <c r="DN16" t="n">
         <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.56</v>
+        <v>14.36</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.12</v>
+        <v>15.05</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.68</v>
+        <v>47.12</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.31</v>
+        <v>11.94</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.75</v>
+        <v>8.23</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.06</v>
+        <v>21.41</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>43.89</v>
+        <v>43.78</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.22</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.18</v>
+        <v>43.12</v>
       </c>
       <c r="DW6" t="n">
         <v>0.17</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.5</v>
+        <v>51.62</v>
       </c>
       <c r="Y13" t="n">
         <v>0.12</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.59</v>
+        <v>49.65</v>
       </c>
       <c r="DW13" t="n">
         <v>0.11</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,52 +3484,52 @@
         <v>2.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>69.56</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN7" t="n">
         <v>28</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.44</v>
+        <v>15.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.22</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.779999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>44.11</v>
+        <v>43.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.779999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.35</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.18</v>
+        <v>4.39</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY7" t="n">
         <v>3.61</v>
@@ -3625,73 +3625,73 @@
         <v>3.84</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.89</v>
+        <v>4.14</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.94</v>
+        <v>6.75</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.61</v>
+        <v>7.61</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL7" t="n">
         <v>2.01</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
       <c r="CR7" t="n">
         <v>1.52</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="CT7" t="n">
         <v>2.65</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CV7" t="n">
         <v>1.74</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CX7" t="n">
         <v>1.66</v>
@@ -3706,13 +3706,13 @@
         <v>1.77</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.4</v>
+        <v>4.29</v>
       </c>
       <c r="DE7" t="n">
         <v>0.06</v>
@@ -3721,73 +3721,73 @@
         <v>2</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>75.94</v>
+        <v>75.83</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.18</v>
+        <v>31</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.82</v>
+        <v>15.61</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.7</v>
+        <v>14.56</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.42</v>
+        <v>8.56</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.94</v>
+        <v>45.56</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.710000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.76</v>
+        <v>5.72</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.65</v>
+        <v>17.61</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="8">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="H18" t="n">
-        <v>124.5</v>
+        <v>121.78</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="K18" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="L18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M18" t="n">
-        <v>60.5</v>
+        <v>59.89</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="P18" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="U18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>59.62</v>
+        <v>59.78</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.25</v>
+        <v>20.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.5</v>
+        <v>12.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.75</v>
+        <v>17.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.78</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
         <v>1.06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.76</v>
+        <v>4.94</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.94</v>
+        <v>4.78</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT18" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="CB18" t="n">
-        <v>7.1</v>
+        <v>7.17</v>
       </c>
       <c r="CC18" t="n">
         <v>1.5</v>
@@ -8073,10 +8073,10 @@
         <v>1.21</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CH18" t="n">
         <v>1.49</v>
@@ -8085,7 +8085,7 @@
         <v>1.72</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CK18" t="n">
         <v>1.47</v>
@@ -8094,16 +8094,16 @@
         <v>1.94</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CO18" t="n">
         <v>1.11</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.45</v>
@@ -8112,19 +8112,19 @@
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CT18" t="n">
         <v>3.15</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CX18" t="n">
         <v>1.61</v>
@@ -8142,85 +8142,85 @@
         <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="DH18" t="n">
-        <v>114.76</v>
+        <v>113.94</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="DK18" t="n">
-        <v>7</v>
+        <v>6.84</v>
       </c>
       <c r="DL18" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DM18" t="n">
-        <v>56.88</v>
+        <v>56.78</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.59</v>
+        <v>12.56</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.53</v>
+        <v>13.44</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.11</v>
+        <v>62.06</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>19.23</v>
+        <v>19.06</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.59</v>
+        <v>11.61</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.65</v>
+        <v>7.44</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.71</v>
+        <v>16.67</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H2" t="n">
-        <v>84.33</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>35.22</v>
+        <v>34.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>16.44</v>
+        <v>15.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.11</v>
+        <v>13.9</v>
       </c>
       <c r="R2" t="n">
-        <v>7.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="T2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.78</v>
+        <v>43.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.44</v>
+        <v>7.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.56</v>
+        <v>21.7</v>
       </c>
       <c r="AD2" t="n">
         <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.62</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.76</v>
+        <v>8.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BT2" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.01</v>
+        <v>4.91</v>
       </c>
       <c r="CC2" t="n">
         <v>10.32</v>
@@ -1625,19 +1625,19 @@
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI2" t="n">
         <v>1.71</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK2" t="n">
         <v>1.57</v>
@@ -1646,37 +1646,37 @@
         <v>2.09</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="CR2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CU2" t="n">
         <v>1.46</v>
       </c>
-      <c r="CS2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="CV2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CX2" t="n">
         <v>1.66</v>
@@ -1703,43 +1703,43 @@
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.53</v>
+        <v>83.33</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.23</v>
+        <v>33.94</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DO2" t="n">
         <v>1.06</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.88</v>
+        <v>14.66</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.41</v>
+        <v>12.39</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.289999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.18</v>
+        <v>41.89</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.18</v>
+        <v>7.28</v>
       </c>
       <c r="DZ2" t="n">
         <v>3</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.36</v>
+        <v>20.94</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="H3" t="n">
-        <v>76.78</v>
+        <v>77.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>42.33</v>
+        <v>42.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="P3" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.33</v>
+        <v>14.3</v>
       </c>
       <c r="R3" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.56</v>
+        <v>46</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.56</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.33</v>
+        <v>6.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.11</v>
+        <v>19.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.88</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.88</v>
+        <v>7.67</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.81</v>
+        <v>4.57</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.88</v>
+        <v>4.64</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.06</v>
+        <v>3.99</v>
       </c>
       <c r="CC3" t="n">
         <v>5.28</v>
@@ -2028,154 +2028,154 @@
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ3" t="n">
         <v>2</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CL3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN3" t="n">
         <v>1.64</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW3" t="n">
         <v>2.07</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DB3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>78.39</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DO3" t="n">
         <v>1.39</v>
       </c>
-      <c r="DC3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>78.06</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>1.23</v>
-      </c>
       <c r="DP3" t="n">
-        <v>12.88</v>
+        <v>13.05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.53</v>
+        <v>14</v>
       </c>
       <c r="DR3" t="n">
         <v>7.94</v>
       </c>
       <c r="DS3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="DW3" t="n">
         <v>0.17</v>
       </c>
-      <c r="DT3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>0.18</v>
-      </c>
       <c r="DX3" t="n">
-        <v>9.24</v>
+        <v>9.56</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.47</v>
+        <v>5.83</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.29</v>
+        <v>19.56</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.11</v>
@@ -2275,139 +2275,139 @@
         <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>109.75</v>
+        <v>112.56</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.5</v>
+        <v>5.22</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>50.62</v>
+        <v>55.22</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.62</v>
+        <v>12.11</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.88</v>
+        <v>13.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.12</v>
+        <v>6.56</v>
       </c>
       <c r="AT4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AU4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>57</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.53</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.39</v>
@@ -2419,13 +2419,13 @@
         <v>5.59</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="CE4" t="n">
         <v>1.31</v>
@@ -2434,7 +2434,7 @@
         <v>2.49</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH4" t="n">
         <v>1.53</v>
@@ -2446,10 +2446,10 @@
         <v>2.09</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM4" t="n">
         <v>2.43</v>
@@ -2461,7 +2461,7 @@
         <v>1.22</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ4" t="n">
         <v>2.76</v>
@@ -2500,82 +2500,82 @@
         <v>1.25</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="DE4" t="n">
         <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="DH4" t="n">
-        <v>115.35</v>
+        <v>116.44</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.53</v>
+        <v>5.83</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>58.94</v>
+        <v>60.78</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.23</v>
+        <v>12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.47</v>
+        <v>14.34</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.76</v>
+        <v>5.56</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>57.76</v>
+        <v>58.06</v>
       </c>
       <c r="DW4" t="n">
         <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>15.59</v>
+        <v>16.06</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.83</v>
+        <v>10.17</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.76</v>
+        <v>5.89</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.65</v>
+        <v>18.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="EC4" t="n">
         <v>1.94</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,49 +2678,49 @@
         <v>3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>94.56</v>
+        <v>92.7</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>37.56</v>
+        <v>37.1</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.44</v>
+        <v>15.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.56</v>
+        <v>11.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.44</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.56</v>
+        <v>42.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA5" t="n">
         <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.89</v>
+        <v>20.5</v>
       </c>
       <c r="BE5" t="n">
         <v>1.37</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.24</v>
+        <v>10.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.76</v>
+        <v>5.83</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>3.95</v>
@@ -2819,16 +2819,16 @@
         <v>4.58</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.62</v>
+        <v>5.58</v>
       </c>
       <c r="CE5" t="n">
         <v>1.42</v>
@@ -2837,7 +2837,7 @@
         <v>2.93</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CH5" t="n">
         <v>1.38</v>
@@ -2852,10 +2852,10 @@
         <v>1.5</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN5" t="n">
         <v>1.93</v>
@@ -2864,7 +2864,7 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.64</v>
@@ -2873,7 +2873,7 @@
         <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CT5" t="n">
         <v>2.82</v>
@@ -2888,13 +2888,13 @@
         <v>1.98</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY5" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA5" t="n">
         <v>1.91</v>
@@ -2906,7 +2906,7 @@
         <v>2.15</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="DE5" t="n">
         <v>0.11</v>
@@ -2915,73 +2915,73 @@
         <v>1.95</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.36</v>
+        <v>88.61</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.65</v>
+        <v>38.34</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO5" t="n">
         <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.71</v>
+        <v>14.89</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.17</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.06</v>
+        <v>44.17</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.82</v>
+        <v>11.89</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.94</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.35</v>
+        <v>20.17</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>84.44</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>37.88</v>
+        <v>37.33</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="P6" t="n">
-        <v>12.25</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.12</v>
+        <v>12.22</v>
       </c>
       <c r="R6" t="n">
-        <v>9.119999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>42.38</v>
+        <v>41.44</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.12</v>
+        <v>11.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.25</v>
+        <v>7.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>20</v>
+        <v>19.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.65</v>
+        <v>9.44</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.37</v>
+        <v>4.62</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.99</v>
+        <v>5.2</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CB6" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="CC6" t="n">
         <v>5.69</v>
@@ -3240,7 +3240,7 @@
         <v>2.92</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
@@ -3252,10 +3252,10 @@
         <v>2.01</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM6" t="n">
         <v>2.15</v>
@@ -3267,28 +3267,28 @@
         <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS6" t="n">
         <v>3.1</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CU6" t="n">
         <v>1.41</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CX6" t="n">
         <v>1.61</v>
@@ -3306,10 +3306,10 @@
         <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3318,73 +3318,73 @@
         <v>2.06</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>82.41</v>
+        <v>82.06</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
         <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="DL6" t="n">
         <v>0.11</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.88</v>
+        <v>35.72</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.18</v>
+        <v>14.44</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.64</v>
+        <v>11.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.35</v>
+        <v>8.23</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.12</v>
+        <v>42.61</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.53</v>
+        <v>11.28</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.76</v>
+        <v>7.61</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.64</v>
+        <v>18.56</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="7">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.22</v>
@@ -4290,49 +4290,49 @@
         <v>3.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AI9" t="n">
-        <v>81</v>
+        <v>88.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.12</v>
+        <v>37.22</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.880000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48.5</v>
+        <v>50.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.25</v>
+        <v>7.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.25</v>
+        <v>21.78</v>
       </c>
       <c r="BE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="BF9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.41</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1</v>
-      </c>
       <c r="BK9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS9" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU9" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>3.72</v>
@@ -4431,70 +4431,70 @@
         <v>4.41</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.11</v>
+        <v>5.73</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.56</v>
+        <v>6.16</v>
       </c>
       <c r="CE9" t="n">
         <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI9" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK9" t="n">
         <v>1.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN9" t="n">
         <v>1.77</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CR9" t="n">
         <v>1.46</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW9" t="n">
         <v>1.96</v>
@@ -4521,46 +4521,46 @@
         <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DH9" t="n">
-        <v>83.76000000000001</v>
+        <v>87.44</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="DK9" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>32.35</v>
+        <v>35.33</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.94</v>
+        <v>13.83</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12</v>
+        <v>11.94</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.59</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.77</v>
+        <v>50.5</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.529999999999999</v>
+        <v>10</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.59</v>
+        <v>7.06</v>
       </c>
       <c r="DZ9" t="n">
         <v>2.94</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.41</v>
+        <v>20.28</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>89.12</v>
+        <v>89.11</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.25</v>
+        <v>5.78</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BL10" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN10" t="n">
-        <v>52.25</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>52</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.53</v>
-      </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
         <v>1</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="BR10" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS10" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
         <v>2.95</v>
@@ -4834,25 +4834,25 @@
         <v>2.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CC10" t="n">
         <v>2.76</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH10" t="n">
         <v>1.28</v>
@@ -4861,28 +4861,28 @@
         <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN10" t="n">
         <v>1.81</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="CR10" t="n">
         <v>1.44</v>
@@ -4897,7 +4897,7 @@
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW10" t="n">
         <v>1.96</v>
@@ -4915,55 +4915,55 @@
         <v>1.9</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.47</v>
+        <v>89.44</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.47</v>
+        <v>5.28</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.12</v>
+        <v>48.28</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DP10" t="n">
-        <v>18.41</v>
+        <v>18.39</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.23</v>
+        <v>16.27</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.65</v>
+        <v>7.78</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.71</v>
+        <v>50.62</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.59</v>
+        <v>13.22</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.119999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.06</v>
+        <v>20.89</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="11">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H12" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M12" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P12" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M12" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P12" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>46.62</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.12</v>
       </c>
       <c r="AF12" t="n">
         <v>0.22</v>
@@ -5580,49 +5580,49 @@
         <v>3.33</v>
       </c>
       <c r="BG12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.18</v>
+        <v>5.28</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BU12" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,16 +5631,16 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CB12" t="n">
         <v>3.6</v>
@@ -5652,34 +5652,34 @@
         <v>3.96</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO12" t="n">
         <v>1.4</v>
@@ -5688,121 +5688,121 @@
         <v>2.28</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="CR12" t="n">
         <v>1.51</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CZ12" t="n">
         <v>2.16</v>
       </c>
-      <c r="CX12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.14</v>
-      </c>
       <c r="DA12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB12" t="n">
         <v>1.42</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="DH12" t="n">
-        <v>87.88</v>
+        <v>87.39</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.06</v>
+        <v>6.11</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.83</v>
+        <v>46.56</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.59</v>
+        <v>14.17</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.7</v>
+        <v>14.88</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.64</v>
+        <v>6.66</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.53</v>
+        <v>48.83</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.18</v>
+        <v>14.27</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.12</v>
+        <v>22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,139 +5902,139 @@
         <v>2.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>75.67</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>34.1</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.89</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>47.89</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BM13" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.35</v>
+        <v>4.11</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU13" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>4.16</v>
@@ -6043,136 +6043,136 @@
         <v>4.43</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.1</v>
+        <v>4.94</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="CR13" t="n">
         <v>1.49</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
         <v>2.08</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="DE13" t="n">
         <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DH13" t="n">
-        <v>73.70999999999999</v>
+        <v>76.28</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.06</v>
+        <v>3.83</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.76</v>
+        <v>32.94</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.65</v>
+        <v>14.17</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.12</v>
+        <v>15.16</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.65</v>
+        <v>50.16</v>
       </c>
       <c r="DW13" t="n">
         <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.41</v>
+        <v>20.33</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.12</v>
@@ -6305,130 +6305,130 @@
         <v>2.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BN14" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>100.33</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>50.11</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>56.78</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS14" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BY14" t="n">
         <v>1.35</v>
@@ -6446,31 +6446,31 @@
         <v>1.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.43</v>
+        <v>5.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.64</v>
+        <v>5.57</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CJ14" t="n">
         <v>2.14</v>
@@ -6479,34 +6479,34 @@
         <v>1.6</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV14" t="n">
         <v>1.72</v>
@@ -6518,97 +6518,97 @@
         <v>1.62</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB14" t="n">
         <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="DE14" t="n">
         <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH14" t="n">
-        <v>105.06</v>
+        <v>104.17</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM14" t="n">
-        <v>51.23</v>
+        <v>50.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.59</v>
+        <v>13.67</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.65</v>
+        <v>11.94</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.82</v>
+        <v>5.89</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.53</v>
+        <v>56.17</v>
       </c>
       <c r="DW14" t="n">
         <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.59</v>
+        <v>14.44</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.24</v>
+        <v>19.17</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="H15" t="n">
-        <v>73</v>
+        <v>71.67</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="K15" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="L15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>23.67</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="P15" t="n">
-        <v>12.5</v>
+        <v>12.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>15.11</v>
       </c>
       <c r="R15" t="n">
-        <v>9.380000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="S15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.25</v>
+        <v>46.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.75</v>
+        <v>16.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.78</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.76</v>
+        <v>10.94</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.82</v>
+        <v>4.94</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS15" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT15" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU15" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.43</v>
+        <v>4.22</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.67</v>
+        <v>4.39</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="CC15" t="n">
         <v>6.58</v>
@@ -6864,40 +6864,40 @@
         <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CH15" t="n">
         <v>1.41</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN15" t="n">
         <v>1.85</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
@@ -6912,7 +6912,7 @@
         <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW15" t="n">
         <v>1.96</v>
@@ -6921,64 +6921,64 @@
         <v>1.58</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.34</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>68.18000000000001</v>
+        <v>67.78</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="DL15" t="n">
         <v>0.11</v>
       </c>
       <c r="DM15" t="n">
-        <v>26.82</v>
+        <v>26.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.88</v>
+        <v>13.77</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.47</v>
+        <v>15.06</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.24</v>
+        <v>10.34</v>
       </c>
       <c r="DS15" t="n">
         <v>0.11</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.83</v>
+        <v>45.34</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.35</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.06</v>
+        <v>16.38</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
-        <v>96.11</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>4.67</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>42.22</v>
+        <v>41.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>15.67</v>
+        <v>15.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.33</v>
+        <v>16.5</v>
       </c>
       <c r="R16" t="n">
-        <v>6.78</v>
+        <v>6.9</v>
       </c>
       <c r="S16" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="U16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>49.44</v>
+        <v>49.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.89</v>
+        <v>12.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.33</v>
+        <v>8.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>23.33</v>
+        <v>23.1</v>
       </c>
       <c r="AD16" t="n">
         <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="AF16" t="n">
         <v>0.25</v>
@@ -7192,70 +7192,70 @@
         <v>2.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.35</v>
+        <v>8.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS16" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BT16" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CC16" t="n">
         <v>4.56</v>
@@ -7267,40 +7267,40 @@
         <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CH16" t="n">
         <v>1.28</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7315,10 +7315,10 @@
         <v>1.34</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CX16" t="n">
         <v>1.8</v>
@@ -7342,79 +7342,79 @@
         <v>5.25</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.41</v>
+        <v>90.44</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.59</v>
+        <v>38.56</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.36</v>
+        <v>14.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.05</v>
+        <v>15.22</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.12</v>
+        <v>47.33</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.94</v>
+        <v>12.11</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.23</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.41</v>
+        <v>21.39</v>
       </c>
       <c r="EB16" t="n">
         <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.25</v>
@@ -7517,136 +7517,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>106.44</v>
+        <v>107.9</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.22</v>
+        <v>56.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.44</v>
+        <v>11.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.22</v>
+        <v>13.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>65.89</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.67</v>
+        <v>14.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.67</v>
+        <v>20.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.59</v>
+        <v>8.44</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN17" t="n">
         <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX17" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.67</v>
@@ -7655,64 +7655,64 @@
         <v>1.74</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="CB17" t="n">
         <v>4.19</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK17" t="n">
         <v>1.57</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
@@ -7721,7 +7721,7 @@
         <v>1.85</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX17" t="n">
         <v>1.59</v>
@@ -7745,73 +7745,73 @@
         <v>3.5</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DH17" t="n">
-        <v>110</v>
+        <v>110.61</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM17" t="n">
-        <v>54.94</v>
+        <v>55.33</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.94</v>
+        <v>11.11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.29</v>
+        <v>12.61</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>64.18000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.18</v>
+        <v>13.06</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.119999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.71</v>
+        <v>21.72</v>
       </c>
       <c r="EB17" t="n">
         <v>1.5</v>
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -8242,82 +8242,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H19" t="n">
-        <v>88.56</v>
+        <v>88.8</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M19" t="n">
-        <v>41.78</v>
+        <v>43.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>15.89</v>
+        <v>16.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.67</v>
+        <v>14.7</v>
       </c>
       <c r="R19" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.22</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.11</v>
+        <v>20.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>1.75</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.119999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU19" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="CC19" t="n">
         <v>3.23</v>
@@ -8476,40 +8476,40 @@
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.97</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO19" t="n">
         <v>1.39</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8518,79 +8518,79 @@
         <v>3.09</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU19" t="n">
         <v>1.4</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB19" t="n">
         <v>1.41</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.70999999999999</v>
+        <v>93.56</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.59</v>
+        <v>44.55</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.59</v>
+        <v>14.83</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.47</v>
+        <v>15.45</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.41</v>
+        <v>7.44</v>
       </c>
       <c r="DS19" t="n">
         <v>0.11</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.65</v>
+        <v>49.67</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.77</v>
+        <v>13.17</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.18</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.47</v>
+        <v>22.22</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
         <v>2.11</v>
@@ -3015,7 +3015,7 @@
         <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -3078,7 +3078,7 @@
         <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DG6" t="n">
         <v>2</v>
@@ -3327,7 +3327,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK6" t="n">
         <v>3.72</v>
@@ -3384,7 +3384,7 @@
         <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="7">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>83.11</v>
+        <v>83.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>33.44</v>
+        <v>33.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>13.56</v>
+        <v>13.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.89</v>
+        <v>16.4</v>
       </c>
       <c r="R8" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54.11</v>
+        <v>52.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.78</v>
+        <v>13.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.67</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.56</v>
+        <v>20.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,70 +3968,70 @@
         <v>2.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.59</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.71</v>
+        <v>4.44</v>
       </c>
       <c r="BR8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="CA8" t="n">
         <v>4.02</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>4.07</v>
-      </c>
       <c r="CB8" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="CC8" t="n">
         <v>7.38</v>
@@ -4043,154 +4043,154 @@
         <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK8" t="n">
         <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO8" t="n">
         <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CX8" t="n">
         <v>1.67</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.19</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="DH8" t="n">
-        <v>73.59</v>
+        <v>74.34</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="DL8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="DS8" t="n">
         <v>0.17</v>
       </c>
-      <c r="DM8" t="n">
-        <v>29.94</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.18</v>
-      </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.41</v>
+        <v>47.94</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.59</v>
+        <v>11.28</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.82</v>
+        <v>7.61</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.24</v>
+        <v>19.28</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="9">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.11</v>
@@ -5096,139 +5096,139 @@
         <v>3.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>93.25</v>
+        <v>94.67</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.38</v>
+        <v>47.44</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>13.78</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.62</v>
+        <v>12.89</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.75</v>
+        <v>50.89</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.88</v>
+        <v>12.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.880000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.25</v>
+        <v>20.44</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.35</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.47</v>
+        <v>4.22</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT11" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU11" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY11" t="n">
         <v>3.48</v>
@@ -5237,40 +5237,40 @@
         <v>3.52</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="CC11" t="n">
-        <v>6.38</v>
+        <v>5.93</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.27</v>
+        <v>5.87</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CG11" t="n">
         <v>2.88</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CM11" t="n">
         <v>2.1</v>
@@ -5282,124 +5282,124 @@
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CU11" t="n">
         <v>1.45</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="DH11" t="n">
-        <v>97.94</v>
+        <v>98.39</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.71</v>
+        <v>45.78</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.35</v>
+        <v>13.28</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.41</v>
+        <v>12.56</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.289999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.41</v>
+        <v>50.94</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.41</v>
+        <v>12.34</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.119999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.3</v>
+        <v>4.39</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.82</v>
+        <v>20.44</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AI2" t="n">
-        <v>82.62</v>
+        <v>85.67</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.38</v>
+        <v>4.22</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>33.12</v>
+        <v>36.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>10.78</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.12</v>
+        <v>10.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>40.38</v>
+        <v>42.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.88</v>
+        <v>8.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>21.89</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.96</v>
+        <v>1.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.56</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.11</v>
+        <v>4.32</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU2" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BX2" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY2" t="n">
         <v>4.43</v>
@@ -1610,67 +1610,67 @@
         <v>4.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.91</v>
+        <v>4.82</v>
       </c>
       <c r="CC2" t="n">
-        <v>10.32</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="CD2" t="n">
-        <v>12.07</v>
+        <v>11.18</v>
       </c>
       <c r="CE2" t="n">
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI2" t="n">
         <v>1.71</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
       </c>
       <c r="CS2" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV2" t="n">
         <v>1.78</v>
@@ -1682,97 +1682,97 @@
         <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
         <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.33</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.17</v>
+        <v>3.58</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM2" t="n">
-        <v>33.94</v>
+        <v>35.58</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.66</v>
+        <v>14.58</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.39</v>
+        <v>12.42</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.550000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>41.89</v>
+        <v>42.74</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.28</v>
+        <v>11.16</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.28</v>
+        <v>7.95</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.94</v>
+        <v>21.79</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="3">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="H7" t="n">
-        <v>83.12</v>
+        <v>81.11</v>
       </c>
       <c r="I7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J7" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="K7" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="L7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>34.75</v>
+        <v>34.89</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="P7" t="n">
-        <v>16.25</v>
+        <v>16.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>6.88</v>
+        <v>7.56</v>
       </c>
       <c r="S7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48</v>
+        <v>47.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="AA7" t="n">
         <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.5</v>
+        <v>20.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AF7" t="n">
         <v>0.1</v>
@@ -3565,70 +3565,70 @@
         <v>3.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.390000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.28</v>
+        <v>4.47</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BX7" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.61</v>
+        <v>3.44</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CC7" t="n">
         <v>6.75</v>
@@ -3637,13 +3637,13 @@
         <v>7.61</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH7" t="n">
         <v>1.35</v>
@@ -3655,31 +3655,31 @@
         <v>2.09</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO7" t="n">
         <v>1.38</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CR7" t="n">
         <v>1.52</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CT7" t="n">
         <v>2.65</v>
@@ -3691,7 +3691,7 @@
         <v>1.74</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CX7" t="n">
         <v>1.66</v>
@@ -3700,61 +3700,61 @@
         <v>2.06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
         <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>75.83</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>31</v>
+        <v>31.26</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.61</v>
+        <v>15.58</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.56</v>
+        <v>14.47</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.56</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.05</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.56</v>
+        <v>45.37</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.56</v>
+        <v>8.58</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.61</v>
+        <v>18</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="8">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1526,16 +1526,16 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.33</v>
+        <v>42.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.33</v>
+        <v>8.44</v>
       </c>
       <c r="BC2" t="n">
         <v>2.67</v>
@@ -1544,7 +1544,7 @@
         <v>21.89</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF2" t="n">
         <v>2</v>
@@ -1679,7 +1679,7 @@
         <v>2.16</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY2" t="n">
         <v>2.07</v>
@@ -1691,13 +1691,13 @@
         <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC2" t="n">
         <v>2.08</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="DE2" t="n">
         <v>0.05</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.74</v>
+        <v>42.68</v>
       </c>
       <c r="DW2" t="n">
         <v>0.21</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.16</v>
+        <v>11.21</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.21</v>
@@ -1769,7 +1769,7 @@
         <v>21.79</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC2" t="n">
         <v>2.42</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AI3" t="n">
-        <v>79.5</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>30.38</v>
+        <v>29.44</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.62</v>
+        <v>13.11</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.75</v>
+        <v>7.11</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.25</v>
+        <v>40.22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.5</v>
+        <v>19.11</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.67</v>
+        <v>7.63</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY3" t="n">
         <v>4.57</v>
@@ -2013,25 +2013,25 @@
         <v>4.64</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.28</v>
+        <v>5.44</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.38</v>
+        <v>6.52</v>
       </c>
       <c r="CE3" t="n">
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
@@ -2043,13 +2043,13 @@
         <v>2</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL3" t="n">
         <v>2.06</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN3" t="n">
         <v>1.64</v>
@@ -2058,19 +2058,19 @@
         <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2088,7 +2088,7 @@
         <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
         <v>1.73</v>
@@ -2097,85 +2097,85 @@
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DH3" t="n">
-        <v>78.39</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="DL3" t="n">
         <v>0.11</v>
       </c>
       <c r="DM3" t="n">
-        <v>37.22</v>
+        <v>36.42</v>
       </c>
       <c r="DN3" t="n">
         <v>0.89</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.05</v>
+        <v>12.95</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14</v>
+        <v>13.74</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.94</v>
+        <v>7.63</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.89</v>
+        <v>43.26</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.56</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.83</v>
+        <v>5.68</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.72</v>
+        <v>3.53</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.56</v>
+        <v>19.37</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>120.33</v>
+        <v>119.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>66.33</v>
+        <v>66.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>11.89</v>
+        <v>11.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="R4" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>58.44</v>
+        <v>59.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.67</v>
+        <v>9.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.89</v>
+        <v>18.9</v>
       </c>
       <c r="AD4" t="n">
         <v>1.94</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
         <v>0.11</v>
@@ -2356,70 +2356,70 @@
         <v>2.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.83</v>
+        <v>8.74</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>1.39</v>
       </c>
-      <c r="BO4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>94.44</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1.41</v>
-      </c>
       <c r="CA4" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.14</v>
+        <v>6.23</v>
       </c>
       <c r="CC4" t="n">
         <v>1.67</v>
@@ -2431,46 +2431,46 @@
         <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH4" t="n">
         <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO4" t="n">
         <v>1.22</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CT4" t="n">
         <v>3.1</v>
@@ -2479,10 +2479,10 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
@@ -2497,88 +2497,88 @@
         <v>1.97</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>116.44</v>
+        <v>116.27</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>60.78</v>
+        <v>61.31</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="DP4" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.34</v>
+        <v>14.79</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.56</v>
+        <v>5.42</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>58.06</v>
+        <v>58.48</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.06</v>
+        <v>16</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.5</v>
+        <v>18.53</v>
       </c>
       <c r="EB4" t="n">
         <v>1.87</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,91 +2588,91 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>83.5</v>
+        <v>83.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>39.88</v>
+        <v>40.67</v>
       </c>
       <c r="N5" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="P5" t="n">
-        <v>13.88</v>
+        <v>14.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.12</v>
+        <v>12.33</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45.75</v>
+        <v>45.89</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>10.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.5</v>
+        <v>6.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.75</v>
+        <v>19.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
         <v>3</v>
@@ -2759,70 +2759,70 @@
         <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.95</v>
+        <v>3.73</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.58</v>
+        <v>4.29</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC5" t="n">
         <v>5.15</v>
@@ -2831,10 +2831,10 @@
         <v>5.58</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG5" t="n">
         <v>2.8</v>
@@ -2843,145 +2843,145 @@
         <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CR5" t="n">
         <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="CU5" t="n">
         <v>1.42</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX5" t="n">
         <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.34</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.61</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
         <v>3.11</v>
       </c>
       <c r="DK5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>44.32</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="DZ5" t="n">
         <v>4</v>
       </c>
-      <c r="DL5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="DS5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DT5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>44.17</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>7.94</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>3.94</v>
-      </c>
       <c r="EA5" t="n">
-        <v>20.17</v>
+        <v>19.89</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,127 +3084,127 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AI6" t="n">
-        <v>79.67</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.11</v>
+        <v>34.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.89</v>
+        <v>16.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>43.78</v>
+        <v>43.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.33</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.44</v>
+        <v>17.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.44</v>
+        <v>9.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BY6" t="n">
         <v>4.62</v>
@@ -3222,25 +3222,25 @@
         <v>5.2</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CB6" t="n">
         <v>4.02</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.63</v>
+        <v>5.72</v>
       </c>
       <c r="CE6" t="n">
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
@@ -3249,19 +3249,19 @@
         <v>1.77</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK6" t="n">
         <v>1.48</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CO6" t="n">
         <v>1.34</v>
@@ -3270,16 +3270,16 @@
         <v>2.1</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU6" t="n">
         <v>1.41</v>
@@ -3294,97 +3294,97 @@
         <v>1.61</v>
       </c>
       <c r="CY6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.26</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
         <v>2.12</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG6" t="n">
         <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>82.06</v>
+        <v>81.52</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.72</v>
+        <v>35.95</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.44</v>
+        <v>14.74</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.72</v>
+        <v>11.58</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.23</v>
+        <v>8.16</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.61</v>
+        <v>42.42</v>
       </c>
       <c r="DW6" t="n">
         <v>0.16</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.28</v>
+        <v>10.79</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.61</v>
+        <v>7.32</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.56</v>
+        <v>18.74</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="7">
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.33</v>
+        <v>47.44</v>
       </c>
       <c r="Y7" t="n">
         <v>0.11</v>
@@ -3628,7 +3628,7 @@
         <v>3.81</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CC7" t="n">
         <v>6.75</v>
@@ -3697,7 +3697,7 @@
         <v>1.66</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.2</v>
@@ -3709,7 +3709,7 @@
         <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD7" t="n">
         <v>4.3</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.37</v>
+        <v>45.42</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>62.88</v>
+        <v>63.11</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.12</v>
+        <v>16.11</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>42</v>
+        <v>41.11</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8</v>
+        <v>7.44</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.75</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.390000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BJ8" t="n">
         <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU8" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV8" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY8" t="n">
         <v>3.89</v>
@@ -4028,73 +4028,73 @@
         <v>4.08</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.02</v>
+        <v>4.18</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="CC8" t="n">
-        <v>7.38</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="CD8" t="n">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="CR8" t="n">
         <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="CT8" t="n">
         <v>2.78</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CX8" t="n">
         <v>1.67</v>
@@ -4109,13 +4109,13 @@
         <v>1.78</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
@@ -4124,73 +4124,73 @@
         <v>1.89</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>74.34</v>
+        <v>73.84</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="DL8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="DS8" t="n">
         <v>0.16</v>
       </c>
-      <c r="DM8" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.17</v>
-      </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.94</v>
+        <v>47.21</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.28</v>
+        <v>10.84</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.61</v>
+        <v>7.31</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.28</v>
+        <v>18.84</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="H9" t="n">
-        <v>86.22</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M9" t="n">
-        <v>33.44</v>
+        <v>32</v>
       </c>
       <c r="N9" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.33</v>
+        <v>12.3</v>
       </c>
       <c r="R9" t="n">
-        <v>7.44</v>
+        <v>7.9</v>
       </c>
       <c r="S9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>50.89</v>
+        <v>49.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.33</v>
+        <v>10.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.78</v>
+        <v>18.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AF9" t="n">
         <v>0.22</v>
@@ -4371,70 +4371,70 @@
         <v>2.22</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.17</v>
+        <v>9.26</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL9" t="n">
         <v>0.89</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU9" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV9" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.72</v>
+        <v>4.17</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.41</v>
+        <v>4.97</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
       <c r="CC9" t="n">
         <v>5.73</v>
@@ -4443,43 +4443,43 @@
         <v>6.16</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK9" t="n">
         <v>1.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN9" t="n">
         <v>1.77</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.46</v>
@@ -4521,46 +4521,46 @@
         <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="DH9" t="n">
-        <v>87.44</v>
+        <v>86.16</v>
       </c>
       <c r="DI9" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.16</v>
+        <v>3.37</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.33</v>
+        <v>34.47</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.83</v>
+        <v>13.68</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.94</v>
+        <v>11.95</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.5</v>
+        <v>49.68</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="DX9" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.06</v>
+        <v>7</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.28</v>
+        <v>20.05</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>89.78</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>44.44</v>
+        <v>43.8</v>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>17.78</v>
+        <v>16.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.22</v>
+        <v>16.6</v>
       </c>
       <c r="R10" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>49.56</v>
+        <v>50.7</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.11</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.56</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.44</v>
+        <v>10.26</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.33</v>
+        <v>4.21</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="BR10" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CC10" t="n">
         <v>2.76</v>
@@ -4852,46 +4852,46 @@
         <v>2.83</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI10" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL10" t="n">
         <v>1.8</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO10" t="n">
         <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4900,7 +4900,7 @@
         <v>1.9</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX10" t="n">
         <v>1.56</v>
@@ -4912,58 +4912,58 @@
         <v>2.36</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="DE10" t="n">
         <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.44</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.28</v>
+        <v>5.16</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM10" t="n">
-        <v>48.28</v>
+        <v>47.74</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="DP10" t="n">
-        <v>18.39</v>
+        <v>17.89</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.27</v>
+        <v>16.47</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.78</v>
+        <v>7.68</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.62</v>
+        <v>51.16</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.22</v>
+        <v>13</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.84</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.89</v>
+        <v>20.74</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>102.11</v>
+        <v>101.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>44.11</v>
+        <v>42.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>12.78</v>
+        <v>12.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.22</v>
+        <v>12.9</v>
       </c>
       <c r="R11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51</v>
+        <v>51.4</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.44</v>
+        <v>20.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5177,70 +5177,70 @@
         <v>2.22</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.109999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="BJ11" t="n">
         <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.83</v>
+        <v>4.63</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BV11" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BX11" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="CC11" t="n">
         <v>5.93</v>
@@ -5261,31 +5261,31 @@
         <v>1.42</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK11" t="n">
         <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO11" t="n">
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
@@ -5300,10 +5300,10 @@
         <v>1.45</v>
       </c>
       <c r="CV11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
@@ -5324,46 +5324,46 @@
         <v>1.98</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DH11" t="n">
-        <v>98.39</v>
+        <v>98.11</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.78</v>
+        <v>45.05</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.28</v>
+        <v>13.05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.56</v>
+        <v>12.9</v>
       </c>
       <c r="DR11" t="n">
         <v>8.109999999999999</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.94</v>
+        <v>51.16</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.34</v>
+        <v>12.53</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.94</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.44</v>
+        <v>20.26</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="12">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
@@ -5824,49 +5824,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="H13" t="n">
-        <v>71.5</v>
+        <v>70</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K13" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M13" t="n">
-        <v>31.5</v>
+        <v>29.89</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P13" t="n">
-        <v>14.38</v>
+        <v>14.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.12</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.62</v>
+        <v>51.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.38</v>
+        <v>9.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.62</v>
+        <v>6.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.5</v>
+        <v>20.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AF13" t="n">
         <v>0.3</v>
@@ -5983,70 +5983,70 @@
         <v>2.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.83</v>
+        <v>7.95</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.16</v>
+        <v>4.02</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.43</v>
+        <v>4.28</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="CC13" t="n">
         <v>4.7</v>
@@ -6055,13 +6055,13 @@
         <v>4.94</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
@@ -6070,28 +6070,28 @@
         <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="CR13" t="n">
         <v>1.49</v>
@@ -6106,73 +6106,73 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>76.28</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.94</v>
+        <v>32.11</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.17</v>
+        <v>14.1</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.16</v>
+        <v>15.53</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.390000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.16</v>
+        <v>50.1</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.779999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY13" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.33</v>
+        <v>20.42</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="14">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.89</v>
+        <v>63.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN15" t="n">
-        <v>29.33</v>
+        <v>29.9</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15.11</v>
+        <v>14.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.56</v>
+        <v>45.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.33</v>
+        <v>16.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.94</v>
+        <v>10.89</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT15" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY15" t="n">
         <v>4.22</v>
@@ -6849,16 +6849,16 @@
         <v>4.39</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.58</v>
+        <v>6.24</v>
       </c>
       <c r="CD15" t="n">
-        <v>8.56</v>
+        <v>8.1</v>
       </c>
       <c r="CE15" t="n">
         <v>1.39</v>
@@ -6873,22 +6873,22 @@
         <v>1.41</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CO15" t="n">
         <v>1.3</v>
@@ -6897,121 +6897,121 @@
         <v>2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CU15" t="n">
         <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX15" t="n">
         <v>1.58</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.34</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
         <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.78</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM15" t="n">
-        <v>26.5</v>
+        <v>26.95</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.77</v>
+        <v>13.37</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.06</v>
+        <v>15.21</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.34</v>
+        <v>10.26</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.34</v>
+        <v>45.74</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.78</v>
+        <v>3.89</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.38</v>
+        <v>16.37</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.2</v>
@@ -7111,139 +7111,139 @@
         <v>3.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>84</v>
+        <v>84.67</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AL16" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN16" t="n">
-        <v>34.5</v>
+        <v>33.89</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.88</v>
+        <v>13.89</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.25</v>
+        <v>8.56</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.5</v>
+        <v>45.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>12</v>
+        <v>11.56</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.119999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.88</v>
+        <v>3.44</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.25</v>
+        <v>18.78</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.5</v>
+        <v>8.58</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.67</v>
+        <v>3.84</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS16" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY16" t="n">
         <v>3.11</v>
@@ -7252,28 +7252,28 @@
         <v>3.24</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.56</v>
+        <v>4.36</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.01</v>
+        <v>4.76</v>
       </c>
       <c r="CE16" t="n">
         <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI16" t="n">
         <v>1.62</v>
@@ -7282,25 +7282,25 @@
         <v>2.2</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7321,100 +7321,100 @@
         <v>2.36</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB16" t="n">
         <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.44</v>
+        <v>90.42</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.56</v>
+        <v>38.05</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.22</v>
+        <v>15.11</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.5</v>
+        <v>7.69</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.33</v>
+        <v>47.53</v>
       </c>
       <c r="DW16" t="n">
         <v>0.16</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.11</v>
+        <v>11.9</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.550000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.56</v>
+        <v>3.37</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.39</v>
+        <v>21.05</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>114</v>
+        <v>114.78</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K17" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="L17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M17" t="n">
-        <v>53.5</v>
+        <v>54.56</v>
       </c>
       <c r="N17" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="P17" t="n">
-        <v>10.38</v>
+        <v>10.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.25</v>
+        <v>11.11</v>
       </c>
       <c r="R17" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="S17" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="V17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>62.25</v>
+        <v>62.89</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.5</v>
+        <v>12.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.12</v>
+        <v>7.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.38</v>
+        <v>4.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>22.88</v>
+        <v>21.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,70 +7595,70 @@
         <v>2.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN17" t="n">
         <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="CC17" t="n">
         <v>2.62</v>
@@ -7673,10 +7673,10 @@
         <v>2.72</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI17" t="n">
         <v>1.79</v>
@@ -7685,31 +7685,31 @@
         <v>1.95</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL17" t="n">
         <v>2.12</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CT17" t="n">
         <v>3.1</v>
@@ -7718,106 +7718,106 @@
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW17" t="n">
         <v>2.04</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DH17" t="n">
-        <v>110.61</v>
+        <v>111.16</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.33</v>
+        <v>55.74</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.61</v>
+        <v>12.47</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.5</v>
+        <v>5.32</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>64.28</v>
+        <v>64.47</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.06</v>
+        <v>13.26</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.050000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.72</v>
+        <v>21.26</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0.11</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>106.11</v>
+        <v>108.3</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="AM18" t="n">
         <v>1</v>
       </c>
       <c r="AN18" t="n">
-        <v>53.67</v>
+        <v>54.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.22</v>
+        <v>13.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.89</v>
+        <v>15.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.56</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>64.33</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>17.44</v>
+        <v>17.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.67</v>
+        <v>6.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>15.78</v>
+        <v>15.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.720000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV18" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX18" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY18" t="n">
         <v>1.27</v>
@@ -8058,16 +8058,16 @@
         <v>1.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="CB18" t="n">
-        <v>7.17</v>
+        <v>7.12</v>
       </c>
       <c r="CC18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CE18" t="n">
         <v>1.21</v>
@@ -8076,10 +8076,10 @@
         <v>2.25</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI18" t="n">
         <v>1.72</v>
@@ -8094,19 +8094,19 @@
         <v>1.94</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CN18" t="n">
         <v>1.73</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CP18" t="n">
         <v>1.65</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
@@ -8121,10 +8121,10 @@
         <v>1.61</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CX18" t="n">
         <v>1.61</v>
@@ -8148,46 +8148,46 @@
         <v>2.72</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="DH18" t="n">
-        <v>113.94</v>
+        <v>114.69</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="DK18" t="n">
         <v>6.84</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DM18" t="n">
-        <v>56.78</v>
+        <v>57.11</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.56</v>
+        <v>12.53</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.44</v>
+        <v>13.32</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="DS18" t="n">
         <v>0.16</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.06</v>
+        <v>62.21</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="DX18" t="n">
-        <v>19.06</v>
+        <v>18.84</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.61</v>
+        <v>11.58</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.44</v>
+        <v>7.26</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.67</v>
+        <v>16.58</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8326,133 +8326,133 @@
         <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI19" t="n">
-        <v>99.5</v>
+        <v>98.78</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>45.62</v>
+        <v>44.89</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.12</v>
+        <v>13.78</v>
       </c>
       <c r="AR19" t="n">
-        <v>16.38</v>
+        <v>15.56</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.25</v>
+        <v>7.56</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>51.5</v>
+        <v>50.78</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.38</v>
+        <v>13.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.25</v>
+        <v>10.11</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE19" t="n">
         <v>1.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.06</v>
+        <v>7.95</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS19" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU19" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV19" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="BX19" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY19" t="n">
         <v>3.62</v>
@@ -8464,37 +8464,37 @@
         <v>3.51</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="CE19" t="n">
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK19" t="n">
         <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM19" t="n">
         <v>2.36</v>
@@ -8503,13 +8503,13 @@
         <v>1.84</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
@@ -8524,10 +8524,10 @@
         <v>1.4</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX19" t="n">
         <v>1.58</v>
@@ -8542,88 +8542,88 @@
         <v>1.86</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.56</v>
+        <v>93.53</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.55</v>
+        <v>44.26</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.83</v>
+        <v>15.05</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.45</v>
+        <v>15.11</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.44</v>
+        <v>7.58</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.67</v>
+        <v>49.42</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.609999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.22</v>
+        <v>21.84</v>
       </c>
       <c r="EB19" t="n">
         <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1935,10 +1935,10 @@
         <v>0.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.22</v>
+        <v>7.33</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="BC3" t="n">
         <v>2.89</v>
@@ -1947,7 +1947,7 @@
         <v>19.11</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BF3" t="n">
         <v>2.78</v>
@@ -2160,10 +2160,10 @@
         <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.68</v>
+        <v>5.73</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.53</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45.89</v>
+        <v>45.78</v>
       </c>
       <c r="Y5" t="n">
         <v>0.44</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.32</v>
+        <v>44.26</v>
       </c>
       <c r="DW5" t="n">
         <v>0.26</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.11</v>
@@ -5499,52 +5499,52 @@
         <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>86.22</v>
+        <v>85.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.56</v>
+        <v>38.7</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.78</v>
+        <v>14.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.22</v>
+        <v>6.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,73 +5556,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.22</v>
+        <v>49.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.11</v>
+        <v>12.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.67</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.78</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.83</v>
+        <v>10.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.56</v>
+        <v>4.79</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.28</v>
+        <v>5.26</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY12" t="n">
         <v>3.13</v>
@@ -5640,40 +5640,40 @@
         <v>3.2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.58</v>
+        <v>4.02</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.96</v>
+        <v>4.52</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CH12" t="n">
         <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM12" t="n">
         <v>2.14</v>
@@ -5682,31 +5682,31 @@
         <v>1.71</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX12" t="n">
         <v>1.69</v>
@@ -5721,88 +5721,88 @@
         <v>1.72</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="DE12" t="n">
         <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="DH12" t="n">
-        <v>87.39</v>
+        <v>86.95</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.11</v>
+        <v>5.95</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DM12" t="n">
-        <v>46.56</v>
+        <v>45.27</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.17</v>
+        <v>13.84</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.88</v>
+        <v>14.79</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.66</v>
+        <v>6.89</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.83</v>
+        <v>48.47</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.27</v>
+        <v>14.1</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.890000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="EA12" t="n">
-        <v>22</v>
+        <v>22.16</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="H14" t="n">
-        <v>110.38</v>
+        <v>106.89</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="M14" t="n">
-        <v>52.5</v>
+        <v>50.56</v>
       </c>
       <c r="N14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="V14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>56.25</v>
+        <v>56.44</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="AA14" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.75</v>
+        <v>20.44</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF14" t="n">
         <v>0.1</v>
@@ -6386,49 +6386,49 @@
         <v>2.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.89</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BZ14" t="n">
         <v>1.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.36</v>
+        <v>5.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="CC14" t="n">
         <v>1.58</v>
@@ -6461,10 +6461,10 @@
         <v>1.34</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CH14" t="n">
         <v>1.48</v>
@@ -6473,13 +6473,13 @@
         <v>1.68</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM14" t="n">
         <v>2.24</v>
@@ -6491,19 +6491,19 @@
         <v>1.24</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU14" t="n">
         <v>1.5</v>
@@ -6512,103 +6512,103 @@
         <v>1.72</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY14" t="n">
         <v>2.03</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA14" t="n">
         <v>1.8</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="DH14" t="n">
-        <v>104.17</v>
+        <v>102.84</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>5.32</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.5</v>
+        <v>49.69</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.67</v>
+        <v>13.63</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.94</v>
+        <v>11.68</v>
       </c>
       <c r="DR14" t="n">
         <v>5.89</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.17</v>
+        <v>56.26</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.44</v>
+        <v>14.42</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.17</v>
+        <v>19.1</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="15">
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.1</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.74</v>
+        <v>45.79</v>
       </c>
       <c r="DW15" t="n">
         <v>0.21</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,139 +5902,139 @@
         <v>2.67</v>
       </c>
       <c r="AF13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>79.27</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>0.3</v>
       </c>
-      <c r="AG13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="BK13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.2</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BM13" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.89</v>
+        <v>4.05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY13" t="n">
         <v>4.02</v>
@@ -6043,13 +6043,13 @@
         <v>4.28</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="CD13" t="n">
         <v>4.94</v>
@@ -6061,7 +6061,7 @@
         <v>3.18</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
@@ -6076,7 +6076,7 @@
         <v>1.74</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CM13" t="n">
         <v>2.02</v>
@@ -6088,19 +6088,19 @@
         <v>1.4</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS13" t="n">
         <v>3.23</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
@@ -6115,7 +6115,7 @@
         <v>1.78</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.04</v>
@@ -6133,46 +6133,46 @@
         <v>4.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>75.31999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.11</v>
+        <v>31.85</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.1</v>
+        <v>13.95</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.53</v>
+        <v>15.65</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.26</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="DW13" t="n">
         <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.42</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.42</v>
+        <v>20.7</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -8242,82 +8242,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="n">
-        <v>88.8</v>
+        <v>88.91</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M19" t="n">
-        <v>43.7</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="P19" t="n">
-        <v>16.2</v>
+        <v>16.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.7</v>
+        <v>14.27</v>
       </c>
       <c r="R19" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>48.2</v>
+        <v>47.82</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>12.91</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.8</v>
+        <v>19.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>1.89</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="BH19" t="n">
-        <v>7.95</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS19" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BT19" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV19" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX19" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.62</v>
+        <v>3.46</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.09</v>
+        <v>3.89</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CC19" t="n">
         <v>3.17</v>
@@ -8476,31 +8476,31 @@
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.96</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
@@ -8509,19 +8509,19 @@
         <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV19" t="n">
         <v>1.86</v>
@@ -8530,100 +8530,100 @@
         <v>2.02</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DB19" t="n">
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.53</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.26</v>
+        <v>43.85</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.05</v>
+        <v>15.2</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.11</v>
+        <v>14.85</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.58</v>
+        <v>7.55</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.42</v>
+        <v>49.15</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.16</v>
+        <v>13.1</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.58</v>
+        <v>9.6</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.84</v>
+        <v>21.3</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="H3" t="n">
-        <v>77.5</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>42.7</v>
+        <v>44.09</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>13.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.3</v>
+        <v>14.55</v>
       </c>
       <c r="R3" t="n">
-        <v>8.1</v>
+        <v>7.64</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>10.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.9</v>
+        <v>6.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.6</v>
+        <v>20.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.78</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.57</v>
+        <v>4.34</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.64</v>
+        <v>4.39</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="CC3" t="n">
         <v>5.44</v>
@@ -2025,31 +2025,31 @@
         <v>6.52</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CM3" t="n">
         <v>2.06</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>2.07</v>
       </c>
       <c r="CN3" t="n">
         <v>1.64</v>
@@ -2058,124 +2058,124 @@
         <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DG3" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="DH3" t="n">
-        <v>77.26000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="DI3" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.16</v>
+        <v>3.45</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.42</v>
+        <v>37.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.95</v>
+        <v>13.15</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.74</v>
+        <v>13.9</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.63</v>
+        <v>7.4</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.26</v>
+        <v>43.95</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.37</v>
+        <v>19.75</v>
       </c>
       <c r="EB3" t="n">
         <v>1.1</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -2275,139 +2275,139 @@
         <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>112.56</v>
+        <v>115.4</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.22</v>
+        <v>6</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.22</v>
+        <v>60.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BF4" t="n">
         <v>2</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>18.11</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BG4" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.74</v>
+        <v>9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.16</v>
+        <v>4.35</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.58</v>
+        <v>4.65</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS4" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY4" t="n">
         <v>1.36</v>
@@ -2416,34 +2416,34 @@
         <v>1.39</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.66</v>
+        <v>5.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.23</v>
+        <v>6.2</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="CE4" t="n">
         <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI4" t="n">
         <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
@@ -2452,10 +2452,10 @@
         <v>1.93</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
         <v>1.22</v>
@@ -2470,28 +2470,28 @@
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA4" t="n">
         <v>1.97</v>
@@ -2500,85 +2500,85 @@
         <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="DH4" t="n">
-        <v>116.27</v>
+        <v>117.5</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.84</v>
+        <v>6.2</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.31</v>
+        <v>63.65</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.89</v>
+        <v>11.55</v>
       </c>
       <c r="DQ4" t="n">
-        <v>14.79</v>
+        <v>15</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.42</v>
+        <v>5.8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>58.48</v>
+        <v>59.35</v>
       </c>
       <c r="DW4" t="n">
         <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>16</v>
+        <v>16.35</v>
       </c>
       <c r="DY4" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.53</v>
+        <v>19.35</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,49 +2678,49 @@
         <v>3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AI5" t="n">
-        <v>92.7</v>
+        <v>92.36</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AL5" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>37.1</v>
+        <v>35.91</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.7</v>
+        <v>15.64</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.1</v>
+        <v>11.18</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.9</v>
+        <v>42.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>12.27</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.1</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.5</v>
+        <v>19.73</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.32</v>
+        <v>10.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.47</v>
+        <v>4.65</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.84</v>
+        <v>5.7</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY5" t="n">
         <v>3.73</v>
@@ -2819,70 +2819,70 @@
         <v>4.29</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.87</v>
+        <v>4.14</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.15</v>
+        <v>6.23</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.58</v>
+        <v>7.04</v>
       </c>
       <c r="CE5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="CH5" t="n">
         <v>1.41</v>
       </c>
-      <c r="CF5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.38</v>
-      </c>
       <c r="CI5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="CR5" t="n">
         <v>1.46</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="CT5" t="n">
         <v>2.86</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW5" t="n">
         <v>1.97</v>
@@ -2891,22 +2891,22 @@
         <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.34</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
@@ -2915,73 +2915,73 @@
         <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.26000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.79</v>
+        <v>38.05</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DP5" t="n">
         <v>15.05</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.68</v>
+        <v>11.7</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.050000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.26</v>
+        <v>43.95</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>12</v>
+        <v>11.65</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>7.65</v>
       </c>
       <c r="DZ5" t="n">
         <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.89</v>
+        <v>19.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="H6" t="n">
-        <v>84.44</v>
+        <v>80.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>37.33</v>
+        <v>36.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.22</v>
+        <v>11.5</v>
       </c>
       <c r="R6" t="n">
-        <v>8.779999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41.44</v>
+        <v>39.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.56</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.89</v>
+        <v>7.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.67</v>
+        <v>19.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>2.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.32</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.89</v>
+        <v>3.96</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.02</v>
+        <v>4.09</v>
       </c>
       <c r="CC6" t="n">
         <v>5.74</v>
@@ -3234,61 +3234,61 @@
         <v>5.72</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK6" t="n">
         <v>1.48</v>
       </c>
       <c r="CL6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CN6" t="n">
         <v>1.71</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.66</v>
+        <v>3.61</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CU6" t="n">
         <v>1.41</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CX6" t="n">
         <v>1.61</v>
@@ -3306,85 +3306,85 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DG6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DH6" t="n">
-        <v>81.52</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.95</v>
+        <v>35.7</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.74</v>
+        <v>14.95</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.58</v>
+        <v>11.25</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.16</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.42</v>
+        <v>41.5</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.79</v>
+        <v>10.55</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.32</v>
+        <v>7.2</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.74</v>
+        <v>18.7</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" t="n">
-        <v>63.11</v>
+        <v>63.6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.11</v>
+        <v>16.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.11</v>
+        <v>41.3</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.44</v>
+        <v>7.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>16.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.32</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.89</v>
+        <v>4.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU8" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV8" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>3.89</v>
@@ -4028,169 +4028,169 @@
         <v>4.08</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="CC8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="CD8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI8" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CN8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CV8" t="n">
         <v>1.81</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>1.82</v>
       </c>
       <c r="CW8" t="n">
         <v>2.1</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DH8" t="n">
-        <v>73.84</v>
+        <v>73.55</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>29.37</v>
+        <v>29.1</v>
       </c>
       <c r="DN8" t="n">
         <v>0.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.89</v>
+        <v>15</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.26</v>
+        <v>15.3</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.369999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.21</v>
+        <v>47</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.84</v>
+        <v>10.55</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.31</v>
+        <v>7.1</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.84</v>
+        <v>18.3</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.2</v>
@@ -4290,52 +4290,52 @@
         <v>3.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>88.67</v>
+        <v>87.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>37.22</v>
+        <v>38.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.56</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.11</v>
+        <v>50</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.22</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>21.78</v>
+        <v>21</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.26</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT9" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>4.17</v>
@@ -4431,25 +4431,25 @@
         <v>4.97</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.02</v>
+        <v>3.97</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.73</v>
+        <v>5.43</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.16</v>
+        <v>5.77</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4458,19 +4458,19 @@
         <v>1.83</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO9" t="n">
         <v>1.32</v>
@@ -4488,79 +4488,79 @@
         <v>3.07</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU9" t="n">
         <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF9" t="n">
         <v>2.1</v>
       </c>
-      <c r="DD9" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>2.21</v>
-      </c>
       <c r="DG9" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.16</v>
+        <v>85.7</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.47</v>
+        <v>35.05</v>
       </c>
       <c r="DN9" t="n">
         <v>0.9</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.68</v>
+        <v>13.75</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.95</v>
+        <v>11.9</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.58</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.68</v>
+        <v>49.65</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.05</v>
+        <v>10.45</v>
       </c>
       <c r="DY9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.05</v>
+        <v>19.75</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.3</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>89.11</v>
+        <v>86.7</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>52.11</v>
+        <v>49.2</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19</v>
+        <v>18.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.33</v>
+        <v>16.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.109999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.67</v>
+        <v>1.1</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.67</v>
+        <v>50.9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.44</v>
+        <v>11.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>22.67</v>
+        <v>21.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.26</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="BO10" t="n">
         <v>0.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.16</v>
+        <v>5.05</v>
       </c>
       <c r="BR10" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS10" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT10" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU10" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BY10" t="n">
         <v>2.82</v>
@@ -4834,10 +4834,10 @@
         <v>2.84</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CC10" t="n">
         <v>2.76</v>
@@ -4846,16 +4846,16 @@
         <v>2.79</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CI10" t="n">
         <v>1.82</v>
@@ -4870,31 +4870,31 @@
         <v>1.8</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
         <v>1.9</v>
@@ -4918,52 +4918,52 @@
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DH10" t="n">
-        <v>90.31999999999999</v>
+        <v>89.05</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.16</v>
+        <v>4.95</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM10" t="n">
-        <v>47.74</v>
+        <v>46.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.89</v>
+        <v>17.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.47</v>
+        <v>16.6</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.68</v>
+        <v>7.65</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.16</v>
+        <v>50.8</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>13</v>
+        <v>12.55</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.630000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.37</v>
+        <v>4.15</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.74</v>
+        <v>20.35</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5096,139 +5096,139 @@
         <v>3.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.67</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.44</v>
+        <v>47</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AU11" t="n">
         <v>2</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AV11" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.89</v>
+        <v>50.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.44</v>
+        <v>8.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.44</v>
+        <v>21.2</v>
       </c>
       <c r="BE11" t="n">
         <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.949999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.63</v>
+        <v>4.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BV11" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BW11" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>3.39</v>
@@ -5237,16 +5237,16 @@
         <v>3.42</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.93</v>
+        <v>5.66</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.87</v>
+        <v>5.65</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
@@ -5255,22 +5255,22 @@
         <v>2.78</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CM11" t="n">
         <v>2.12</v>
@@ -5282,10 +5282,10 @@
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
@@ -5306,100 +5306,100 @@
         <v>1.87</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="DE11" t="n">
         <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="DH11" t="n">
-        <v>98.11</v>
+        <v>97.05</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.05</v>
+        <v>44.95</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.05</v>
+        <v>12.95</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.9</v>
+        <v>12.95</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.16</v>
+        <v>50.9</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.53</v>
+        <v>12.45</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.050000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.26</v>
+        <v>20.65</v>
       </c>
       <c r="EB11" t="n">
         <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>88.56</v>
+        <v>86.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="K12" t="n">
-        <v>5.89</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M12" t="n">
-        <v>52.56</v>
+        <v>50.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>13.56</v>
+        <v>14.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.44</v>
+        <v>14.8</v>
       </c>
       <c r="R12" t="n">
-        <v>7.11</v>
+        <v>6.9</v>
       </c>
       <c r="S12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.44</v>
+        <v>48.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.44</v>
+        <v>15.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>11.11</v>
+        <v>10.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.22</v>
+        <v>20.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
         <v>0.2</v>
@@ -5580,70 +5580,70 @@
         <v>3.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.05</v>
+        <v>9.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="BR12" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CC12" t="n">
         <v>4.02</v>
@@ -5658,28 +5658,28 @@
         <v>3.13</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH12" t="n">
         <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CO12" t="n">
         <v>1.39</v>
@@ -5694,28 +5694,28 @@
         <v>1.5</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA12" t="n">
         <v>1.72</v>
@@ -5727,82 +5727,82 @@
         <v>2.29</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.95</v>
+        <v>86</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.27</v>
+        <v>44.75</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.84</v>
+        <v>14.1</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.79</v>
+        <v>14.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.47</v>
+        <v>48.85</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.1</v>
+        <v>14.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.68</v>
+        <v>9.6</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.42</v>
+        <v>4.65</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.16</v>
+        <v>21.8</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="13">
@@ -5911,7 +5911,7 @@
         <v>1.27</v>
       </c>
       <c r="AI13" t="n">
-        <v>79.27</v>
+        <v>79.55</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>0.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>33.45</v>
+        <v>33.55</v>
       </c>
       <c r="AO13" t="n">
         <v>0.55</v>
@@ -5935,10 +5935,10 @@
         <v>2.09</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.73</v>
+        <v>13.82</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.18</v>
+        <v>16.27</v>
       </c>
       <c r="AS13" t="n">
         <v>9.18</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.64</v>
+        <v>49.73</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.09</v>
@@ -6052,7 +6052,7 @@
         <v>4.67</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.94</v>
+        <v>4.91</v>
       </c>
       <c r="CE13" t="n">
         <v>1.47</v>
@@ -6094,22 +6094,22 @@
         <v>4.24</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS13" t="n">
         <v>3.23</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX13" t="n">
         <v>1.78</v>
@@ -6127,10 +6127,10 @@
         <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="DE13" t="n">
         <v>0.15</v>
@@ -6142,7 +6142,7 @@
         <v>1.95</v>
       </c>
       <c r="DH13" t="n">
-        <v>75.09999999999999</v>
+        <v>75.25</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
@@ -6157,7 +6157,7 @@
         <v>0.35</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.85</v>
+        <v>31.9</v>
       </c>
       <c r="DN13" t="n">
         <v>0.9</v>
@@ -6166,10 +6166,10 @@
         <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.95</v>
+        <v>14</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.65</v>
+        <v>15.7</v>
       </c>
       <c r="DR13" t="n">
         <v>8.550000000000001</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.4</v>
+        <v>50.45</v>
       </c>
       <c r="DW13" t="n">
         <v>0.1</v>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>71.67</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M15" t="n">
-        <v>23.67</v>
+        <v>24.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>12.44</v>
+        <v>12.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.11</v>
+        <v>15.1</v>
       </c>
       <c r="R15" t="n">
-        <v>9.67</v>
+        <v>9.6</v>
       </c>
       <c r="S15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.11</v>
+        <v>46.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.22</v>
+        <v>5.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.44</v>
+        <v>16.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6792,67 +6792,67 @@
         <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.89</v>
+        <v>10.85</v>
       </c>
       <c r="BI15" t="n">
         <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="BQ15" t="n">
         <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS15" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT15" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU15" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.22</v>
+        <v>4.07</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="CC15" t="n">
         <v>6.24</v>
@@ -6864,7 +6864,7 @@
         <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG15" t="n">
         <v>2.88</v>
@@ -6873,22 +6873,22 @@
         <v>1.41</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK15" t="n">
         <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO15" t="n">
         <v>1.3</v>
@@ -6897,34 +6897,34 @@
         <v>2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS15" t="n">
         <v>2.94</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CU15" t="n">
         <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA15" t="n">
         <v>1.9</v>
@@ -6942,43 +6942,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.20999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="DL15" t="n">
         <v>0.1</v>
       </c>
       <c r="DM15" t="n">
-        <v>26.95</v>
+        <v>27.15</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.37</v>
+        <v>13.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.21</v>
+        <v>15.2</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.26</v>
+        <v>10.2</v>
       </c>
       <c r="DS15" t="n">
         <v>0.1</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.79</v>
+        <v>46.05</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.31</v>
+        <v>9.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.42</v>
+        <v>5.55</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.37</v>
+        <v>16.3</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="H16" t="n">
-        <v>95.59999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M16" t="n">
-        <v>41.8</v>
+        <v>41.27</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="P16" t="n">
-        <v>15.8</v>
+        <v>15.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="R16" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.2</v>
+        <v>12.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>23.1</v>
+        <v>22.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AF16" t="n">
         <v>0.22</v>
@@ -7192,70 +7192,70 @@
         <v>2.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.58</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BO16" t="n">
         <v>0.95</v>
       </c>
-      <c r="BO16" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BP16" t="n">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="BR16" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS16" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BX16" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC16" t="n">
         <v>4.36</v>
@@ -7267,40 +7267,40 @@
         <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="CG16" t="n">
         <v>2.44</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN16" t="n">
         <v>1.61</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7315,10 +7315,10 @@
         <v>1.34</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CX16" t="n">
         <v>1.82</v>
@@ -7336,85 +7336,85 @@
         <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.32</v>
+        <v>5.26</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.42</v>
+        <v>89.55</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.05</v>
+        <v>37.95</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DP16" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="DQ16" t="n">
         <v>14.9</v>
       </c>
-      <c r="DQ16" t="n">
-        <v>15.11</v>
-      </c>
       <c r="DR16" t="n">
-        <v>7.69</v>
+        <v>7.65</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.53</v>
+        <v>47.85</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.529999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.05</v>
+        <v>20.8</v>
       </c>
       <c r="EB16" t="n">
         <v>1.27</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>121.78</v>
+        <v>121.3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="K18" t="n">
-        <v>5.89</v>
+        <v>6.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="M18" t="n">
-        <v>59.89</v>
+        <v>60.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>11.89</v>
+        <v>11.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="R18" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>59.78</v>
+        <v>60</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.67</v>
+        <v>20.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.44</v>
+        <v>12.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>17.56</v>
+        <v>18.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.789999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.79</v>
+        <v>4.95</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT18" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.14</v>
+        <v>6.26</v>
       </c>
       <c r="CB18" t="n">
-        <v>7.12</v>
+        <v>7.23</v>
       </c>
       <c r="CC18" t="n">
         <v>1.48</v>
@@ -8073,13 +8073,13 @@
         <v>1.21</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CI18" t="n">
         <v>1.72</v>
@@ -8088,139 +8088,139 @@
         <v>2.12</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CT18" t="n">
         <v>3.15</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CV18" t="n">
         <v>1.74</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CX18" t="n">
         <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.27</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DE18" t="n">
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="DH18" t="n">
-        <v>114.69</v>
+        <v>114.8</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="DK18" t="n">
-        <v>6.84</v>
+        <v>7.05</v>
       </c>
       <c r="DL18" t="n">
         <v>0.95</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.11</v>
+        <v>57.75</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.53</v>
+        <v>12.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.32</v>
+        <v>13.4</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.21</v>
+        <v>62.2</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>18.84</v>
+        <v>18.7</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.58</v>
+        <v>11.45</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.58</v>
+        <v>16.9</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -8242,19 +8242,19 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="G19" t="n">
         <v>2.36</v>
       </c>
       <c r="H19" t="n">
-        <v>88.91</v>
+        <v>89</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="K19" t="n">
         <v>4.64</v>
@@ -8272,10 +8272,10 @@
         <v>2.18</v>
       </c>
       <c r="P19" t="n">
-        <v>16.36</v>
+        <v>16.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.27</v>
+        <v>14.36</v>
       </c>
       <c r="R19" t="n">
         <v>7.55</v>
@@ -8296,28 +8296,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>47.82</v>
+        <v>47.73</v>
       </c>
       <c r="Y19" t="n">
         <v>0.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.91</v>
+        <v>13.09</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.18</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB19" t="n">
         <v>3.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.91</v>
+        <v>20</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
         <v>3.46</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CA19" t="n">
         <v>3.49</v>
@@ -8515,13 +8515,13 @@
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV19" t="n">
         <v>1.86</v>
@@ -8545,28 +8545,28 @@
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="DG19" t="n">
         <v>2.25</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.34999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="DK19" t="n">
         <v>4.35</v>
@@ -8584,10 +8584,10 @@
         <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.2</v>
+        <v>15.25</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.85</v>
+        <v>14.9</v>
       </c>
       <c r="DR19" t="n">
         <v>7.55</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.15</v>
+        <v>49.1</v>
       </c>
       <c r="DW19" t="n">
         <v>0.2</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ19" t="n">
         <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.3</v>
+        <v>21.35</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>83.90000000000001</v>
+        <v>83.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.2</v>
       </c>
-      <c r="P2" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.789999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU2" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.43</v>
+        <v>4.89</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.5</v>
+        <v>5.14</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.82</v>
+        <v>4.85</v>
       </c>
       <c r="CC2" t="n">
         <v>9.609999999999999</v>
@@ -1625,10 +1625,10 @@
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
@@ -1637,10 +1637,10 @@
         <v>1.71</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL2" t="n">
         <v>2.1</v>
@@ -1655,10 +1655,10 @@
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="CR2" t="n">
         <v>1.47</v>
@@ -1688,58 +1688,58 @@
         <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
         <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="DE2" t="n">
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.73999999999999</v>
+        <v>84.25</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.58</v>
+        <v>35.2</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.58</v>
+        <v>14</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.42</v>
+        <v>12.1</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.42</v>
+        <v>9.15</v>
       </c>
       <c r="DS2" t="n">
         <v>0.1</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.68</v>
+        <v>42.2</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.21</v>
+        <v>11.05</v>
       </c>
       <c r="DY2" t="n">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.79</v>
+        <v>21.75</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47</v>
+        <v>47.09</v>
       </c>
       <c r="Y3" t="n">
         <v>0.09</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.95</v>
+        <v>44</v>
       </c>
       <c r="DW3" t="n">
         <v>0.15</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.1</v>
@@ -2419,7 +2419,7 @@
         <v>5.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="CC4" t="n">
         <v>1.64</v>
@@ -2470,13 +2470,13 @@
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV4" t="n">
         <v>1.72</v>
@@ -2488,10 +2488,10 @@
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA4" t="n">
         <v>1.97</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59.35</v>
+        <v>59.4</v>
       </c>
       <c r="DW4" t="n">
         <v>0.1</v>
@@ -2750,7 +2750,7 @@
         <v>3.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.73</v>
+        <v>19.82</v>
       </c>
       <c r="BE5" t="n">
         <v>1.31</v>
@@ -2975,7 +2975,7 @@
         <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.5</v>
+        <v>19.55</v>
       </c>
       <c r="EB5" t="n">
         <v>1.29</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="Y6" t="n">
         <v>0.1</v>
@@ -3219,13 +3219,13 @@
         <v>5.06</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="CA6" t="n">
         <v>3.96</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="CC6" t="n">
         <v>5.74</v>
@@ -3273,13 +3273,13 @@
         <v>3.61</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CU6" t="n">
         <v>1.41</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.5</v>
+        <v>41.45</v>
       </c>
       <c r="DW6" t="n">
         <v>0.15</v>
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>81.11</v>
+        <v>80</v>
       </c>
       <c r="I7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>34.89</v>
+        <v>33.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="P7" t="n">
-        <v>16.11</v>
+        <v>15.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="R7" t="n">
-        <v>7.56</v>
+        <v>8.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>47.44</v>
+        <v>45.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.67</v>
+        <v>7.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.11</v>
+        <v>18.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AF7" t="n">
         <v>0.1</v>
@@ -3568,67 +3568,67 @@
         <v>3.05</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.58</v>
+        <v>9.6</v>
       </c>
       <c r="BI7" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM7" t="n">
         <v>0.95</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.47</v>
+        <v>4.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.44</v>
+        <v>4.14</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.65</v>
+        <v>4.58</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.81</v>
+        <v>3.91</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.09</v>
+        <v>4.18</v>
       </c>
       <c r="CC7" t="n">
         <v>6.75</v>
@@ -3637,22 +3637,22 @@
         <v>7.61</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CH7" t="n">
         <v>1.35</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CK7" t="n">
         <v>1.6</v>
@@ -3661,58 +3661,58 @@
         <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CU7" t="n">
         <v>1.42</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY7" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA7" t="n">
         <v>1.76</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="DE7" t="n">
         <v>0.1</v>
@@ -3721,40 +3721,40 @@
         <v>2.05</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DH7" t="n">
-        <v>75.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.26</v>
+        <v>30.8</v>
       </c>
       <c r="DN7" t="n">
         <v>1.1</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.58</v>
+        <v>15.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.47</v>
+        <v>14.45</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.789999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="DS7" t="n">
         <v>0.05</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.42</v>
+        <v>44.75</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.58</v>
+        <v>8.4</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.68</v>
+        <v>5.55</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="EA7" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="EC7" t="n">
         <v>3.05</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47</v>
+        <v>46.95</v>
       </c>
       <c r="DW8" t="n">
         <v>0.15</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6305,130 +6305,130 @@
         <v>2.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="AI14" t="n">
-        <v>99.2</v>
+        <v>102.09</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>48.9</v>
+        <v>50.73</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.6</v>
+        <v>14.55</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.3</v>
+        <v>13.36</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.5</v>
+        <v>6.18</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.1</v>
+        <v>57.18</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.4</v>
+        <v>14.45</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.9</v>
+        <v>18.45</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.210000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT14" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU14" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="n">
         <v>1.34</v>
@@ -6446,16 +6446,16 @@
         <v>1.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CE14" t="n">
         <v>1.34</v>
@@ -6467,13 +6467,13 @@
         <v>3.11</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CK14" t="n">
         <v>1.61</v>
@@ -6482,10 +6482,10 @@
         <v>2.12</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO14" t="n">
         <v>1.24</v>
@@ -6494,10 +6494,10 @@
         <v>1.82</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
         <v>2.74</v>
@@ -6509,106 +6509,106 @@
         <v>1.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CX14" t="n">
         <v>1.63</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB14" t="n">
         <v>1.28</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="DE14" t="n">
         <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.84</v>
+        <v>104.25</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.32</v>
+        <v>5.55</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.69</v>
+        <v>50.65</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.63</v>
+        <v>13.65</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.68</v>
+        <v>11.8</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.89</v>
+        <v>5.75</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.26</v>
+        <v>56.85</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.42</v>
+        <v>14.45</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.84</v>
+        <v>8.85</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.58</v>
+        <v>5.6</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.1</v>
+        <v>19.35</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.22</v>
@@ -7514,139 +7514,139 @@
         <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AI17" t="n">
-        <v>107.9</v>
+        <v>107.91</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.8</v>
+        <v>56.45</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.7</v>
+        <v>11.18</v>
       </c>
       <c r="AR17" t="n">
-        <v>13.7</v>
+        <v>12.73</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>65.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.3</v>
+        <v>13.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.5</v>
+        <v>5.73</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.8</v>
+        <v>20.64</v>
       </c>
       <c r="BE17" t="n">
         <v>1.55</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.369999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY17" t="n">
         <v>1.64</v>
@@ -7655,16 +7655,16 @@
         <v>1.71</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="CC17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CD17" t="n">
         <v>2.62</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>2.75</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
@@ -7673,16 +7673,16 @@
         <v>2.72</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
         <v>1.79</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
@@ -7691,19 +7691,19 @@
         <v>2.12</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7721,103 +7721,103 @@
         <v>1.84</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB17" t="n">
         <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DH17" t="n">
-        <v>111.16</v>
+        <v>111</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.74</v>
+        <v>55.6</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DP17" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.47</v>
+        <v>12</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>64.47</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="DW17" t="n">
         <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.26</v>
+        <v>13.1</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.16</v>
+        <v>7.85</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.26</v>
+        <v>21.15</v>
       </c>
       <c r="EB17" t="n">
         <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -2338,13 +2338,13 @@
         <v>0.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD4" t="n">
         <v>19.8</v>
@@ -2563,13 +2563,13 @@
         <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.35</v>
+        <v>16.4</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="EA4" t="n">
         <v>19.35</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,127 +3084,127 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>78.90000000000001</v>
+        <v>77.64</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.7</v>
+        <v>33.18</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16.3</v>
+        <v>15.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>10.73</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>8.27</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>43.3</v>
+        <v>42.27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.1</v>
+        <v>9.73</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>6.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.9</v>
+        <v>18.09</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS6" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT6" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
         <v>5.06</v>
@@ -3222,40 +3222,40 @@
         <v>5.83</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.72</v>
+        <v>5.63</v>
       </c>
       <c r="CE6" t="n">
         <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CL6" t="n">
         <v>2.01</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>1.99</v>
       </c>
       <c r="CM6" t="n">
         <v>2.19</v>
@@ -3267,28 +3267,28 @@
         <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX6" t="n">
         <v>1.61</v>
@@ -3306,85 +3306,85 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DH6" t="n">
-        <v>79.84999999999999</v>
+        <v>79.14</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.7</v>
+        <v>34.86</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.95</v>
+        <v>14.62</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.25</v>
+        <v>11.1</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.45</v>
+        <v>41</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.55</v>
+        <v>10.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.7</v>
+        <v>18.76</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="7">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="H8" t="n">
-        <v>83.5</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>33.3</v>
+        <v>33.27</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>13.8</v>
+        <v>13.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.4</v>
+        <v>15.73</v>
       </c>
       <c r="R8" t="n">
-        <v>7.7</v>
+        <v>7.82</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.7</v>
+        <v>52</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.9</v>
+        <v>13.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.5</v>
+        <v>20.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,70 +3968,70 @@
         <v>2.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BP8" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BR8" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT8" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU8" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.08</v>
+        <v>4.13</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="CC8" t="n">
         <v>8.01</v>
@@ -4040,13 +4040,13 @@
         <v>9.220000000000001</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4064,19 +4064,19 @@
         <v>2.15</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="CR8" t="n">
         <v>1.48</v>
@@ -4091,106 +4091,106 @@
         <v>1.43</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CX8" t="n">
         <v>1.69</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.91</v>
+        <v>4.01</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DH8" t="n">
-        <v>73.55</v>
+        <v>74.19</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DM8" t="n">
-        <v>29.1</v>
+        <v>29.28</v>
       </c>
       <c r="DN8" t="n">
         <v>0.9</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="DP8" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="DQ8" t="n">
         <v>15</v>
       </c>
-      <c r="DQ8" t="n">
-        <v>15.3</v>
-      </c>
       <c r="DR8" t="n">
-        <v>8.25</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.95</v>
+        <v>46.86</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.55</v>
+        <v>10.62</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.3</v>
+        <v>18.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="H9" t="n">
-        <v>83.90000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M9" t="n">
-        <v>32</v>
+        <v>31.36</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>14.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.3</v>
+        <v>12.55</v>
       </c>
       <c r="R9" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49.3</v>
+        <v>49.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.4</v>
+        <v>10.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.5</v>
+        <v>19.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AF9" t="n">
         <v>0.2</v>
@@ -4371,70 +4371,70 @@
         <v>2.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.97</v>
+        <v>4.77</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC9" t="n">
         <v>5.43</v>
@@ -4443,28 +4443,28 @@
         <v>5.77</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.93</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM9" t="n">
         <v>2.27</v>
@@ -4479,13 +4479,13 @@
         <v>2.01</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CR9" t="n">
         <v>1.46</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CT9" t="n">
         <v>2.84</v>
@@ -4497,13 +4497,13 @@
         <v>1.92</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.3</v>
@@ -4512,55 +4512,55 @@
         <v>1.81</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.7</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="DK9" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.05</v>
+        <v>34.57</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.9</v>
+        <v>12.05</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.449999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.65</v>
+        <v>49.71</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.2</v>
+        <v>7.05</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.75</v>
+        <v>20.09</v>
       </c>
       <c r="EB9" t="n">
         <v>1.14</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="H11" t="n">
-        <v>101.2</v>
+        <v>108.09</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M11" t="n">
-        <v>42.9</v>
+        <v>44.73</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="P11" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.9</v>
+        <v>12.45</v>
       </c>
       <c r="R11" t="n">
-        <v>9.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.4</v>
+        <v>52.91</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.4</v>
+        <v>12.64</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.7</v>
+        <v>7.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.1</v>
+        <v>20.82</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5177,64 +5177,64 @@
         <v>2.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="BH11" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BW11" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.39</v>
+        <v>3.23</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="CA11" t="n">
         <v>3.88</v>
@@ -5258,19 +5258,19 @@
         <v>2.86</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK11" t="n">
         <v>1.52</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM11" t="n">
         <v>2.12</v>
@@ -5282,19 +5282,19 @@
         <v>1.3</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CR11" t="n">
         <v>1.41</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU11" t="n">
         <v>1.45</v>
@@ -5303,7 +5303,7 @@
         <v>2.02</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX11" t="n">
         <v>1.63</v>
@@ -5321,85 +5321,85 @@
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>97.05</v>
+        <v>100.86</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.95</v>
+        <v>45.81</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.95</v>
+        <v>12.71</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.95</v>
+        <v>12.71</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.4</v>
+        <v>8.15</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.9</v>
+        <v>51.71</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.45</v>
+        <v>12.57</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.65</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.1</v>
@@ -5499,139 +5499,139 @@
         <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AI12" t="n">
-        <v>85.5</v>
+        <v>89</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AL12" t="n">
         <v>6</v>
       </c>
       <c r="AM12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BN12" t="n">
         <v>1</v>
       </c>
-      <c r="AN12" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0.95</v>
-      </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT12" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV12" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY12" t="n">
         <v>3.1</v>
@@ -5640,28 +5640,28 @@
         <v>3.16</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.02</v>
+        <v>3.84</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.52</v>
+        <v>4.31</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI12" t="n">
         <v>1.71</v>
@@ -5673,22 +5673,22 @@
         <v>1.64</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="CR12" t="n">
         <v>1.5</v>
@@ -5697,7 +5697,7 @@
         <v>3.17</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CU12" t="n">
         <v>1.38</v>
@@ -5721,88 +5721,88 @@
         <v>1.72</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="DH12" t="n">
-        <v>86</v>
+        <v>87.81</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>44.75</v>
+        <v>45.95</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.1</v>
+        <v>14.19</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.5</v>
+        <v>14.62</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.8</v>
+        <v>6.57</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.85</v>
+        <v>49.28</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.25</v>
+        <v>14.29</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.6</v>
+        <v>9.67</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.8</v>
+        <v>21.95</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="13">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
@@ -5824,49 +5824,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>29.89</v>
+        <v>28.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="P13" t="n">
-        <v>14.22</v>
+        <v>14.6</v>
       </c>
       <c r="Q13" t="n">
         <v>15</v>
       </c>
       <c r="R13" t="n">
-        <v>7.78</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.33</v>
+        <v>50.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.56</v>
+        <v>8.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.11</v>
+        <v>5.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.67</v>
+        <v>20.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AF13" t="n">
         <v>0.27</v>
@@ -5983,70 +5983,70 @@
         <v>2.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.050000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BP13" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT13" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CC13" t="n">
         <v>4.67</v>
@@ -6058,13 +6058,13 @@
         <v>1.47</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI13" t="n">
         <v>1.74</v>
@@ -6076,40 +6076,40 @@
         <v>1.74</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CM13" t="n">
         <v>2.02</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO13" t="n">
         <v>1.4</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS13" t="n">
         <v>3.23</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CU13" t="n">
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX13" t="n">
         <v>1.78</v>
@@ -6124,55 +6124,55 @@
         <v>1.63</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DH13" t="n">
-        <v>75.25</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.9</v>
+        <v>31.15</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="DO13" t="n">
         <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>14</v>
+        <v>14.19</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.7</v>
+        <v>15.67</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.550000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.45</v>
+        <v>50.05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.449999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.95</v>
+        <v>5.76</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.7</v>
+        <v>20.43</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="14">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.18</v>
@@ -7111,139 +7111,139 @@
         <v>3.45</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AI16" t="n">
-        <v>84.67</v>
+        <v>86.2</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>33.89</v>
+        <v>35.3</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.89</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.56</v>
+        <v>13.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>45.22</v>
+        <v>46.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.56</v>
+        <v>12.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.109999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.78</v>
+        <v>19</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN16" t="n">
         <v>1.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP16" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="BR16" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS16" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BT16" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX16" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY16" t="n">
         <v>3.03</v>
@@ -7252,55 +7252,55 @@
         <v>3.15</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.36</v>
+        <v>4.14</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.76</v>
+        <v>4.48</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI16" t="n">
         <v>1.63</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CK16" t="n">
         <v>1.75</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN16" t="n">
         <v>1.61</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.78</v>
+        <v>4.82</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7318,7 +7318,7 @@
         <v>1.65</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CX16" t="n">
         <v>1.82</v>
@@ -7336,85 +7336,85 @@
         <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.26</v>
+        <v>5.29</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DH16" t="n">
-        <v>89.55</v>
+        <v>90.05</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.95</v>
+        <v>38.43</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.95</v>
+        <v>14.72</v>
       </c>
       <c r="DQ16" t="n">
         <v>14.9</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.65</v>
+        <v>7.57</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.85</v>
+        <v>48.19</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX16" t="n">
-        <v>12</v>
+        <v>12.24</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.6</v>
+        <v>8.76</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.8</v>
+        <v>20.81</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" t="n">
-        <v>98.78</v>
+        <v>98.8</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>44.89</v>
+        <v>45.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.78</v>
+        <v>13.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.56</v>
+        <v>15.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.56</v>
+        <v>7.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>50.78</v>
+        <v>50.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.11</v>
+        <v>9.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BR19" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS19" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU19" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV19" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW19" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX19" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY19" t="n">
         <v>3.46</v>
@@ -8461,22 +8461,22 @@
         <v>3.9</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="CE19" t="n">
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CG19" t="n">
         <v>2.67</v>
@@ -8494,10 +8494,10 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN19" t="n">
         <v>1.83</v>
@@ -8509,13 +8509,13 @@
         <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CR19" t="n">
         <v>1.48</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT19" t="n">
         <v>2.8</v>
@@ -8524,10 +8524,10 @@
         <v>1.4</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX19" t="n">
         <v>1.59</v>
@@ -8548,55 +8548,55 @@
         <v>2.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.40000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.35</v>
+        <v>4.43</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.85</v>
+        <v>44.33</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO19" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.25</v>
+        <v>15.24</v>
       </c>
       <c r="DQ19" t="n">
-        <v>14.9</v>
+        <v>15.09</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.55</v>
+        <v>7.43</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
@@ -8605,25 +8605,25 @@
         <v>49.1</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.2</v>
+        <v>13.24</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.699999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.35</v>
+        <v>21.62</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.09</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.67</v>
+        <v>82.8</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.67</v>
+        <v>36.1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.11</v>
+        <v>13.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.22</v>
+        <v>41.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.11</v>
+        <v>10.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.89</v>
+        <v>21.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BF2" t="n">
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.6</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="BM2" t="n">
         <v>0.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT2" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX2" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY2" t="n">
         <v>4.89</v>
@@ -1613,61 +1613,61 @@
         <v>4.33</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="CC2" t="n">
-        <v>9.609999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="CD2" t="n">
-        <v>11.18</v>
+        <v>10.8</v>
       </c>
       <c r="CE2" t="n">
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CG2" t="n">
         <v>2.84</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CK2" t="n">
         <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CU2" t="n">
         <v>1.45</v>
@@ -1676,70 +1676,70 @@
         <v>1.78</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="DE2" t="n">
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.25</v>
+        <v>82.95</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DP2" t="n">
         <v>14</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.1</v>
+        <v>11.95</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.15</v>
+        <v>9.24</v>
       </c>
       <c r="DS2" t="n">
         <v>0.1</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>42.2</v>
+        <v>41.81</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.05</v>
+        <v>10.86</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.85</v>
+        <v>7.76</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.75</v>
+        <v>21.67</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>77</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.44</v>
+        <v>28.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.89</v>
+        <v>13.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.11</v>
+        <v>12.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.11</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>40.22</v>
+        <v>39.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.33</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.11</v>
+        <v>19.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY3" t="n">
         <v>4.34</v>
@@ -2013,55 +2013,55 @@
         <v>4.39</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.81</v>
+        <v>3.98</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.99</v>
+        <v>4.16</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.44</v>
+        <v>7.17</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.52</v>
+        <v>7.48</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
         <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="CR3" t="n">
         <v>1.49</v>
@@ -2076,106 +2076,106 @@
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DH3" t="n">
-        <v>78.55</v>
+        <v>77.95</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM3" t="n">
-        <v>37.5</v>
+        <v>36.76</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.15</v>
+        <v>13.38</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.9</v>
+        <v>13.76</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.4</v>
+        <v>7.72</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44</v>
+        <v>43.67</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.65</v>
+        <v>5.57</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.75</v>
+        <v>19.71</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="H4" t="n">
-        <v>119.6</v>
+        <v>120</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>6.64</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>66.8</v>
+        <v>68.36</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="P4" t="n">
-        <v>11.7</v>
+        <v>11.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="R4" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>59.2</v>
+        <v>59.55</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.9</v>
+        <v>17.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.4</v>
+        <v>10.27</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.5</v>
+        <v>6.82</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2356,70 +2356,70 @@
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.64</v>
+        <v>5.72</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.21</v>
+        <v>6.28</v>
       </c>
       <c r="CC4" t="n">
         <v>1.64</v>
@@ -2428,22 +2428,22 @@
         <v>1.66</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG4" t="n">
         <v>3.29</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
@@ -2452,19 +2452,19 @@
         <v>1.93</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN4" t="n">
         <v>1.91</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2482,103 +2482,103 @@
         <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="n">
         <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="DH4" t="n">
-        <v>117.5</v>
+        <v>117.81</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.2</v>
+        <v>6.34</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.65</v>
+        <v>64.62</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.55</v>
+        <v>11.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15</v>
+        <v>15.14</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59.4</v>
+        <v>59.57</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.3</v>
+        <v>10.71</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.1</v>
+        <v>6.29</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.35</v>
+        <v>19.38</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>83.33</v>
+        <v>85.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.11</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>40.67</v>
+        <v>40.6</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="P5" t="n">
-        <v>14.33</v>
+        <v>14.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.33</v>
+        <v>12.2</v>
       </c>
       <c r="R5" t="n">
-        <v>9.44</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45.78</v>
+        <v>48.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.89</v>
+        <v>11.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.78</v>
+        <v>7.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.22</v>
+        <v>19.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,70 +2759,70 @@
         <v>2.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.35</v>
+        <v>10.48</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.7</v>
+        <v>5.81</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU5" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.73</v>
+        <v>3.53</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.29</v>
+        <v>4.04</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CC5" t="n">
         <v>6.23</v>
@@ -2837,7 +2837,7 @@
         <v>2.86</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CH5" t="n">
         <v>1.41</v>
@@ -2846,7 +2846,7 @@
         <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
@@ -2858,28 +2858,28 @@
         <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.52</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV5" t="n">
         <v>1.9</v>
@@ -2888,100 +2888,100 @@
         <v>1.97</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA5" t="n">
         <v>1.95</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
         <v>2.09</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
         <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.3</v>
+        <v>89.09</v>
       </c>
       <c r="DI5" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.85</v>
+        <v>4.24</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.05</v>
+        <v>38.14</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="DP5" t="n">
         <v>15.05</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.7</v>
+        <v>11.67</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.9</v>
+        <v>8.76</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>43.95</v>
+        <v>45.14</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.65</v>
+        <v>12.09</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.65</v>
+        <v>8.09</v>
       </c>
       <c r="DZ5" t="n">
         <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.55</v>
+        <v>19.52</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.1</v>
@@ -3484,52 +3484,52 @@
         <v>2.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>69.91</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>28.45</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.1</v>
+        <v>14.73</v>
       </c>
       <c r="AR7" t="n">
-        <v>14</v>
+        <v>14.09</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.9</v>
+        <v>10.18</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>43.6</v>
+        <v>42.45</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.4</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.1</v>
+        <v>16.55</v>
       </c>
       <c r="BE7" t="n">
         <v>1.02</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.6</v>
+        <v>9.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY7" t="n">
         <v>4.14</v>
@@ -3625,22 +3625,22 @@
         <v>4.58</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.75</v>
+        <v>6.51</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.61</v>
+        <v>7.35</v>
       </c>
       <c r="CE7" t="n">
         <v>1.45</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CG7" t="n">
         <v>2.68</v>
@@ -3649,10 +3649,10 @@
         <v>1.35</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CK7" t="n">
         <v>1.6</v>
@@ -3661,100 +3661,100 @@
         <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO7" t="n">
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS7" t="n">
         <v>3</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CU7" t="n">
         <v>1.42</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB7" t="n">
         <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DH7" t="n">
-        <v>75</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.5</v>
+        <v>15.29</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.45</v>
+        <v>14.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.25</v>
+        <v>9.43</v>
       </c>
       <c r="DS7" t="n">
         <v>0.05</v>
@@ -3766,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>44.75</v>
+        <v>44.09</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.4</v>
+        <v>8.43</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.4</v>
+        <v>17.57</v>
       </c>
       <c r="EB7" t="n">
         <v>0.96</v>
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>91.40000000000001</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.82</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M10" t="n">
-        <v>43.8</v>
+        <v>44.73</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P10" t="n">
-        <v>16.9</v>
+        <v>16.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.6</v>
+        <v>16.36</v>
       </c>
       <c r="R10" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>50.7</v>
+        <v>52.09</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>13.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>19.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BR10" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS10" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT10" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CC10" t="n">
         <v>2.76</v>
@@ -4849,13 +4849,13 @@
         <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI10" t="n">
         <v>1.82</v>
@@ -4867,7 +4867,7 @@
         <v>1.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM10" t="n">
         <v>2.37</v>
@@ -4879,22 +4879,22 @@
         <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV10" t="n">
         <v>1.9</v>
@@ -4906,64 +4906,64 @@
         <v>1.56</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.36</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB10" t="n">
         <v>1.37</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.05</v>
+        <v>90.09</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.5</v>
+        <v>46.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.5</v>
+        <v>17.09</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.6</v>
+        <v>16.47</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.65</v>
+        <v>7.48</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.8</v>
+        <v>51.52</v>
       </c>
       <c r="DW10" t="n">
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.55</v>
+        <v>12.62</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.35</v>
+        <v>20.52</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="11">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>106.89</v>
+        <v>106.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.67</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M14" t="n">
-        <v>50.56</v>
+        <v>48.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>12.56</v>
+        <v>12.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="R14" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="S14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>56.44</v>
+        <v>55.3</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.44</v>
+        <v>13.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.56</v>
+        <v>5.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.44</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
         <v>0.09</v>
@@ -6386,49 +6386,49 @@
         <v>2.27</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="BR14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU14" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.34</v>
+        <v>5.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.56</v>
+        <v>5.44</v>
       </c>
       <c r="CC14" t="n">
         <v>1.54</v>
@@ -6461,154 +6461,154 @@
         <v>1.34</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CH14" t="n">
         <v>1.47</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN14" t="n">
         <v>1.77</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB14" t="n">
         <v>1.28</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DH14" t="n">
-        <v>104.25</v>
+        <v>104.33</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.65</v>
+        <v>49.62</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.65</v>
+        <v>13.67</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.85</v>
+        <v>56.28</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.45</v>
+        <v>14.14</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.85</v>
+        <v>8.76</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.6</v>
+        <v>5.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.35</v>
+        <v>19.19</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>63.2</v>
+        <v>61.82</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN15" t="n">
-        <v>29.9</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.2</v>
+        <v>13.73</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.3</v>
+        <v>15.18</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.8</v>
+        <v>10.36</v>
       </c>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.5</v>
+        <v>44.73</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.4</v>
+        <v>9.18</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.3</v>
+        <v>16.09</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BG15" t="n">
         <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
       <c r="BI15" t="n">
         <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR15" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT15" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY15" t="n">
         <v>4.07</v>
@@ -6849,55 +6849,55 @@
         <v>4.29</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.97</v>
+        <v>4.11</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.24</v>
+        <v>6.95</v>
       </c>
       <c r="CD15" t="n">
-        <v>8.1</v>
+        <v>8.69</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN15" t="n">
         <v>1.88</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
@@ -6912,106 +6912,106 @@
         <v>1.45</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA15" t="n">
         <v>1.91</v>
       </c>
-      <c r="CZ15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="DB15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.55</v>
+        <v>66.62</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM15" t="n">
-        <v>27.15</v>
+        <v>26.81</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.25</v>
+        <v>13.05</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.2</v>
+        <v>15.14</v>
       </c>
       <c r="DR15" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.05</v>
+        <v>45.62</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.25</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.55</v>
+        <v>5.53</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.3</v>
+        <v>16.19</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="16">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>114.78</v>
+        <v>118</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K17" t="n">
-        <v>5.44</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>54.56</v>
+        <v>57</v>
       </c>
       <c r="N17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.11</v>
+        <v>10.8</v>
       </c>
       <c r="R17" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="S17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>62.89</v>
+        <v>62.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.11</v>
+        <v>12.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.78</v>
+        <v>21.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0.09</v>
@@ -7598,7 +7598,7 @@
         <v>2.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI17" t="n">
         <v>2.95</v>
@@ -7607,58 +7607,58 @@
         <v>1.05</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT17" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.12</v>
+        <v>4.25</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.28</v>
+        <v>4.43</v>
       </c>
       <c r="CC17" t="n">
         <v>2.5</v>
@@ -7670,16 +7670,16 @@
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.96</v>
@@ -7688,22 +7688,22 @@
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="CR17" t="n">
         <v>1.39</v>
@@ -7718,106 +7718,106 @@
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DA17" t="n">
         <v>1.84</v>
       </c>
-      <c r="CW17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CX17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CY17" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>1.82</v>
-      </c>
       <c r="DB17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="DH17" t="n">
-        <v>111</v>
+        <v>112.71</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM17" t="n">
-        <v>55.6</v>
+        <v>56.71</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.75</v>
+        <v>10.86</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12</v>
+        <v>11.81</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.25</v>
+        <v>5.14</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>64.59999999999999</v>
+        <v>64.52</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.1</v>
+        <v>13.19</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.15</v>
+        <v>21.05</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0.1</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>108.3</v>
+        <v>105.91</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="AM18" t="n">
         <v>1</v>
       </c>
       <c r="AN18" t="n">
-        <v>54.6</v>
+        <v>53.73</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.1</v>
+        <v>12.91</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.4</v>
+        <v>15.18</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>64.40000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA18" t="n">
-        <v>17.2</v>
+        <v>16.64</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.8</v>
+        <v>10.55</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="BD18" t="n">
-        <v>15.7</v>
+        <v>15.73</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.85</v>
+        <v>9.81</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL18" t="n">
         <v>1.1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN18" t="n">
         <v>1.9</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.95</v>
+        <v>4.81</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY18" t="n">
         <v>1.26</v>
@@ -8058,169 +8058,169 @@
         <v>1.24</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.26</v>
+        <v>6.11</v>
       </c>
       <c r="CB18" t="n">
-        <v>7.23</v>
+        <v>7.04</v>
       </c>
       <c r="CC18" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM18" t="n">
         <v>2.23</v>
       </c>
-      <c r="CG18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>2.24</v>
-      </c>
       <c r="CN18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CV18" t="n">
         <v>1.76</v>
       </c>
-      <c r="CO18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>1.74</v>
-      </c>
       <c r="CW18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="DE18" t="n">
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="DH18" t="n">
-        <v>114.8</v>
+        <v>113.24</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="DK18" t="n">
-        <v>7.05</v>
+        <v>7.1</v>
       </c>
       <c r="DL18" t="n">
         <v>0.95</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.75</v>
+        <v>57.14</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.4</v>
+        <v>13.38</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.4</v>
+        <v>4.52</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.2</v>
+        <v>61.86</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX18" t="n">
-        <v>18.7</v>
+        <v>18.34</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.45</v>
+        <v>11.29</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.25</v>
+        <v>7.05</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.9</v>
+        <v>16.86</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>76</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE3" t="n">
         <v>0.9</v>
       </c>
-      <c r="AI3" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.87</v>
-      </c>
       <c r="BF3" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.9</v>
+        <v>8.27</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL3" t="n">
         <v>0.86</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>4.34</v>
@@ -2013,28 +2013,28 @@
         <v>4.39</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="CC3" t="n">
-        <v>7.17</v>
+        <v>6.79</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.48</v>
+        <v>7.07</v>
       </c>
       <c r="CE3" t="n">
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG3" t="n">
         <v>2.71</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI3" t="n">
         <v>1.76</v>
@@ -2043,13 +2043,13 @@
         <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN3" t="n">
         <v>1.65</v>
@@ -2058,10 +2058,10 @@
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="CR3" t="n">
         <v>1.49</v>
@@ -2082,100 +2082,100 @@
         <v>2.1</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY3" t="n">
         <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>77.95</v>
+        <v>77.91</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="DL3" t="n">
         <v>0.09</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.76</v>
+        <v>36.91</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.38</v>
+        <v>13.18</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.76</v>
+        <v>13.78</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.72</v>
+        <v>7.91</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.67</v>
+        <v>43.5</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.050000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.71</v>
+        <v>19.64</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.09</v>
@@ -2275,139 +2275,139 @@
         <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AI4" t="n">
-        <v>115.4</v>
+        <v>114.64</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL4" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>60.5</v>
+        <v>59.45</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.4</v>
+        <v>10.82</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>6.73</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>59.6</v>
+        <v>58.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.9</v>
+        <v>16.36</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.2</v>
+        <v>10.91</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.7</v>
+        <v>5.45</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.8</v>
+        <v>20.45</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS4" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.35</v>
@@ -2416,55 +2416,55 @@
         <v>1.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.72</v>
+        <v>5.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.28</v>
+        <v>6.18</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL4" t="n">
         <v>1.93</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2485,97 +2485,97 @@
         <v>2.22</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="DH4" t="n">
-        <v>117.81</v>
+        <v>117.32</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
         <v>2.09</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.34</v>
+        <v>6.36</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>64.62</v>
+        <v>63.9</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DO4" t="n">
         <v>2.95</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.53</v>
+        <v>11.23</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.14</v>
+        <v>15.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59.57</v>
+        <v>59</v>
       </c>
       <c r="DW4" t="n">
         <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>17</v>
+        <v>16.72</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.71</v>
+        <v>10.59</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.29</v>
+        <v>6.14</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.38</v>
+        <v>19.72</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="EC4" t="n">
         <v>1.95</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>80.8</v>
+        <v>82.91</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>36.7</v>
+        <v>39.27</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>13.6</v>
+        <v>13.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.5</v>
+        <v>11.36</v>
       </c>
       <c r="R6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>39.6</v>
+        <v>41.45</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>11.64</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.6</v>
+        <v>8.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.5</v>
+        <v>19.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>2.64</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.52</v>
+        <v>9.82</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
         <v>0.95</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.76</v>
+        <v>4.95</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.83</v>
+        <v>5.54</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="CC6" t="n">
         <v>5.65</v>
@@ -3234,43 +3234,43 @@
         <v>5.63</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ6" t="n">
         <v>2</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CO6" t="n">
         <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
@@ -3291,100 +3291,100 @@
         <v>2.02</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="DH6" t="n">
-        <v>79.14</v>
+        <v>80.27</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="DM6" t="n">
-        <v>34.86</v>
+        <v>36.22</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.62</v>
+        <v>14.6</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.1</v>
+        <v>11.04</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.76</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41</v>
+        <v>41.86</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.33</v>
+        <v>10.68</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.9</v>
+        <v>7.22</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.76</v>
+        <v>18.87</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="H7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>33.6</v>
+        <v>32.64</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="P7" t="n">
-        <v>15.9</v>
+        <v>16.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.9</v>
+        <v>14.18</v>
       </c>
       <c r="R7" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>45.9</v>
+        <v>44.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.4</v>
+        <v>7.73</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.7</v>
+        <v>18.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="AF7" t="n">
         <v>0.09</v>
@@ -3565,70 +3565,70 @@
         <v>3.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.76</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.38</v>
+        <v>4.27</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.14</v>
+        <v>4.03</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CC7" t="n">
         <v>6.51</v>
@@ -3643,22 +3643,22 @@
         <v>3.06</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH7" t="n">
         <v>1.35</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK7" t="n">
         <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM7" t="n">
         <v>2.21</v>
@@ -3673,28 +3673,28 @@
         <v>2.21</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CR7" t="n">
         <v>1.5</v>
       </c>
       <c r="CS7" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY7" t="n">
         <v>2.06</v>
@@ -3718,76 +3718,76 @@
         <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DH7" t="n">
-        <v>74.70999999999999</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.9</v>
+        <v>30.54</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.29</v>
+        <v>15.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.48</v>
+        <v>14.14</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.43</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>44.09</v>
+        <v>43.5</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.43</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.57</v>
+        <v>5.64</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.57</v>
+        <v>17.41</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.55</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>63.6</v>
+        <v>63.36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>24.9</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.2</v>
+        <v>16.27</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.2</v>
+        <v>14.09</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="AT8" t="n">
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.2</v>
+        <v>41.64</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>7.09</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.1</v>
+        <v>16.64</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BG8" t="n">
         <v>2.95</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.48</v>
+        <v>8.59</v>
       </c>
       <c r="BI8" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP8" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU8" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV8" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>3.82</v>
@@ -4028,28 +4028,28 @@
         <v>4.13</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CC8" t="n">
-        <v>8.01</v>
+        <v>7.73</v>
       </c>
       <c r="CD8" t="n">
-        <v>9.220000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="CE8" t="n">
         <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI8" t="n">
         <v>1.75</v>
@@ -4058,7 +4058,7 @@
         <v>2.05</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL8" t="n">
         <v>2.15</v>
@@ -4076,16 +4076,16 @@
         <v>2.11</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU8" t="n">
         <v>1.43</v>
@@ -4106,7 +4106,7 @@
         <v>2.16</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB8" t="n">
         <v>1.38</v>
@@ -4118,79 +4118,79 @@
         <v>4.01</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DH8" t="n">
-        <v>74.19</v>
+        <v>73.59</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM8" t="n">
-        <v>29.28</v>
+        <v>28.64</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.95</v>
+        <v>15.04</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15</v>
+        <v>14.91</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.289999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.86</v>
+        <v>46.82</v>
       </c>
       <c r="DW8" t="n">
         <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.62</v>
+        <v>10.41</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.14</v>
+        <v>6.91</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.53</v>
+        <v>18.69</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.18</v>
@@ -4290,52 +4290,52 @@
         <v>2.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
-        <v>87.5</v>
+        <v>89.55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>38.1</v>
+        <v>38.91</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>13.09</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>12.36</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50</v>
+        <v>51.73</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.5</v>
+        <v>10.27</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>7.27</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
-        <v>21</v>
+        <v>21.73</v>
       </c>
       <c r="BE9" t="n">
         <v>1.15</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.19</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BK9" t="n">
         <v>0.86</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="BL9" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.29</v>
+        <v>4.18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY9" t="n">
         <v>4.05</v>
@@ -4431,52 +4431,52 @@
         <v>4.77</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.43</v>
+        <v>5.16</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.77</v>
+        <v>5.48</v>
       </c>
       <c r="CE9" t="n">
         <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI9" t="n">
         <v>1.84</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK9" t="n">
         <v>1.56</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
         <v>2.27</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CO9" t="n">
         <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
         <v>3.53</v>
@@ -4485,13 +4485,13 @@
         <v>1.46</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT9" t="n">
         <v>2.84</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV9" t="n">
         <v>1.92</v>
@@ -4500,13 +4500,13 @@
         <v>1.94</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY9" t="n">
         <v>2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA9" t="n">
         <v>1.81</v>
@@ -4515,52 +4515,52 @@
         <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.43000000000001</v>
+        <v>86.55</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.57</v>
+        <v>35.14</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DP9" t="n">
-        <v>14</v>
+        <v>13.77</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.05</v>
+        <v>12.46</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.48</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.71</v>
+        <v>50.59</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.43</v>
+        <v>10.32</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.05</v>
+        <v>6.91</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.09</v>
+        <v>20.5</v>
       </c>
       <c r="EB9" t="n">
         <v>1.14</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="H12" t="n">
-        <v>86.5</v>
+        <v>86.55</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M12" t="n">
-        <v>50.8</v>
+        <v>50.73</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>14.1</v>
+        <v>13.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.8</v>
+        <v>15.09</v>
       </c>
       <c r="R12" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.3</v>
+        <v>48.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.6</v>
+        <v>15.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.6</v>
+        <v>20.91</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
         <v>0.18</v>
@@ -5580,70 +5580,70 @@
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.14</v>
+        <v>5.23</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU12" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC12" t="n">
         <v>3.84</v>
@@ -5655,10 +5655,10 @@
         <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CH12" t="n">
         <v>1.31</v>
@@ -5667,19 +5667,19 @@
         <v>1.71</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CM12" t="n">
         <v>2.15</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CO12" t="n">
         <v>1.4</v>
@@ -5694,7 +5694,7 @@
         <v>1.5</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CT12" t="n">
         <v>2.72</v>
@@ -5703,19 +5703,19 @@
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DA12" t="n">
         <v>1.72</v>
@@ -5727,82 +5727,82 @@
         <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
         <v>2.09</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="DH12" t="n">
-        <v>87.81</v>
+        <v>87.78</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.81</v>
+        <v>5.78</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DM12" t="n">
-        <v>45.95</v>
+        <v>46.14</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.19</v>
+        <v>13.91</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.62</v>
+        <v>14.77</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.57</v>
+        <v>6.64</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.28</v>
+        <v>49.32</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.29</v>
+        <v>14.32</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.95</v>
+        <v>22.04</v>
       </c>
       <c r="EB12" t="n">
         <v>1.56</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="13">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F16" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H16" t="n">
-        <v>93.55</v>
+        <v>94.33</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="K16" t="n">
-        <v>5.18</v>
+        <v>4.83</v>
       </c>
       <c r="L16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M16" t="n">
-        <v>41.27</v>
+        <v>40.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O16" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="P16" t="n">
-        <v>15.82</v>
+        <v>16.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>15.08</v>
       </c>
       <c r="R16" t="n">
-        <v>6.91</v>
+        <v>7.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="U16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50</v>
+        <v>50.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.36</v>
+        <v>12.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.45</v>
+        <v>22.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="AF16" t="n">
         <v>0.2</v>
@@ -7192,70 +7192,70 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.710000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="BR16" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS16" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU16" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.03</v>
+        <v>3.28</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.15</v>
+        <v>3.51</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CC16" t="n">
         <v>4.14</v>
@@ -7264,43 +7264,43 @@
         <v>4.48</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CK16" t="n">
         <v>1.75</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN16" t="n">
         <v>1.61</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.82</v>
+        <v>4.76</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7318,103 +7318,103 @@
         <v>1.65</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DA16" t="n">
         <v>1.61</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.05</v>
+        <v>90.63</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.19</v>
+        <v>3.32</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.76</v>
+        <v>4.59</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.43</v>
+        <v>38.27</v>
       </c>
       <c r="DN16" t="n">
         <v>1</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="DP16" t="n">
-        <v>14.72</v>
+        <v>15.09</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.9</v>
+        <v>14.45</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.19</v>
+        <v>48.41</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.24</v>
+        <v>12.09</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.76</v>
+        <v>8.68</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.81</v>
+        <v>21</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC16" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.3</v>
@@ -7514,139 +7514,139 @@
         <v>1.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>107.91</v>
+        <v>106.67</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.55</v>
+        <v>5.58</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.45</v>
+        <v>55.58</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.18</v>
+        <v>11.58</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.73</v>
+        <v>12.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.36</v>
+        <v>5.67</v>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AU17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>64.67</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF17" t="n">
         <v>2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>66</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.09</v>
       </c>
       <c r="BG17" t="n">
         <v>2.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.289999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="BI17" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT17" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX17" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY17" t="n">
         <v>1.59</v>
@@ -7655,28 +7655,28 @@
         <v>1.66</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
         <v>1.78</v>
@@ -7688,136 +7688,136 @@
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV17" t="n">
         <v>1.83</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DB17" t="n">
         <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DH17" t="n">
-        <v>112.71</v>
+        <v>111.82</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.71</v>
+        <v>56.23</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DP17" t="n">
-        <v>10.86</v>
+        <v>11.09</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.81</v>
+        <v>11.59</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.14</v>
+        <v>5.32</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>64.52</v>
+        <v>63.87</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.19</v>
+        <v>13.09</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.86</v>
+        <v>7.91</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.33</v>
+        <v>5.18</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.05</v>
+        <v>20.91</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="18">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -8242,82 +8242,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="H19" t="n">
-        <v>89</v>
+        <v>90.08</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="K19" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M19" t="n">
-        <v>43</v>
+        <v>44.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>16.45</v>
+        <v>16.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.36</v>
+        <v>14.67</v>
       </c>
       <c r="R19" t="n">
-        <v>7.55</v>
+        <v>7.17</v>
       </c>
       <c r="S19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>47.73</v>
+        <v>48.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.09</v>
+        <v>13.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.359999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="AC19" t="n">
         <v>20</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,70 +8401,70 @@
         <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="BH19" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO19" t="n">
         <v>1.14</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS19" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT19" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV19" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW19" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX19" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.9</v>
+        <v>3.71</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC19" t="n">
         <v>3.12</v>
@@ -8479,7 +8479,7 @@
         <v>3.12</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
@@ -8500,7 +8500,7 @@
         <v>2.34</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO19" t="n">
         <v>1.38</v>
@@ -8509,10 +8509,10 @@
         <v>2.17</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS19" t="n">
         <v>3.11</v>
@@ -8548,49 +8548,49 @@
         <v>2.26</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.67</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.43</v>
+        <v>4.64</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.33</v>
+        <v>45.23</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DO19" t="n">
         <v>2.09</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.24</v>
+        <v>15.14</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.09</v>
+        <v>15.23</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.43</v>
+        <v>7.23</v>
       </c>
       <c r="DS19" t="n">
         <v>0.14</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.1</v>
+        <v>49.32</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.24</v>
+        <v>13.55</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.619999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.62</v>
+        <v>21.55</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="G2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H2" t="n">
+        <v>82.17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>83.09</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M2" t="n">
-        <v>34</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.91</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>14.73</v>
+        <v>14.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.18</v>
+        <v>12.92</v>
       </c>
       <c r="R2" t="n">
-        <v>7.91</v>
+        <v>8.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="T2" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>42.18</v>
+        <v>41.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.36</v>
+        <v>7.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.64</v>
+        <v>20.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.619999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="BJ2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BM2" t="n">
         <v>0.86</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.9</v>
-      </c>
       <c r="BN2" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.57</v>
+        <v>3.77</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.29</v>
+        <v>4.55</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5.14</v>
+        <v>5.08</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="CC2" t="n">
         <v>9.35</v>
@@ -1622,157 +1622,157 @@
         <v>10.8</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CH2" t="n">
         <v>1.41</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK2" t="n">
         <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CR2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CU2" t="n">
         <v>1.46</v>
       </c>
-      <c r="CS2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.45</v>
-      </c>
       <c r="CV2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CX2" t="n">
         <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
         <v>1.33</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="DH2" t="n">
-        <v>82.95</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.38</v>
+        <v>3.63</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.19</v>
+        <v>0.36</v>
       </c>
       <c r="DM2" t="n">
-        <v>35</v>
+        <v>35.23</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="DP2" t="n">
-        <v>14</v>
+        <v>13.77</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.95</v>
+        <v>11.87</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.24</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>41.81</v>
+        <v>41.23</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.86</v>
+        <v>11.04</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.76</v>
+        <v>7.95</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.67</v>
+        <v>21.14</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="3">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>85.5</v>
+        <v>85.55</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>40.6</v>
+        <v>40.18</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P5" t="n">
-        <v>14.4</v>
+        <v>14.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.2</v>
+        <v>12.09</v>
       </c>
       <c r="R5" t="n">
-        <v>9.1</v>
+        <v>9.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.9</v>
+        <v>11.64</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.8</v>
+        <v>7.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.2</v>
+        <v>19.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,70 +2759,70 @@
         <v>2.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.48</v>
+        <v>10.59</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS5" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.53</v>
+        <v>3.84</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.04</v>
+        <v>4.44</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="CC5" t="n">
         <v>6.23</v>
@@ -2834,10 +2834,10 @@
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CH5" t="n">
         <v>1.41</v>
@@ -2846,7 +2846,7 @@
         <v>1.85</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
@@ -2858,7 +2858,7 @@
         <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO5" t="n">
         <v>1.32</v>
@@ -2867,7 +2867,7 @@
         <v>2.05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CR5" t="n">
         <v>1.45</v>
@@ -2885,16 +2885,16 @@
         <v>1.9</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
         <v>1.86</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
         <v>1.95</v>
@@ -2903,85 +2903,85 @@
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="DE5" t="n">
         <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DH5" t="n">
-        <v>89.09</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.14</v>
+        <v>38.04</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO5" t="n">
         <v>1.95</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.05</v>
+        <v>14.96</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.67</v>
+        <v>11.64</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.76</v>
+        <v>8.82</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.14</v>
+        <v>45.22</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.09</v>
+        <v>11.96</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.09</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.52</v>
+        <v>19.55</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.27</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>86.7</v>
+        <v>84</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.3</v>
+        <v>4.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>49.2</v>
+        <v>45.91</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.1</v>
+        <v>18.09</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.6</v>
+        <v>16.64</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>50.9</v>
+        <v>49</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.6</v>
+        <v>10.73</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.55</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.7</v>
+        <v>21.09</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.9</v>
+        <v>10.14</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL10" t="n">
         <v>0.86</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BT10" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BY10" t="n">
         <v>2.69</v>
@@ -4834,28 +4834,28 @@
         <v>2.71</v>
       </c>
       <c r="CA10" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="CC10" t="n">
         <v>3.53</v>
       </c>
-      <c r="CB10" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>2.76</v>
-      </c>
       <c r="CD10" t="n">
-        <v>2.79</v>
+        <v>3.48</v>
       </c>
       <c r="CE10" t="n">
         <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI10" t="n">
         <v>1.82</v>
@@ -4867,103 +4867,103 @@
         <v>1.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CT10" t="n">
         <v>2.93</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CY10" t="n">
         <v>1.9</v>
       </c>
-      <c r="CW10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CY10" t="n">
+      <c r="CZ10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA10" t="n">
         <v>1.91</v>
       </c>
-      <c r="CZ10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.9</v>
-      </c>
       <c r="DB10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="DE10" t="n">
         <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="DH10" t="n">
-        <v>90.09</v>
+        <v>88.59</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.05</v>
+        <v>4.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.86</v>
+        <v>45.32</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.09</v>
+        <v>17.14</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.47</v>
+        <v>16.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.48</v>
+        <v>7.78</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.52</v>
+        <v>50.54</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.62</v>
+        <v>12.14</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.380000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.24</v>
+        <v>4.09</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.52</v>
+        <v>20.27</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5096,139 +5096,139 @@
         <v>3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.90000000000001</v>
+        <v>97.91</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.4</v>
+        <v>4.82</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="AN11" t="n">
-        <v>47</v>
+        <v>49.09</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13.18</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>12.64</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.7</v>
+        <v>7.64</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.4</v>
+        <v>52.27</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.1</v>
+        <v>8.27</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="BE11" t="n">
         <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.050000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.81</v>
+        <v>4.95</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.19</v>
+        <v>4.45</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BV11" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BW11" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY11" t="n">
         <v>3.23</v>
@@ -5237,37 +5237,37 @@
         <v>3.26</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CB11" t="n">
         <v>3.98</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.66</v>
+        <v>5.3</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.65</v>
+        <v>5.29</v>
       </c>
       <c r="CE11" t="n">
         <v>1.38</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CH11" t="n">
         <v>1.42</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL11" t="n">
         <v>2.09</v>
@@ -5279,31 +5279,31 @@
         <v>1.68</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX11" t="n">
         <v>1.63</v>
@@ -5315,91 +5315,91 @@
         <v>2.25</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB11" t="n">
         <v>1.31</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="DE11" t="n">
         <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.86</v>
+        <v>103</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.53</v>
+        <v>4.73</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.81</v>
+        <v>46.91</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.71</v>
+        <v>12.59</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.71</v>
+        <v>12.54</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.15</v>
+        <v>8.1</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.71</v>
+        <v>52.59</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.57</v>
+        <v>12.54</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.95</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>21.41</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="12">
@@ -5637,7 +5637,7 @@
         <v>3.15</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="CA12" t="n">
         <v>3.47</v>
@@ -5694,7 +5694,7 @@
         <v>1.5</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT12" t="n">
         <v>2.72</v>
@@ -5703,10 +5703,10 @@
         <v>1.38</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX12" t="n">
         <v>1.69</v>
@@ -5727,7 +5727,7 @@
         <v>2.31</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="DE12" t="n">
         <v>0.13</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,52 +5902,52 @@
         <v>2.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>79.55</v>
+        <v>78.42</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>33.55</v>
+        <v>32.08</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.82</v>
+        <v>14.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.27</v>
+        <v>16.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.18</v>
+        <v>9.08</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.73</v>
+        <v>48.92</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.82</v>
+        <v>5.58</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>20.73</v>
+        <v>20.67</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>3.96</v>
@@ -6043,22 +6043,22 @@
         <v>4.25</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.67</v>
+        <v>4.48</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.91</v>
+        <v>4.68</v>
       </c>
       <c r="CE13" t="n">
         <v>1.47</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CG13" t="n">
         <v>2.6</v>
@@ -6070,19 +6070,19 @@
         <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
         <v>1.74</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
         <v>1.4</v>
@@ -6106,22 +6106,22 @@
         <v>1.37</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX13" t="n">
         <v>1.78</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB13" t="n">
         <v>1.42</v>
@@ -6130,19 +6130,19 @@
         <v>2.31</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="DE13" t="n">
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DH13" t="n">
-        <v>74.76000000000001</v>
+        <v>74.37</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
@@ -6151,28 +6151,28 @@
         <v>2.86</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.15</v>
+        <v>30.45</v>
       </c>
       <c r="DN13" t="n">
         <v>0.95</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.19</v>
+        <v>14.64</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.67</v>
+        <v>15.73</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.619999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>50.05</v>
+        <v>49.59</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.140000000000001</v>
+        <v>9</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.76</v>
+        <v>5.63</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.43</v>
+        <v>20.41</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.1</v>
@@ -6305,130 +6305,130 @@
         <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AI14" t="n">
-        <v>102.09</v>
+        <v>100.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.45</v>
+        <v>5.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.73</v>
+        <v>50.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.55</v>
+        <v>14.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>13.36</v>
+        <v>13.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.18</v>
+        <v>56.83</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.45</v>
+        <v>13.92</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.82</v>
+        <v>8.33</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.45</v>
+        <v>19</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BF14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG14" t="n">
         <v>2.27</v>
       </c>
-      <c r="BG14" t="n">
-        <v>2.33</v>
-      </c>
       <c r="BH14" t="n">
-        <v>8.33</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
         <v>0.86</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BY14" t="n">
         <v>1.46</v>
@@ -6446,22 +6446,22 @@
         <v>1.48</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CE14" t="n">
         <v>1.34</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG14" t="n">
         <v>3.08</v>
@@ -6473,19 +6473,19 @@
         <v>1.68</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO14" t="n">
         <v>1.25</v>
@@ -6494,7 +6494,7 @@
         <v>1.84</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
@@ -6509,22 +6509,22 @@
         <v>1.49</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CW14" t="n">
         <v>2.24</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB14" t="n">
         <v>1.28</v>
@@ -6533,82 +6533,82 @@
         <v>1.87</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="DE14" t="n">
         <v>0.09</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DH14" t="n">
-        <v>104.33</v>
+        <v>103.23</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.33</v>
+        <v>5.46</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.62</v>
+        <v>49.64</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.67</v>
+        <v>13.55</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.81</v>
+        <v>11.86</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.28</v>
+        <v>56.13</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.14</v>
+        <v>13.87</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.76</v>
+        <v>8.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.19</v>
+        <v>19.45</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
-        <v>71.90000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="M15" t="n">
-        <v>24.4</v>
+        <v>27.45</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="P15" t="n">
-        <v>12.3</v>
+        <v>12.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.1</v>
+        <v>15.91</v>
       </c>
       <c r="R15" t="n">
-        <v>9.6</v>
+        <v>8.91</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.6</v>
+        <v>47.82</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.1</v>
+        <v>9.91</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.5</v>
+        <v>6.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.3</v>
+        <v>16.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6792,67 +6792,67 @@
         <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.81</v>
+        <v>10.68</v>
       </c>
       <c r="BI15" t="n">
         <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX15" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY15" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="CA15" t="n">
         <v>4.07</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>4.11</v>
-      </c>
       <c r="CB15" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
       <c r="CC15" t="n">
         <v>6.95</v>
@@ -6861,13 +6861,13 @@
         <v>8.69</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CH15" t="n">
         <v>1.42</v>
@@ -6879,37 +6879,37 @@
         <v>1.91</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN15" t="n">
         <v>1.88</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV15" t="n">
         <v>1.95</v>
@@ -6918,67 +6918,67 @@
         <v>1.95</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DA15" t="n">
         <v>1.9</v>
       </c>
-      <c r="CZ15" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DB15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DH15" t="n">
-        <v>66.62</v>
+        <v>70.78</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.76</v>
+        <v>3.91</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DM15" t="n">
-        <v>26.81</v>
+        <v>28.22</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.05</v>
+        <v>13.19</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.14</v>
+        <v>15.54</v>
       </c>
       <c r="DR15" t="n">
-        <v>10</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.62</v>
+        <v>46.28</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.140000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.53</v>
+        <v>5.82</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.19</v>
+        <v>16.45</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="16">
@@ -7664,7 +7664,7 @@
         <v>2.48</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
@@ -7721,7 +7721,7 @@
         <v>1.83</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX17" t="n">
         <v>1.61</v>
@@ -7736,13 +7736,13 @@
         <v>1.82</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="DE17" t="n">
         <v>0.18</v>
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="H18" t="n">
-        <v>121.3</v>
+        <v>122.73</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="K18" t="n">
-        <v>6.4</v>
+        <v>7.09</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M18" t="n">
-        <v>60.9</v>
+        <v>62.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>11.9</v>
+        <v>12.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.4</v>
+        <v>12.09</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>60</v>
+        <v>60.91</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.2</v>
+        <v>20.36</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.1</v>
+        <v>12.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.1</v>
+        <v>7.82</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.1</v>
+        <v>18.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>3.09</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.81</v>
+        <v>10.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV18" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX18" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
         <v>1.26</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="CB18" t="n">
-        <v>7.04</v>
+        <v>6.97</v>
       </c>
       <c r="CC18" t="n">
         <v>1.62</v>
@@ -8070,10 +8070,10 @@
         <v>1.62</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG18" t="n">
         <v>3.31</v>
@@ -8085,28 +8085,28 @@
         <v>1.73</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK18" t="n">
         <v>1.47</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP18" t="n">
         <v>1.66</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
@@ -8127,16 +8127,16 @@
         <v>2.2</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB18" t="n">
         <v>1.22</v>
@@ -8145,49 +8145,49 @@
         <v>1.68</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.71</v>
+        <v>3.91</v>
       </c>
       <c r="DH18" t="n">
-        <v>113.24</v>
+        <v>114.32</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DK18" t="n">
-        <v>7.1</v>
+        <v>7.41</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.14</v>
+        <v>58.14</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.43</v>
+        <v>12.59</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.38</v>
+        <v>13.64</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.52</v>
+        <v>4.36</v>
       </c>
       <c r="DS18" t="n">
         <v>0.14</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>61.86</v>
+        <v>62.23</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX18" t="n">
-        <v>18.34</v>
+        <v>18.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.29</v>
+        <v>11.55</v>
       </c>
       <c r="DZ18" t="n">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
       <c r="EA18" t="n">
-        <v>16.86</v>
+        <v>17.28</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AI2" t="n">
-        <v>82.8</v>
+        <v>81.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.1</v>
+        <v>35.36</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.2</v>
+        <v>13.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.6</v>
+        <v>10.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>41.4</v>
+        <v>40.82</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.73</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.7</v>
+        <v>21.73</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.050000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT2" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY2" t="n">
         <v>4.81</v>
@@ -1610,55 +1610,55 @@
         <v>5.08</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.3</v>
+        <v>4.62</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.79</v>
+        <v>5.07</v>
       </c>
       <c r="CC2" t="n">
-        <v>9.35</v>
+        <v>10.13</v>
       </c>
       <c r="CD2" t="n">
-        <v>10.8</v>
+        <v>12.07</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1673,73 +1673,73 @@
         <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CX2" t="n">
         <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="DE2" t="n">
         <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH2" t="n">
-        <v>82.45999999999999</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.23</v>
+        <v>34.91</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.87</v>
+        <v>11.65</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.460000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>41.23</v>
+        <v>40.96</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>11.04</v>
+        <v>10.69</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.95</v>
+        <v>7.74</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.14</v>
+        <v>21.18</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="3">
@@ -1782,91 +1782,91 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>79.81999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="L3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>44.09</v>
+        <v>43.42</v>
       </c>
       <c r="N3" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="P3" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.55</v>
+        <v>14.42</v>
       </c>
       <c r="R3" t="n">
-        <v>7.64</v>
+        <v>8.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="U3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="V3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.09</v>
+        <v>46.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.73</v>
+        <v>10.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.27</v>
+        <v>19.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1953,70 +1953,70 @@
         <v>2.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.27</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT3" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.39</v>
+        <v>4.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="CC3" t="n">
         <v>6.79</v>
@@ -2025,13 +2025,13 @@
         <v>7.07</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
@@ -2040,10 +2040,10 @@
         <v>1.76</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL3" t="n">
         <v>2.1</v>
@@ -2052,16 +2052,16 @@
         <v>2.07</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="CR3" t="n">
         <v>1.49</v>
@@ -2070,7 +2070,7 @@
         <v>3.24</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2085,97 +2085,97 @@
         <v>1.69</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.18</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="DH3" t="n">
-        <v>77.91</v>
+        <v>78.05</v>
       </c>
       <c r="DI3" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="DL3" t="n">
         <v>0.09</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.91</v>
+        <v>36.87</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.18</v>
+        <v>13.3</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.78</v>
+        <v>13.74</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.91</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.5</v>
+        <v>43.57</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.09</v>
+        <v>9</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.64</v>
+        <v>19.48</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>120</v>
+        <v>121.42</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="K4" t="n">
-        <v>6.64</v>
+        <v>6.92</v>
       </c>
       <c r="L4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>68.36</v>
+        <v>70.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>11.64</v>
+        <v>11.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>15.83</v>
       </c>
       <c r="R4" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="T4" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="V4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>59.55</v>
+        <v>60</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.09</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.27</v>
+        <v>10.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.82</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
-        <v>19</v>
+        <v>18.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2356,70 +2356,70 @@
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT4" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>1.35</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1.37</v>
-      </c>
       <c r="CA4" t="n">
-        <v>5.64</v>
+        <v>5.91</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.18</v>
+        <v>6.4</v>
       </c>
       <c r="CC4" t="n">
         <v>1.63</v>
@@ -2428,22 +2428,22 @@
         <v>1.65</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
         <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CK4" t="n">
         <v>1.51</v>
@@ -2452,19 +2452,19 @@
         <v>1.93</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN4" t="n">
         <v>1.9</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2479,106 +2479,106 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="DH4" t="n">
-        <v>117.32</v>
+        <v>118.18</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.36</v>
+        <v>6.52</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.9</v>
+        <v>65.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.23</v>
+        <v>11.04</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.5</v>
+        <v>15.43</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59</v>
+        <v>59.26</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.72</v>
+        <v>16.95</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.59</v>
+        <v>10.7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.14</v>
+        <v>6.26</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.72</v>
+        <v>19.65</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,52 +2678,52 @@
         <v>3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>92.36</v>
+        <v>90.92</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>35.91</v>
+        <v>35.67</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.64</v>
+        <v>15.42</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.18</v>
+        <v>11.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.45</v>
+        <v>42.17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.27</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.82</v>
+        <v>19.42</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.59</v>
+        <v>10.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.82</v>
+        <v>5.61</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY5" t="n">
         <v>3.84</v>
@@ -2819,55 +2819,55 @@
         <v>4.44</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.23</v>
+        <v>5.95</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.04</v>
+        <v>6.74</v>
       </c>
       <c r="CE5" t="n">
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CH5" t="n">
         <v>1.41</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CR5" t="n">
         <v>1.45</v>
@@ -2885,7 +2885,7 @@
         <v>1.9</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX5" t="n">
         <v>1.56</v>
@@ -2906,49 +2906,49 @@
         <v>2.08</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF5" t="n">
         <v>2.04</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.95999999999999</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.28</v>
+        <v>4.13</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.04</v>
+        <v>37.83</v>
       </c>
       <c r="DN5" t="n">
         <v>0.96</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.96</v>
+        <v>14.87</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.64</v>
+        <v>11.69</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.82</v>
+        <v>8.74</v>
       </c>
       <c r="DS5" t="n">
         <v>0.22</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.22</v>
+        <v>44.96</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.96</v>
+        <v>12.09</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.039999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.55</v>
+        <v>19.35</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,130 +3081,130 @@
         <v>2.45</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AI6" t="n">
-        <v>77.64</v>
+        <v>75.75</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.36</v>
+        <v>4.25</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>33.18</v>
+        <v>32.83</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.55</v>
+        <v>15.58</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.73</v>
+        <v>10.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>42.27</v>
+        <v>41.58</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.73</v>
+        <v>9.83</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.09</v>
+        <v>17.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.82</v>
+        <v>9.74</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT6" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY6" t="n">
         <v>4.84</v>
@@ -3222,25 +3222,25 @@
         <v>5.54</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.65</v>
+        <v>5.4</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.63</v>
+        <v>5.39</v>
       </c>
       <c r="CE6" t="n">
         <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
         <v>1.38</v>
@@ -3261,28 +3261,28 @@
         <v>2.18</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV6" t="n">
         <v>1.86</v>
@@ -3294,7 +3294,7 @@
         <v>1.63</v>
       </c>
       <c r="CY6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.24</v>
@@ -3303,88 +3303,88 @@
         <v>1.81</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DH6" t="n">
-        <v>80.27</v>
+        <v>79.17</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.22</v>
+        <v>35.91</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.6</v>
+        <v>14.65</v>
       </c>
       <c r="DQ6" t="n">
         <v>11.04</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.539999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.86</v>
+        <v>41.52</v>
       </c>
       <c r="DW6" t="n">
         <v>0.13</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.68</v>
+        <v>10.7</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.22</v>
+        <v>7.17</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.87</v>
+        <v>18.43</v>
       </c>
       <c r="EB6" t="n">
         <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.09</v>
@@ -3484,52 +3484,52 @@
         <v>3.09</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>69.91</v>
+        <v>69.17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.45</v>
+        <v>29.33</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.73</v>
+        <v>14.83</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.09</v>
+        <v>14.33</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.18</v>
+        <v>9.92</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.45</v>
+        <v>42.08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.359999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.55</v>
+        <v>16.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.550000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.68</v>
+        <v>4.91</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY7" t="n">
         <v>4.03</v>
@@ -3625,25 +3625,25 @@
         <v>4.45</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CB7" t="n">
         <v>4.11</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.51</v>
+        <v>6.47</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.35</v>
+        <v>7.27</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CH7" t="n">
         <v>1.35</v>
@@ -3655,34 +3655,34 @@
         <v>2.08</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO7" t="n">
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CR7" t="n">
         <v>1.5</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3697,13 +3697,13 @@
         <v>1.65</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB7" t="n">
         <v>1.41</v>
@@ -3712,49 +3712,49 @@
         <v>2.26</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>73.95999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.54</v>
+        <v>3.69</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.54</v>
+        <v>30.91</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.5</v>
+        <v>15.52</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.14</v>
+        <v>14.26</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.359999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43.5</v>
+        <v>43.26</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.539999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.41</v>
+        <v>17.52</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
@@ -3809,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>83.81999999999999</v>
+        <v>85.83</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3824,67 +3824,67 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>33.27</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>13.82</v>
+        <v>13.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.73</v>
+        <v>15.83</v>
       </c>
       <c r="R8" t="n">
-        <v>7.82</v>
+        <v>7.58</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T8" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52</v>
+        <v>53.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.73</v>
+        <v>13.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.82</v>
+        <v>9.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.73</v>
+        <v>20.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF8" t="n">
         <v>0.18</v>
@@ -3968,70 +3968,70 @@
         <v>2.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.59</v>
+        <v>8.57</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU8" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="CC8" t="n">
         <v>7.73</v>
@@ -4043,10 +4043,10 @@
         <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH8" t="n">
         <v>1.37</v>
@@ -4058,10 +4058,10 @@
         <v>2.05</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM8" t="n">
         <v>2.26</v>
@@ -4073,28 +4073,28 @@
         <v>1.36</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV8" t="n">
         <v>1.8</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CX8" t="n">
         <v>1.69</v>
@@ -4112,22 +4112,22 @@
         <v>1.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="DE8" t="n">
         <v>0.09</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG8" t="n">
         <v>1.78</v>
       </c>
       <c r="DH8" t="n">
-        <v>73.59</v>
+        <v>75.08</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
@@ -4136,61 +4136,61 @@
         <v>2.78</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DM8" t="n">
-        <v>28.64</v>
+        <v>29.74</v>
       </c>
       <c r="DN8" t="n">
         <v>0.87</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.04</v>
+        <v>14.96</v>
       </c>
       <c r="DQ8" t="n">
-        <v>14.91</v>
+        <v>15</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.460000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>46.82</v>
+        <v>47.66</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.41</v>
+        <v>10.56</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.91</v>
+        <v>7.09</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.69</v>
+        <v>18.87</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F9" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>83.55</v>
+        <v>82.67</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="K9" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="L9" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="M9" t="n">
-        <v>31.36</v>
+        <v>31.5</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="P9" t="n">
-        <v>14.45</v>
+        <v>14.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.55</v>
+        <v>12.58</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="S9" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49.45</v>
+        <v>50.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.55</v>
+        <v>6.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.82</v>
+        <v>4.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.27</v>
+        <v>19</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
         <v>0.18</v>
@@ -4371,70 +4371,70 @@
         <v>2.09</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BV9" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.77</v>
+        <v>4.56</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CC9" t="n">
         <v>5.16</v>
@@ -4455,10 +4455,10 @@
         <v>1.41</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK9" t="n">
         <v>1.56</v>
@@ -4479,7 +4479,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CR9" t="n">
         <v>1.46</v>
@@ -4494,10 +4494,10 @@
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX9" t="n">
         <v>1.61</v>
@@ -4515,52 +4515,52 @@
         <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.55</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.14</v>
+        <v>35.04</v>
       </c>
       <c r="DN9" t="n">
         <v>0.87</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.46</v>
+        <v>12.47</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.279999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.59</v>
+        <v>51.05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.32</v>
+        <v>10.3</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.91</v>
+        <v>6.74</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.41</v>
+        <v>3.56</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.5</v>
+        <v>20.31</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>93.18000000000001</v>
+        <v>94.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="K10" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M10" t="n">
-        <v>44.73</v>
+        <v>45.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>16.18</v>
+        <v>16.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.36</v>
+        <v>16.42</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="S10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.09</v>
+        <v>52.92</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.55</v>
+        <v>14.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.45</v>
+        <v>19.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.36</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.14</v>
+        <v>10.3</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.23</v>
+        <v>5.43</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS10" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BT10" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="CC10" t="n">
         <v>3.53</v>
@@ -4852,19 +4852,19 @@
         <v>2.82</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.91</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
         <v>1.8</v>
@@ -4882,7 +4882,7 @@
         <v>2.07</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
@@ -4897,7 +4897,7 @@
         <v>1.41</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW10" t="n">
         <v>1.98</v>
@@ -4909,7 +4909,7 @@
         <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA10" t="n">
         <v>1.91</v>
@@ -4921,46 +4921,46 @@
         <v>2.13</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="DH10" t="n">
-        <v>88.59</v>
+        <v>89.39</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.86</v>
+        <v>4.96</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>45.32</v>
+        <v>45.83</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.14</v>
+        <v>17.13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.5</v>
+        <v>16.53</v>
       </c>
       <c r="DR10" t="n">
         <v>7.78</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.54</v>
+        <v>51.05</v>
       </c>
       <c r="DW10" t="n">
         <v>0.09</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.14</v>
+        <v>12.66</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.050000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.09</v>
+        <v>4.22</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.27</v>
+        <v>20.13</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="G11" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>108.09</v>
+        <v>107.08</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="L11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M11" t="n">
-        <v>44.73</v>
+        <v>44.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.45</v>
+        <v>12.08</v>
       </c>
       <c r="R11" t="n">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.91</v>
+        <v>52.5</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.64</v>
+        <v>12.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.82</v>
+        <v>7.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.82</v>
+        <v>21.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5177,70 +5177,70 @@
         <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.449999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN11" t="n">
         <v>1.91</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.95</v>
+        <v>4.83</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT11" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BV11" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BW11" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX11" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CC11" t="n">
         <v>5.3</v>
@@ -5261,22 +5261,22 @@
         <v>1.42</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK11" t="n">
         <v>1.53</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO11" t="n">
         <v>1.29</v>
@@ -5294,16 +5294,16 @@
         <v>2.87</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU11" t="n">
         <v>1.46</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX11" t="n">
         <v>1.63</v>
@@ -5315,91 +5315,91 @@
         <v>2.25</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DH11" t="n">
-        <v>103</v>
+        <v>102.69</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.91</v>
+        <v>46.7</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.59</v>
+        <v>12.61</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.54</v>
+        <v>12.35</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.1</v>
+        <v>8.18</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.59</v>
+        <v>52.39</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.54</v>
+        <v>12.43</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.039999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.41</v>
+        <v>21.65</v>
       </c>
       <c r="EB11" t="n">
         <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.09</v>
@@ -5499,139 +5499,139 @@
         <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>89</v>
+        <v>89.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="AL12" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.55</v>
+        <v>42.33</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.27</v>
+        <v>13.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.45</v>
+        <v>14.25</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.27</v>
+        <v>6.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.18</v>
+        <v>50.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="BD12" t="n">
-        <v>23.18</v>
+        <v>23.42</v>
       </c>
       <c r="BE12" t="n">
         <v>1.44</v>
       </c>
       <c r="BF12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.77</v>
+        <v>9.57</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY12" t="n">
         <v>3.15</v>
@@ -5640,34 +5640,34 @@
         <v>3.28</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CB12" t="n">
         <v>3.6</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.31</v>
+        <v>4.14</v>
       </c>
       <c r="CE12" t="n">
         <v>1.46</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CK12" t="n">
         <v>1.65</v>
@@ -5679,37 +5679,37 @@
         <v>2.15</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY12" t="n">
         <v>2.12</v>
@@ -5721,88 +5721,88 @@
         <v>1.72</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="DE12" t="n">
         <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DH12" t="n">
-        <v>87.78</v>
+        <v>88.22</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM12" t="n">
-        <v>46.14</v>
+        <v>46.35</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.91</v>
+        <v>13.65</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.77</v>
+        <v>14.65</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.64</v>
+        <v>6.57</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.32</v>
+        <v>49.43</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.32</v>
+        <v>14.22</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.68</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.04</v>
+        <v>22.22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="13">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -5824,49 +5824,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="H13" t="n">
-        <v>69.5</v>
+        <v>69.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M13" t="n">
-        <v>28.5</v>
+        <v>28.27</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="O13" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>14.6</v>
+        <v>14.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>14.91</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.4</v>
+        <v>49.27</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.1</v>
+        <v>19.27</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AF13" t="n">
         <v>0.25</v>
@@ -5983,70 +5983,70 @@
         <v>2.58</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.09</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BP13" t="n">
         <v>4.09</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.25</v>
+        <v>4.99</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.51</v>
+        <v>3.61</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="CC13" t="n">
         <v>4.48</v>
@@ -6055,124 +6055,124 @@
         <v>4.68</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="CT13" t="n">
         <v>2.72</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA13" t="n">
         <v>1.64</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.36</v>
+        <v>4.28</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG13" t="n">
         <v>1.82</v>
       </c>
-      <c r="DG13" t="n">
-        <v>1.86</v>
-      </c>
       <c r="DH13" t="n">
-        <v>74.37</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>30.45</v>
+        <v>30.26</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.64</v>
+        <v>14.52</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.73</v>
+        <v>15.65</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.59</v>
+        <v>8.43</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.59</v>
+        <v>49.09</v>
       </c>
       <c r="DW13" t="n">
         <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.63</v>
+        <v>5.57</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.41</v>
+        <v>20</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="H14" t="n">
-        <v>106.8</v>
+        <v>108.55</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.64</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="M14" t="n">
-        <v>48.4</v>
+        <v>50.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>12.7</v>
+        <v>12.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.1</v>
+        <v>10.64</v>
       </c>
       <c r="R14" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>55.3</v>
+        <v>55.27</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.699999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>20.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
         <v>0.08</v>
@@ -6386,49 +6386,49 @@
         <v>2.08</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.550000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BO14" t="n">
         <v>0.91</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="CA14" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.41</v>
+        <v>5.61</v>
       </c>
       <c r="CC14" t="n">
         <v>1.53</v>
@@ -6458,154 +6458,154 @@
         <v>1.62</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI14" t="n">
         <v>1.68</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CR14" t="n">
         <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CT14" t="n">
         <v>3.1</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CX14" t="n">
         <v>1.63</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.26</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DB14" t="n">
         <v>1.28</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="DH14" t="n">
-        <v>103.23</v>
+        <v>104.22</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.46</v>
+        <v>5.66</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.64</v>
+        <v>50.56</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.55</v>
+        <v>13.57</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.86</v>
+        <v>12.04</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.86</v>
+        <v>5.83</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.13</v>
+        <v>56.08</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.87</v>
+        <v>13.96</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.5</v>
+        <v>8.69</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.45</v>
+        <v>19.56</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC14" t="n">
         <v>2.13</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>61.82</v>
+        <v>62.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>27.67</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.73</v>
+        <v>13.92</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.18</v>
+        <v>15.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.36</v>
+        <v>10.58</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.73</v>
+        <v>44.75</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.18</v>
+        <v>8.92</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.09</v>
+        <v>16.42</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.68</v>
+        <v>10.7</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.64</v>
+        <v>5.52</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.91</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU15" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY15" t="n">
         <v>3.97</v>
@@ -6849,169 +6849,169 @@
         <v>4.22</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.07</v>
+        <v>4.28</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.49</v>
+        <v>4.73</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.95</v>
+        <v>7.78</v>
       </c>
       <c r="CD15" t="n">
-        <v>8.69</v>
+        <v>10</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL15" t="n">
         <v>1.91</v>
       </c>
-      <c r="CK15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>1.93</v>
-      </c>
       <c r="CM15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="CT15" t="n">
         <v>2.92</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.36</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>70.78</v>
+        <v>70.91</v>
       </c>
       <c r="DI15" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.91</v>
+        <v>3.78</v>
       </c>
       <c r="DL15" t="n">
         <v>0.13</v>
       </c>
       <c r="DM15" t="n">
-        <v>28.22</v>
+        <v>27.56</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.19</v>
+        <v>13.31</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.54</v>
+        <v>15.48</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.28</v>
+        <v>46.22</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.539999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.82</v>
+        <v>5.78</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.45</v>
+        <v>16.61</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.17</v>
@@ -7111,139 +7111,139 @@
         <v>3.58</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" t="n">
-        <v>86.2</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>35.3</v>
+        <v>35.09</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>13.55</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.7</v>
+        <v>13.91</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.300000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>46.2</v>
+        <v>47</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.1</v>
+        <v>12.45</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.5</v>
+        <v>8.91</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BD16" t="n">
         <v>19</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.68</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN16" t="n">
         <v>1.09</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BP16" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="BR16" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS16" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BT16" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BU16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY16" t="n">
         <v>3.28</v>
@@ -7252,31 +7252,31 @@
         <v>3.51</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.14</v>
+        <v>3.99</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.48</v>
+        <v>4.29</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CJ16" t="n">
         <v>2.18</v>
@@ -7291,16 +7291,16 @@
         <v>2.02</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CP16" t="n">
         <v>2.49</v>
       </c>
       <c r="CQ16" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="CR16" t="n">
         <v>1.57</v>
@@ -7315,10 +7315,10 @@
         <v>1.34</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CX16" t="n">
         <v>1.81</v>
@@ -7342,79 +7342,79 @@
         <v>5.24</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DG16" t="n">
         <v>2.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.63</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.59</v>
+        <v>4.48</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.27</v>
+        <v>38.04</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.09</v>
+        <v>15.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.45</v>
+        <v>14.52</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.63</v>
+        <v>7.43</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.41</v>
+        <v>48.7</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.09</v>
+        <v>12.26</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.68</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="EA16" t="n">
-        <v>21</v>
+        <v>20.91</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="H17" t="n">
-        <v>118</v>
+        <v>115.09</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>5.27</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M17" t="n">
-        <v>57</v>
+        <v>54.36</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>11.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.8</v>
+        <v>10.64</v>
       </c>
       <c r="R17" t="n">
-        <v>4.9</v>
+        <v>5.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>62.9</v>
+        <v>61.36</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.4</v>
+        <v>11.91</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.5</v>
+        <v>6.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.5</v>
+        <v>21.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AF17" t="n">
         <v>0.08</v>
@@ -7595,64 +7595,64 @@
         <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.41</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.27</v>
+        <v>4.13</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX17" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY17" t="n">
         <v>1.59</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CA17" t="n">
         <v>4.21</v>
@@ -7667,13 +7667,13 @@
         <v>2.57</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF17" t="n">
         <v>2.71</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH17" t="n">
         <v>1.42</v>
@@ -7682,13 +7682,13 @@
         <v>1.78</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM17" t="n">
         <v>2.24</v>
@@ -7700,10 +7700,10 @@
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
@@ -7712,13 +7712,13 @@
         <v>2.95</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU17" t="n">
         <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW17" t="n">
         <v>2.06</v>
@@ -7745,16 +7745,16 @@
         <v>3.46</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="DH17" t="n">
-        <v>111.82</v>
+        <v>110.7</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
@@ -7763,61 +7763,61 @@
         <v>1.91</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.68</v>
+        <v>5.43</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.23</v>
+        <v>55</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.09</v>
+        <v>11.35</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.59</v>
+        <v>11.48</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.32</v>
+        <v>5.44</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>63.87</v>
+        <v>63.09</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.09</v>
+        <v>12.83</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.91</v>
+        <v>7.57</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.18</v>
+        <v>5.26</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.91</v>
+        <v>20.74</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="18">
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -7920,49 +7920,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>105.91</v>
+        <v>107.67</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AN18" t="n">
-        <v>53.73</v>
+        <v>53.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.91</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.18</v>
+        <v>14.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>63.55</v>
+        <v>63.42</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA18" t="n">
-        <v>16.64</v>
+        <v>16.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>10.55</v>
+        <v>10.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.09</v>
+        <v>6.25</v>
       </c>
       <c r="BD18" t="n">
-        <v>15.73</v>
+        <v>16.42</v>
       </c>
       <c r="BE18" t="n">
         <v>1.87</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="BG18" t="n">
         <v>3.09</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="BI18" t="n">
         <v>3.09</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT18" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU18" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY18" t="n">
         <v>1.26</v>
@@ -8058,22 +8058,22 @@
         <v>1.25</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.97</v>
+        <v>6.95</v>
       </c>
       <c r="CC18" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CE18" t="n">
         <v>1.23</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG18" t="n">
         <v>3.31</v>
@@ -8094,7 +8094,7 @@
         <v>1.94</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN18" t="n">
         <v>1.77</v>
@@ -8106,13 +8106,13 @@
         <v>1.66</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CT18" t="n">
         <v>3.11</v>
@@ -8121,7 +8121,7 @@
         <v>1.61</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW18" t="n">
         <v>2.2</v>
@@ -8130,10 +8130,10 @@
         <v>1.61</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA18" t="n">
         <v>1.88</v>
@@ -8151,76 +8151,76 @@
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="DH18" t="n">
-        <v>114.32</v>
+        <v>114.87</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="DK18" t="n">
-        <v>7.41</v>
+        <v>7.43</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="DM18" t="n">
-        <v>58.14</v>
+        <v>57.83</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.59</v>
+        <v>12.65</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.64</v>
+        <v>13.57</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.23</v>
+        <v>62.22</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>18.5</v>
+        <v>18.35</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.55</v>
+        <v>11.35</v>
       </c>
       <c r="DZ18" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.28</v>
+        <v>17.57</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="19">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8323,136 +8323,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>98.8</v>
+        <v>97.36</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>45.8</v>
+        <v>43.64</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.9</v>
+        <v>13.64</v>
       </c>
       <c r="AR19" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.3</v>
+        <v>7.18</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>50.6</v>
+        <v>50.91</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BD19" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="BE19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BN19" t="n">
         <v>1.43</v>
       </c>
-      <c r="BF19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.41</v>
-      </c>
       <c r="BO19" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS19" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT19" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW19" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX19" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY19" t="n">
         <v>3.31</v>
@@ -8461,25 +8461,25 @@
         <v>3.71</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="CE19" t="n">
         <v>1.45</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CH19" t="n">
         <v>1.35</v>
@@ -8494,7 +8494,7 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM19" t="n">
         <v>2.34</v>
@@ -8503,31 +8503,31 @@
         <v>1.82</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CR19" t="n">
         <v>1.47</v>
       </c>
       <c r="CS19" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CT19" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CU19" t="n">
         <v>1.4</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX19" t="n">
         <v>1.59</v>
@@ -8545,10 +8545,10 @@
         <v>1.4</v>
       </c>
       <c r="DC19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
@@ -8557,73 +8557,73 @@
         <v>1.87</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.04000000000001</v>
+        <v>93.56</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.64</v>
+        <v>4.52</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.23</v>
+        <v>44.22</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="DP19" t="n">
-        <v>15.14</v>
+        <v>14.96</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.23</v>
+        <v>15.31</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.23</v>
+        <v>7.17</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.32</v>
+        <v>49.52</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.55</v>
+        <v>13.35</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.82</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.55</v>
+        <v>21.43</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
@@ -1391,49 +1391,49 @@
         <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G2" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="H2" t="n">
-        <v>82.17</v>
+        <v>81.77</v>
       </c>
       <c r="I2" t="n">
         <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M2" t="n">
-        <v>34.5</v>
+        <v>36.38</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P2" t="n">
-        <v>14.25</v>
+        <v>14.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.92</v>
+        <v>12.62</v>
       </c>
       <c r="R2" t="n">
-        <v>8.42</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="T2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>41.08</v>
+        <v>41</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.67</v>
+        <v>21.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>1.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.130000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.65</v>
+        <v>4.83</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.81</v>
+        <v>4.66</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5.08</v>
+        <v>4.91</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="CC2" t="n">
         <v>10.13</v>
@@ -1628,25 +1628,25 @@
         <v>2.85</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH2" t="n">
         <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN2" t="n">
         <v>1.64</v>
@@ -1670,22 +1670,22 @@
         <v>2.86</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA2" t="n">
         <v>1.79</v>
@@ -1703,73 +1703,73 @@
         <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="DH2" t="n">
-        <v>81.95999999999999</v>
+        <v>81.75</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>34.91</v>
+        <v>35.91</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.78</v>
+        <v>13.91</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.65</v>
+        <v>11.54</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.65</v>
+        <v>9.67</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>40.96</v>
+        <v>40.92</v>
       </c>
       <c r="DW2" t="n">
         <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.69</v>
+        <v>10.71</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.18</v>
+        <v>21.67</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC2" t="n">
         <v>2.17</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
@@ -1872,139 +1872,139 @@
         <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AI3" t="n">
-        <v>76</v>
+        <v>77.42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.73</v>
+        <v>31</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>12.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.18</v>
+        <v>8.25</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>39.91</v>
+        <v>40.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.45</v>
+        <v>7.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="BD3" t="n">
         <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
         <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY3" t="n">
         <v>4.24</v>
@@ -2013,16 +2013,16 @@
         <v>4.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CC3" t="n">
-        <v>6.79</v>
+        <v>6.6</v>
       </c>
       <c r="CD3" t="n">
-        <v>7.07</v>
+        <v>6.9</v>
       </c>
       <c r="CE3" t="n">
         <v>1.45</v>
@@ -2040,28 +2040,28 @@
         <v>1.76</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL3" t="n">
         <v>2.1</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO3" t="n">
         <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CR3" t="n">
         <v>1.49</v>
@@ -2079,103 +2079,103 @@
         <v>1.81</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX3" t="n">
         <v>1.69</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.18</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB3" t="n">
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="DH3" t="n">
-        <v>78.05</v>
+        <v>78.67</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.48</v>
+        <v>3.79</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.87</v>
+        <v>37.21</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.3</v>
+        <v>12.96</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.74</v>
+        <v>13.84</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.57</v>
+        <v>43.71</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.39</v>
+        <v>3.46</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.48</v>
+        <v>19.46</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H5" t="n">
-        <v>85.55</v>
+        <v>86</v>
       </c>
       <c r="I5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="K5" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>40.18</v>
+        <v>39.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P5" t="n">
-        <v>14.27</v>
+        <v>14.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.09</v>
+        <v>12.33</v>
       </c>
       <c r="R5" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="T5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>48</v>
+        <v>47.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.64</v>
+        <v>11.83</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.73</v>
+        <v>7.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AF5" t="n">
         <v>0.08</v>
@@ -2759,70 +2759,70 @@
         <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.35</v>
+        <v>10.29</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
         <v>0.96</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO5" t="n">
         <v>0.96</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.61</v>
+        <v>5.58</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.44</v>
+        <v>4.61</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="CC5" t="n">
         <v>5.95</v>
@@ -2834,7 +2834,7 @@
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG5" t="n">
         <v>2.89</v>
@@ -2846,142 +2846,142 @@
         <v>1.86</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP5" t="n">
         <v>2.04</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB5" t="n">
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.34999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.83</v>
+        <v>37.46</v>
       </c>
       <c r="DN5" t="n">
         <v>0.96</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.87</v>
+        <v>14.88</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.69</v>
+        <v>11.83</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.74</v>
+        <v>8.75</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.96</v>
+        <v>44.62</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.09</v>
+        <v>12.16</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.130000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.35</v>
+        <v>19.38</v>
       </c>
       <c r="EB5" t="n">
         <v>1.32</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="6">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>66.92</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AU8" t="n">
         <v>1</v>
       </c>
-      <c r="AI8" t="n">
-        <v>63.36</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AV8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>41.64</v>
+        <v>43.17</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.09</v>
+        <v>7.83</v>
       </c>
       <c r="BB8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.64</v>
+        <v>16.33</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.57</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.39</v>
+        <v>4.58</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY8" t="n">
         <v>3.72</v>
@@ -4028,73 +4028,73 @@
         <v>4.03</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CC8" t="n">
-        <v>7.73</v>
+        <v>7.29</v>
       </c>
       <c r="CD8" t="n">
-        <v>8.98</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="CE8" t="n">
         <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH8" t="n">
         <v>1.37</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL8" t="n">
         <v>2.14</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU8" t="n">
         <v>1.42</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX8" t="n">
         <v>1.69</v>
@@ -4106,7 +4106,7 @@
         <v>2.16</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
         <v>1.38</v>
@@ -4115,82 +4115,82 @@
         <v>2.19</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="DH8" t="n">
-        <v>75.08</v>
+        <v>76.38</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.17</v>
+        <v>3.42</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>29.74</v>
+        <v>30.08</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.96</v>
+        <v>14.71</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.66</v>
+        <v>48.17</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.56</v>
+        <v>10.79</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.09</v>
+        <v>7.21</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.87</v>
+        <v>18.62</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.17</v>
@@ -4290,52 +4290,52 @@
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>89.55</v>
+        <v>86.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN9" t="n">
-        <v>38.91</v>
+        <v>36.75</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.36</v>
+        <v>12.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.73</v>
+        <v>51</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.27</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BD9" t="n">
-        <v>21.73</v>
+        <v>20.92</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.83</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS9" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BV9" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY9" t="n">
         <v>3.91</v>
@@ -4431,34 +4431,34 @@
         <v>4.56</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.07</v>
+        <v>4.19</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.16</v>
+        <v>5.69</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.48</v>
+        <v>6.3</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CK9" t="n">
         <v>1.56</v>
@@ -4467,7 +4467,7 @@
         <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CN9" t="n">
         <v>1.79</v>
@@ -4476,91 +4476,91 @@
         <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY9" t="n">
         <v>2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="DE9" t="n">
         <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.95999999999999</v>
+        <v>84.67</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.04</v>
+        <v>34.12</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.74</v>
+        <v>13.66</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.47</v>
+        <v>12.42</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.05</v>
+        <v>50.71</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.3</v>
+        <v>10.17</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.31</v>
+        <v>19.96</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5096,139 +5096,139 @@
         <v>2.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>97.91</v>
+        <v>98.25</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>49.09</v>
+        <v>49</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.18</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>52.27</v>
+        <v>51.83</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.45</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.27</v>
+        <v>7.92</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="BD11" t="n">
-        <v>22</v>
+        <v>21.92</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.26</v>
+        <v>9.08</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BU11" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BW11" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY11" t="n">
         <v>3.2</v>
@@ -5237,28 +5237,28 @@
         <v>3.27</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.83</v>
+        <v>4.01</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.3</v>
+        <v>5.86</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.29</v>
+        <v>6.03</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI11" t="n">
         <v>1.91</v>
@@ -5270,34 +5270,34 @@
         <v>1.53</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="CT11" t="n">
         <v>3.07</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
         <v>2.05</v>
@@ -5306,100 +5306,100 @@
         <v>1.84</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DB11" t="n">
         <v>1.3</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DH11" t="n">
-        <v>102.69</v>
+        <v>102.66</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.56</v>
+        <v>4.42</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.7</v>
+        <v>46.75</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.61</v>
+        <v>12.79</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.35</v>
+        <v>12.2</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.39</v>
+        <v>52.16</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.43</v>
+        <v>12.21</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.83</v>
+        <v>7.67</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.65</v>
+        <v>21.62</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="12">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="H14" t="n">
-        <v>108.55</v>
+        <v>111.33</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="L14" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M14" t="n">
-        <v>50.45</v>
+        <v>50.42</v>
       </c>
       <c r="N14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="P14" t="n">
-        <v>12.82</v>
+        <v>12.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.64</v>
+        <v>10.83</v>
       </c>
       <c r="R14" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="T14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="V14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>55.27</v>
+        <v>55.42</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.09</v>
+        <v>9.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.18</v>
+        <v>20.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>0.08</v>
@@ -6386,49 +6386,49 @@
         <v>2.08</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.65</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="BM14" t="n">
         <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP14" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS14" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6437,19 +6437,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BY14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>1.43</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1.45</v>
-      </c>
       <c r="CA14" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.61</v>
+        <v>5.67</v>
       </c>
       <c r="CC14" t="n">
         <v>1.53</v>
@@ -6461,28 +6461,28 @@
         <v>1.33</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL14" t="n">
         <v>2.1</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CN14" t="n">
         <v>1.8</v>
@@ -6494,25 +6494,25 @@
         <v>1.82</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
         <v>2.73</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU14" t="n">
         <v>1.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CX14" t="n">
         <v>1.63</v>
@@ -6527,88 +6527,88 @@
         <v>1.81</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC14" t="n">
         <v>1.85</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DH14" t="n">
-        <v>104.22</v>
+        <v>105.79</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.66</v>
+        <v>5.62</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.56</v>
+        <v>50.54</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.57</v>
+        <v>13.54</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.04</v>
+        <v>12.08</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.08</v>
+        <v>56.12</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.96</v>
+        <v>14.21</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.69</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.26</v>
+        <v>5.33</v>
       </c>
       <c r="EA14" t="n">
-        <v>19.56</v>
+        <v>19.96</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="15">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>0.27</v>
@@ -7517,43 +7517,43 @@
         <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AI17" t="n">
-        <v>106.67</v>
+        <v>105.62</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>55.58</v>
+        <v>56</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.58</v>
+        <v>11.85</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.25</v>
+        <v>12.38</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.67</v>
+        <v>5.54</v>
       </c>
       <c r="AT17" t="n">
         <v>1.08</v>
@@ -7562,91 +7562,91 @@
         <v>1.92</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>64.67</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.67</v>
+        <v>14.15</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.25</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.42</v>
+        <v>5.62</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.42</v>
+        <v>20.31</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG17" t="n">
         <v>3.04</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.130000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="BI17" t="n">
         <v>3.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK17" t="n">
         <v>0.83</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT17" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BU17" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.59</v>
@@ -7655,16 +7655,16 @@
         <v>1.64</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="CB17" t="n">
         <v>4.38</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="CE17" t="n">
         <v>1.37</v>
@@ -7679,10 +7679,10 @@
         <v>1.42</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK17" t="n">
         <v>1.58</v>
@@ -7694,34 +7694,34 @@
         <v>2.24</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CU17" t="n">
         <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX17" t="n">
         <v>1.61</v>
@@ -7736,88 +7736,88 @@
         <v>1.82</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="DE17" t="n">
         <v>0.17</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DH17" t="n">
-        <v>110.7</v>
+        <v>109.96</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM17" t="n">
-        <v>55</v>
+        <v>55.25</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.35</v>
+        <v>11.5</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.48</v>
+        <v>11.58</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>63.09</v>
+        <v>63.08</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.83</v>
+        <v>13.12</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.26</v>
+        <v>5.38</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.74</v>
+        <v>20.67</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="18">
@@ -7827,94 +7827,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H18" t="n">
-        <v>122.73</v>
+        <v>120.75</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>7.09</v>
+        <v>6.83</v>
       </c>
       <c r="L18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M18" t="n">
-        <v>62.55</v>
+        <v>61.42</v>
       </c>
       <c r="N18" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O18" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="P18" t="n">
-        <v>12.27</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.09</v>
+        <v>12.42</v>
       </c>
       <c r="R18" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="T18" t="n">
         <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>60.91</v>
+        <v>60.25</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.36</v>
+        <v>19.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>12.55</v>
+        <v>12.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.82</v>
+        <v>7.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>18.82</v>
+        <v>18.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7998,70 +7998,70 @@
         <v>2.92</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BH18" t="n">
-        <v>10</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL18" t="n">
         <v>1.04</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.87</v>
+        <v>4.75</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY18" t="n">
         <v>1.26</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.09</v>
+        <v>6.17</v>
       </c>
       <c r="CB18" t="n">
-        <v>6.95</v>
+        <v>7.01</v>
       </c>
       <c r="CC18" t="n">
         <v>1.59</v>
@@ -8073,19 +8073,19 @@
         <v>1.23</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK18" t="n">
         <v>1.47</v>
@@ -8094,133 +8094,133 @@
         <v>1.94</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CO18" t="n">
         <v>1.13</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CR18" t="n">
         <v>1.39</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="CT18" t="n">
         <v>3.11</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CW18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DG18" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="DH18" t="n">
-        <v>114.87</v>
+        <v>114.21</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DK18" t="n">
-        <v>7.43</v>
+        <v>7.29</v>
       </c>
       <c r="DL18" t="n">
         <v>0.96</v>
       </c>
       <c r="DM18" t="n">
-        <v>57.83</v>
+        <v>57.46</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO18" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.65</v>
+        <v>12.5</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.57</v>
+        <v>13.67</v>
       </c>
       <c r="DR18" t="n">
-        <v>4.39</v>
+        <v>4.46</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>62.22</v>
+        <v>61.84</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>18.35</v>
+        <v>18.16</v>
       </c>
       <c r="DY18" t="n">
-        <v>11.35</v>
+        <v>11.16</v>
       </c>
       <c r="DZ18" t="n">
         <v>7</v>
       </c>
       <c r="EA18" t="n">
-        <v>17.57</v>
+        <v>17.42</v>
       </c>
       <c r="EB18" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="19">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
@@ -8242,82 +8242,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="G19" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="H19" t="n">
-        <v>90.08</v>
+        <v>91</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4.62</v>
       </c>
       <c r="L19" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M19" t="n">
-        <v>44.75</v>
+        <v>45.38</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="O19" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>16.17</v>
+        <v>16.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>14.67</v>
+        <v>13.92</v>
       </c>
       <c r="R19" t="n">
-        <v>7.17</v>
+        <v>6.92</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>48.25</v>
+        <v>48.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.67</v>
+        <v>13.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.75</v>
+        <v>9.69</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="AC19" t="n">
-        <v>20</v>
+        <v>20.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8401,64 +8401,64 @@
         <v>2.18</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BH19" t="n">
-        <v>7.87</v>
+        <v>8</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL19" t="n">
         <v>0.96</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW19" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX19" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="CA19" t="n">
         <v>3.52</v>
@@ -8473,7 +8473,7 @@
         <v>3.7</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF19" t="n">
         <v>3.11</v>
@@ -8494,10 +8494,10 @@
         <v>1.55</v>
       </c>
       <c r="CL19" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CN19" t="n">
         <v>1.82</v>
@@ -8506,10 +8506,10 @@
         <v>1.37</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CR19" t="n">
         <v>1.47</v>
@@ -8524,10 +8524,10 @@
         <v>1.4</v>
       </c>
       <c r="CV19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX19" t="n">
         <v>1.59</v>
@@ -8536,94 +8536,94 @@
         <v>1.98</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA19" t="n">
         <v>1.84</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC19" t="n">
         <v>2.24</v>
       </c>
       <c r="DD19" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.56</v>
+        <v>93.92</v>
       </c>
       <c r="DI19" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.52</v>
+        <v>4.34</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.22</v>
+        <v>44.58</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.96</v>
+        <v>15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>15.31</v>
+        <v>14.87</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.17</v>
+        <v>7.04</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>49.52</v>
+        <v>49.67</v>
       </c>
       <c r="DW19" t="n">
         <v>0.17</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.35</v>
+        <v>13.42</v>
       </c>
       <c r="DY19" t="n">
-        <v>9.609999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.43</v>
+        <v>21.46</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1391,7 +1391,7 @@
         <v>0.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
         <v>1.62</v>
@@ -1403,7 +1403,7 @@
         <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
         <v>3.62</v>
@@ -1466,7 +1466,7 @@
         <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="DG2" t="n">
         <v>2.05</v>
@@ -1715,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DK2" t="n">
         <v>3.67</v>
@@ -1772,7 +1772,7 @@
         <v>1.15</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.08</v>
@@ -2275,139 +2275,139 @@
         <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>114.64</v>
+        <v>112.92</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AL4" t="n">
-        <v>6.09</v>
+        <v>5.83</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>59.45</v>
+        <v>58.33</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.82</v>
+        <v>10.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.73</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>58.45</v>
+        <v>57.83</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>16.36</v>
+        <v>15.92</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.91</v>
+        <v>10.67</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.45</v>
+        <v>20.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.09</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.33</v>
@@ -2416,34 +2416,34 @@
         <v>1.35</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="CC4" t="n">
         <v>1.63</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI4" t="n">
         <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK4" t="n">
         <v>1.51</v>
@@ -2461,10 +2461,10 @@
         <v>1.21</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2479,10 +2479,10 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CX4" t="n">
         <v>1.54</v>
@@ -2494,91 +2494,91 @@
         <v>2.41</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="DH4" t="n">
-        <v>118.18</v>
+        <v>117.17</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.52</v>
+        <v>6.38</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>65.22</v>
+        <v>64.42</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DO4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="DP4" t="n">
         <v>11.04</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.43</v>
+        <v>15.46</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.44</v>
+        <v>5.62</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>59.26</v>
+        <v>58.92</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.95</v>
+        <v>16.71</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.7</v>
+        <v>10.58</v>
       </c>
       <c r="DZ4" t="n">
-        <v>6.26</v>
+        <v>6.12</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.65</v>
+        <v>19.84</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="5">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="H6" t="n">
-        <v>82.91</v>
+        <v>80.33</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="L6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>39.27</v>
+        <v>37.67</v>
       </c>
       <c r="N6" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.36</v>
+        <v>11.58</v>
       </c>
       <c r="R6" t="n">
-        <v>8.82</v>
+        <v>9.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41.45</v>
+        <v>41.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.64</v>
+        <v>11.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.18</v>
+        <v>8.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.64</v>
+        <v>19.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,49 +3162,49 @@
         <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.74</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.3</v>
+        <v>4.38</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.84</v>
+        <v>4.7</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.54</v>
+        <v>5.34</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.01</v>
+        <v>3.96</v>
       </c>
       <c r="CC6" t="n">
         <v>5.4</v>
@@ -3234,16 +3234,16 @@
         <v>5.39</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI6" t="n">
         <v>1.77</v>
@@ -3267,10 +3267,10 @@
         <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
@@ -3285,106 +3285,106 @@
         <v>1.41</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX6" t="n">
         <v>1.63</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.83</v>
+        <v>3.91</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DH6" t="n">
-        <v>79.17</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DK6" t="n">
         <v>3.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.91</v>
+        <v>35.25</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.65</v>
+        <v>14.66</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.04</v>
+        <v>11.16</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.56</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.52</v>
+        <v>41.54</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX6" t="n">
         <v>10.7</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.17</v>
+        <v>7.16</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.43</v>
+        <v>18.25</v>
       </c>
       <c r="EB6" t="n">
         <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>78</v>
+        <v>78.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="L7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>32.64</v>
+        <v>32.33</v>
       </c>
       <c r="N7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="P7" t="n">
-        <v>16.27</v>
+        <v>16.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.18</v>
+        <v>13.92</v>
       </c>
       <c r="R7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="T7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>44.55</v>
+        <v>43.83</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.73</v>
+        <v>7.67</v>
       </c>
       <c r="AA7" t="n">
         <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.27</v>
+        <v>17.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>3.08</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.74</v>
+        <v>9.67</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM7" t="n">
         <v>0.83</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.03</v>
+        <v>3.92</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC7" t="n">
         <v>6.47</v>
@@ -3640,10 +3640,10 @@
         <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH7" t="n">
         <v>1.35</v>
@@ -3652,28 +3652,28 @@
         <v>1.71</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CO7" t="n">
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="CR7" t="n">
         <v>1.5</v>
@@ -3682,112 +3682,112 @@
         <v>3.03</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB7" t="n">
         <v>1.41</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
       <c r="DE7" t="n">
         <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DH7" t="n">
-        <v>73.39</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.69</v>
+        <v>3.58</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.91</v>
+        <v>30.83</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.52</v>
+        <v>15.75</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.26</v>
+        <v>14.12</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.26</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43.26</v>
+        <v>42.96</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.48</v>
+        <v>8.42</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.52</v>
+        <v>17.2</v>
       </c>
       <c r="EB7" t="n">
         <v>0.96</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4696,49 +4696,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AI10" t="n">
-        <v>84</v>
+        <v>85.08</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.91</v>
+        <v>46</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.09</v>
+        <v>17.83</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.64</v>
+        <v>16.83</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49</v>
+        <v>49.42</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.73</v>
+        <v>10.67</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.09</v>
+        <v>21.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BT10" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BY10" t="n">
         <v>2.6</v>
@@ -4834,22 +4834,22 @@
         <v>2.62</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CB10" t="n">
         <v>3.79</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.53</v>
+        <v>3.39</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="CE10" t="n">
         <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG10" t="n">
         <v>2.66</v>
@@ -4858,7 +4858,7 @@
         <v>1.31</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.91</v>
@@ -4867,10 +4867,10 @@
         <v>1.43</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN10" t="n">
         <v>1.84</v>
@@ -4879,91 +4879,91 @@
         <v>1.27</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CU10" t="n">
         <v>1.41</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX10" t="n">
         <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.38</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.39</v>
+        <v>89.7</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK10" t="n">
         <v>4.96</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM10" t="n">
-        <v>45.83</v>
+        <v>45.88</v>
       </c>
       <c r="DN10" t="n">
         <v>0.96</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.13</v>
+        <v>17.04</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.53</v>
+        <v>16.62</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.78</v>
+        <v>7.83</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.05</v>
+        <v>51.17</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.66</v>
+        <v>12.54</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.44</v>
+        <v>8.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.13</v>
+        <v>20.38</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="11">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>86.55</v>
+        <v>86.17</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="K12" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M12" t="n">
-        <v>50.73</v>
+        <v>49.83</v>
       </c>
       <c r="N12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>13.55</v>
+        <v>13.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.09</v>
+        <v>14.83</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="S12" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.45</v>
+        <v>48.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.55</v>
+        <v>15.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.91</v>
+        <v>20.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF12" t="n">
         <v>0.17</v>
@@ -5580,70 +5580,70 @@
         <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL12" t="n">
         <v>0.83</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.13</v>
+        <v>5.17</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>3.72</v>
@@ -5652,13 +5652,13 @@
         <v>4.14</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH12" t="n">
         <v>1.32</v>
@@ -5667,16 +5667,16 @@
         <v>1.73</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CN12" t="n">
         <v>1.72</v>
@@ -5685,10 +5685,10 @@
         <v>1.39</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="CR12" t="n">
         <v>1.49</v>
@@ -5706,103 +5706,103 @@
         <v>1.78</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CX12" t="n">
         <v>1.68</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB12" t="n">
         <v>1.41</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
         <v>2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="DH12" t="n">
-        <v>88.22</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM12" t="n">
-        <v>46.35</v>
+        <v>46.08</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.65</v>
+        <v>13.75</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.65</v>
+        <v>14.54</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.57</v>
+        <v>6.67</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.43</v>
+        <v>49.42</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>14.22</v>
+        <v>14.16</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.609999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="EA12" t="n">
-        <v>22.22</v>
+        <v>22.04</v>
       </c>
       <c r="EB12" t="n">
         <v>1.55</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5902,139 +5902,139 @@
         <v>2.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" t="n">
-        <v>78.42</v>
+        <v>79.08</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.17</v>
+        <v>3.46</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN13" t="n">
-        <v>32.08</v>
+        <v>32.69</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.67</v>
+        <v>14.46</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.33</v>
+        <v>16.69</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.92</v>
+        <v>50.08</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.08</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.08</v>
+        <v>9.31</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="BD13" t="n">
-        <v>20.67</v>
+        <v>20.23</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.130000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BQ13" t="n">
         <v>4.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT13" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>4.6</v>
@@ -6043,16 +6043,16 @@
         <v>4.99</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.68</v>
+        <v>4.55</v>
       </c>
       <c r="CE13" t="n">
         <v>1.46</v>
@@ -6061,7 +6061,7 @@
         <v>3.16</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
@@ -6070,28 +6070,28 @@
         <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CM13" t="n">
         <v>2.04</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
@@ -6100,7 +6100,7 @@
         <v>3.18</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CU13" t="n">
         <v>1.38</v>
@@ -6112,13 +6112,13 @@
         <v>2.1</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DA13" t="n">
         <v>1.64</v>
@@ -6127,85 +6127,85 @@
         <v>1.41</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="DH13" t="n">
-        <v>74.04000000000001</v>
+        <v>74.58</v>
       </c>
       <c r="DI13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="DS13" t="n">
         <v>0.04</v>
       </c>
-      <c r="DJ13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="DK13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>30.26</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0</v>
-      </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.09</v>
+        <v>49.71</v>
       </c>
       <c r="DW13" t="n">
         <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.869999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.57</v>
+        <v>5.59</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="EA13" t="n">
-        <v>20</v>
+        <v>19.79</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="14">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>79.73</v>
+        <v>80.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="K15" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M15" t="n">
-        <v>27.45</v>
+        <v>28.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="O15" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>12.64</v>
+        <v>13.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.91</v>
+        <v>15.83</v>
       </c>
       <c r="R15" t="n">
-        <v>8.91</v>
+        <v>8.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.91</v>
+        <v>10.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.09</v>
+        <v>6.58</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.82</v>
+        <v>17.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.42</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.7</v>
+        <v>10.67</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.13</v>
+        <v>5.21</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX15" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="BZ15" t="n">
         <v>4.22</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="CC15" t="n">
         <v>7.78</v>
@@ -6864,7 +6864,7 @@
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CG15" t="n">
         <v>2.94</v>
@@ -6873,7 +6873,7 @@
         <v>1.43</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.93</v>
@@ -6894,28 +6894,28 @@
         <v>1.29</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CU15" t="n">
         <v>1.46</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
@@ -6924,61 +6924,61 @@
         <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB15" t="n">
         <v>1.3</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DH15" t="n">
-        <v>70.91</v>
+        <v>71.67</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM15" t="n">
-        <v>27.56</v>
+        <v>28.08</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
         <v>1.96</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.31</v>
+        <v>13.58</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.48</v>
+        <v>15.46</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.779999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.22</v>
+        <v>46.21</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.390000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.78</v>
+        <v>6.04</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.61</v>
+        <v>16.8</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0.17</v>
@@ -7111,139 +7111,139 @@
         <v>3.58</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AI16" t="n">
-        <v>86.18000000000001</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>35.09</v>
+        <v>34.75</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.55</v>
+        <v>13.67</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.91</v>
+        <v>13.92</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>47</v>
+        <v>47.92</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.45</v>
+        <v>12.83</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.91</v>
+        <v>9.33</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>19</v>
+        <v>19.67</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.609999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS16" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BT16" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX16" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY16" t="n">
         <v>3.28</v>
@@ -7252,16 +7252,16 @@
         <v>3.51</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.29</v>
+        <v>4.16</v>
       </c>
       <c r="CE16" t="n">
         <v>1.53</v>
@@ -7270,7 +7270,7 @@
         <v>3.42</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CH16" t="n">
         <v>1.27</v>
@@ -7279,25 +7279,25 @@
         <v>1.63</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO16" t="n">
         <v>1.48</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CQ16" t="n">
         <v>4.77</v>
@@ -7321,55 +7321,55 @@
         <v>2.32</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.01</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DD16" t="n">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="DE16" t="n">
         <v>0.17</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="DH16" t="n">
-        <v>90.43000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.04</v>
+        <v>37.75</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="DO16" t="n">
         <v>2.04</v>
@@ -7378,43 +7378,43 @@
         <v>15.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.52</v>
+        <v>14.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.7</v>
+        <v>49.08</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.26</v>
+        <v>12.46</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.869999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.91</v>
+        <v>21.17</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -2338,10 +2338,10 @@
         <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>15.92</v>
+        <v>15.83</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.67</v>
+        <v>10.58</v>
       </c>
       <c r="BC4" t="n">
         <v>5.25</v>
@@ -2350,7 +2350,7 @@
         <v>20.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BF4" t="n">
         <v>2.08</v>
@@ -2563,10 +2563,10 @@
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.71</v>
+        <v>16.67</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.58</v>
+        <v>10.54</v>
       </c>
       <c r="DZ4" t="n">
         <v>6.12</v>

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.08</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>81.73</v>
+        <v>81</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>35.36</v>
+        <v>35.17</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.27</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>11.42</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>40.82</v>
+        <v>40</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.73</v>
+        <v>7.92</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.73</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.42</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.83</v>
+        <v>92</v>
       </c>
       <c r="BS2" t="n">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BU2" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
         <v>4.66</v>
@@ -1610,16 +1610,16 @@
         <v>4.91</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="CB2" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="CC2" t="n">
-        <v>10.13</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="CD2" t="n">
-        <v>12.07</v>
+        <v>11.48</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
@@ -1640,16 +1640,16 @@
         <v>2.06</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO2" t="n">
         <v>1.31</v>
@@ -1658,7 +1658,7 @@
         <v>2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CR2" t="n">
         <v>1.45</v>
@@ -1676,16 +1676,16 @@
         <v>1.81</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
         <v>1.79</v>
@@ -1694,7 +1694,7 @@
         <v>1.32</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD2" t="n">
         <v>3.52</v>
@@ -1703,43 +1703,43 @@
         <v>0.04</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="DH2" t="n">
-        <v>81.75</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM2" t="n">
-        <v>35.91</v>
+        <v>35.8</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.91</v>
+        <v>13.88</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.54</v>
+        <v>11.36</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.67</v>
+        <v>9.92</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>40.92</v>
+        <v>40.52</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.71</v>
+        <v>10.76</v>
       </c>
       <c r="DY2" t="n">
-        <v>7.75</v>
+        <v>7.84</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.67</v>
+        <v>21.32</v>
       </c>
       <c r="EB2" t="n">
         <v>1.15</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
@@ -1794,82 +1794,82 @@
         <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
-        <v>79.92</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.08</v>
+        <v>4.38</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>43.42</v>
+        <v>45.38</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="O3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>13.58</v>
+        <v>13.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.42</v>
+        <v>14.31</v>
       </c>
       <c r="R3" t="n">
-        <v>8.25</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="U3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.92</v>
+        <v>48.62</v>
       </c>
       <c r="Y3" t="n">
         <v>0.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.42</v>
+        <v>10.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.58</v>
+        <v>7.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.92</v>
+        <v>21.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,70 +1953,70 @@
         <v>2.58</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.33</v>
+        <v>8.32</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU3" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.3</v>
+        <v>4.11</v>
       </c>
       <c r="CA3" t="n">
         <v>3.87</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="CC3" t="n">
         <v>6.6</v>
@@ -2031,28 +2031,28 @@
         <v>3.08</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
         <v>1.57</v>
       </c>
       <c r="CL3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CM3" t="n">
         <v>2.1</v>
       </c>
-      <c r="CM3" t="n">
-        <v>2.08</v>
-      </c>
       <c r="CN3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO3" t="n">
         <v>1.37</v>
@@ -2061,7 +2061,7 @@
         <v>2.15</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CR3" t="n">
         <v>1.49</v>
@@ -2079,70 +2079,70 @@
         <v>1.81</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="DH3" t="n">
-        <v>78.67</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DM3" t="n">
-        <v>37.21</v>
+        <v>38.48</v>
       </c>
       <c r="DN3" t="n">
         <v>0.88</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="DP3" t="n">
-        <v>12.96</v>
+        <v>12.72</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.84</v>
+        <v>13.8</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.25</v>
+        <v>8.32</v>
       </c>
       <c r="DS3" t="n">
         <v>0.2</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.71</v>
+        <v>44.72</v>
       </c>
       <c r="DW3" t="n">
         <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.08</v>
+        <v>9.4</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.62</v>
+        <v>6</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.46</v>
+        <v>20.36</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2681,46 +2681,46 @@
         <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>90.92</v>
+        <v>93.31</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>35.67</v>
+        <v>36.62</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.42</v>
+        <v>15.08</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.33</v>
+        <v>11.46</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AU5" t="n">
         <v>0.92</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.17</v>
+        <v>43.08</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.5</v>
+        <v>13.08</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.5</v>
+        <v>8.85</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.42</v>
+        <v>19.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.29</v>
+        <v>10.32</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BO5" t="n">
         <v>0.96</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.58</v>
+        <v>5.52</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT5" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>3.95</v>
@@ -2819,25 +2819,25 @@
         <v>4.61</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.95</v>
+        <v>5.73</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.74</v>
+        <v>6.47</v>
       </c>
       <c r="CE5" t="n">
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH5" t="n">
         <v>1.41</v>
@@ -2855,7 +2855,7 @@
         <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN5" t="n">
         <v>1.94</v>
@@ -2867,19 +2867,19 @@
         <v>2.04</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV5" t="n">
         <v>1.91</v>
@@ -2903,10 +2903,10 @@
         <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
@@ -2915,73 +2915,73 @@
         <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>88.45999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.46</v>
+        <v>37.88</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.88</v>
+        <v>14.72</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.83</v>
+        <v>11.88</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.62</v>
+        <v>45</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.16</v>
+        <v>12.48</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.17</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.38</v>
+        <v>19.48</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="6">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.17</v>
@@ -4290,52 +4290,52 @@
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" t="n">
-        <v>86.67</v>
+        <v>85.23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.75</v>
+        <v>36.23</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>13.31</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.25</v>
+        <v>12.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51</v>
+        <v>50.54</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA9" t="n">
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.17</v>
+        <v>7.08</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.92</v>
+        <v>21.23</v>
       </c>
       <c r="BE9" t="n">
         <v>1.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BP9" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>4.08</v>
       </c>
-      <c r="BQ9" t="n">
-        <v>4.29</v>
-      </c>
       <c r="BR9" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS9" t="n">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="BT9" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BU9" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY9" t="n">
         <v>3.91</v>
@@ -4431,28 +4431,28 @@
         <v>4.56</v>
       </c>
       <c r="CA9" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.3</v>
+        <v>6.24</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
         <v>1.83</v>
@@ -4467,10 +4467,10 @@
         <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO9" t="n">
         <v>1.32</v>
@@ -4479,7 +4479,7 @@
         <v>2.01</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CR9" t="n">
         <v>1.45</v>
@@ -4494,7 +4494,7 @@
         <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW9" t="n">
         <v>1.96</v>
@@ -4515,52 +4515,52 @@
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="DH9" t="n">
-        <v>84.67</v>
+        <v>84</v>
       </c>
       <c r="DI9" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.12</v>
+        <v>33.96</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.66</v>
+        <v>13.8</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.25</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.71</v>
+        <v>50.48</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.71</v>
+        <v>6.68</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.96</v>
+        <v>20.16</v>
       </c>
       <c r="EB9" t="n">
         <v>1.12</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="H10" t="n">
-        <v>94.33</v>
+        <v>93.62</v>
       </c>
       <c r="I10" t="n">
         <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="M10" t="n">
-        <v>45.75</v>
+        <v>46.69</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="P10" t="n">
-        <v>16.25</v>
+        <v>15.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.42</v>
+        <v>16.38</v>
       </c>
       <c r="R10" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.92</v>
+        <v>53.08</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.42</v>
+        <v>14.23</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.17</v>
+        <v>5.23</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.25</v>
+        <v>19.31</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.08</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>5.24</v>
       </c>
       <c r="BR10" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS10" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BT10" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU10" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="CA10" t="n">
         <v>3.65</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CC10" t="n">
         <v>3.39</v>
@@ -4852,7 +4852,7 @@
         <v>2.81</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH10" t="n">
         <v>1.31</v>
@@ -4861,7 +4861,7 @@
         <v>1.82</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK10" t="n">
         <v>1.43</v>
@@ -4873,16 +4873,16 @@
         <v>2.39</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CR10" t="n">
         <v>1.43</v>
@@ -4918,52 +4918,52 @@
         <v>1.35</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="DE10" t="n">
         <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="DH10" t="n">
-        <v>89.7</v>
+        <v>89.52</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DK10" t="n">
         <v>4.96</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>45.88</v>
+        <v>46.36</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="DP10" t="n">
-        <v>17.04</v>
+        <v>16.76</v>
       </c>
       <c r="DQ10" t="n">
-        <v>16.62</v>
+        <v>16.6</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.83</v>
+        <v>7.76</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.17</v>
+        <v>51.32</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.54</v>
+        <v>12.52</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.33</v>
+        <v>8.24</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.21</v>
+        <v>4.28</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="11">
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>13</v>
@@ -5824,49 +5824,49 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="G13" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>69.27</v>
+        <v>68.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="L13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>28.27</v>
+        <v>27.83</v>
       </c>
       <c r="N13" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="O13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="P13" t="n">
-        <v>14.36</v>
+        <v>14.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.91</v>
+        <v>14.75</v>
       </c>
       <c r="R13" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.27</v>
+        <v>49</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.640000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.27</v>
+        <v>18.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AF13" t="n">
         <v>0.23</v>
@@ -5983,70 +5983,70 @@
         <v>2.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.119999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="BO13" t="n">
         <v>0.88</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="BQ13" t="n">
         <v>4.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS13" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU13" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.6</v>
+        <v>4.42</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.99</v>
+        <v>4.78</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC13" t="n">
         <v>4.35</v>
@@ -6070,46 +6070,46 @@
         <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL13" t="n">
         <v>2.28</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP13" t="n">
         <v>2.25</v>
       </c>
       <c r="CQ13" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="CR13" t="n">
         <v>1.5</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CU13" t="n">
         <v>1.38</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX13" t="n">
         <v>1.78</v>
@@ -6130,49 +6130,49 @@
         <v>2.29</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="DE13" t="n">
         <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DH13" t="n">
-        <v>74.58</v>
+        <v>73.84</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>30.66</v>
+        <v>30.36</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.41</v>
+        <v>14.4</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.87</v>
+        <v>15.76</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.04</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.71</v>
+        <v>49.56</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.59</v>
+        <v>5.56</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="EA13" t="n">
-        <v>19.79</v>
+        <v>19.6</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Liga_Portugal_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1619,7 +1619,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="CD2" t="n">
-        <v>11.48</v>
+        <v>11.5</v>
       </c>
       <c r="CE2" t="n">
         <v>1.39</v>
@@ -1694,10 +1694,10 @@
         <v>1.32</v>
       </c>
       <c r="DC2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="DE2" t="n">
         <v>0.04</v>
@@ -2010,13 +2010,13 @@
         <v>4.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CA3" t="n">
         <v>3.87</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CC3" t="n">
         <v>6.6</v>
@@ -2076,22 +2076,22 @@
         <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW3" t="n">
         <v>2.08</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB3" t="n">
         <v>1.39</v>
@@ -2100,7 +2100,7 @@
         <v>2.24</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -2197,82 +2197,82 @@
         <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="H4" t="n">
-        <v>121.42</v>
+        <v>120.77</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>70.23</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="AB4" t="n">
         <v>6.92</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M4" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="P4" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7</v>
-      </c>
       <c r="AC4" t="n">
-        <v>18.92</v>
+        <v>19</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
         <v>0.08</v>
@@ -2356,70 +2356,70 @@
         <v>2.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BO4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>92</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>84</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>68</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>52</v>
+      </c>
+      <c r="BY4" t="n">
         <v>1.38</v>
       </c>
-      <c r="BP4" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.82</v>
+        <v>5.72</v>
       </c>
       <c r="CB4" t="n">
-        <v>6.3</v>
+        <v>6.18</v>
       </c>
       <c r="CC4" t="n">
         <v>1.63</v>
@@ -2431,52 +2431,52 @@
         <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI4" t="n">
         <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV4" t="n">
         <v>1.72</v>
@@ -2485,73 +2485,73 @@
         <v>2.22</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="DH4" t="n">
-        <v>117.17</v>
+        <v>117</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>64.42</v>
+        <v>64.52</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="DP4" t="n">
         <v>11.04</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.46</v>
+        <v>15.52</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>58.92</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>16.67</v>
+        <v>16.8</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.54</v>
+        <v>10.68</v>
       </c>
       <c r="DZ4" t="n">
         <v>6.12</v>
@@ -2575,10 +2575,10 @@
         <v>19.84</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="5">
@@ -2828,7 +2828,7 @@
         <v>5.73</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.47</v>
+        <v>6.45</v>
       </c>
       <c r="CE5" t="n">
         <v>1.4</v>
@@ -2873,13 +2873,13 @@
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV5" t="n">
         <v>1.91</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
@@ -3003,82 +3003,82 @@
         <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H6" t="n">
-        <v>80.33</v>
+        <v>80.31</v>
       </c>
       <c r="I6" t="n">
         <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="K6" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="L6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>37.67</v>
+        <v>37.77</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.58</v>
+        <v>11.77</v>
       </c>
       <c r="R6" t="n">
-        <v>9.08</v>
+        <v>8.92</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41.5</v>
+        <v>41.92</v>
       </c>
       <c r="Y6" t="n">
         <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.58</v>
+        <v>11.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.08</v>
+        <v>7.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.17</v>
+        <v>19.77</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,49 +3162,49 @@
         <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT6" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.34</v>
+        <v>5.1</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CC6" t="n">
         <v>5.4</v>
@@ -3249,19 +3249,19 @@
         <v>1.77</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK6" t="n">
         <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO6" t="n">
         <v>1.34</v>
@@ -3270,7 +3270,7 @@
         <v>2.12</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
@@ -3285,22 +3285,22 @@
         <v>1.41</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW6" t="n">
         <v>2.03</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB6" t="n">
         <v>1.37</v>
@@ -3315,76 +3315,76 @@
         <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DG6" t="n">
         <v>2.04</v>
       </c>
       <c r="DH6" t="n">
-        <v>78.04000000000001</v>
+        <v>78.12</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.25</v>
+        <v>35.4</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.66</v>
+        <v>14.64</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.16</v>
+        <v>11.28</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.54</v>
+        <v>41.76</v>
       </c>
       <c r="DW6" t="n">
         <v>0.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.7</v>
+        <v>10.52</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.16</v>
+        <v>7.04</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.25</v>
+        <v>18.6</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
@@ -3487,49 +3487,49 @@
         <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AI7" t="n">
-        <v>69.17</v>
+        <v>70.08</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>29.33</v>
+        <v>29.31</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.83</v>
+        <v>14.54</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.33</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>42.08</v>
+        <v>41.62</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.17</v>
+        <v>9.15</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.25</v>
+        <v>6.31</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.83</v>
+        <v>16.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.67</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BQ7" t="n">
         <v>4.88</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.67</v>
+        <v>88</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY7" t="n">
         <v>3.92</v>
@@ -3631,49 +3631,49 @@
         <v>4.06</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.47</v>
+        <v>6.31</v>
       </c>
       <c r="CD7" t="n">
-        <v>7.27</v>
+        <v>7.07</v>
       </c>
       <c r="CE7" t="n">
         <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK7" t="n">
         <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.96</v>
+        <v>3.91</v>
       </c>
       <c r="CR7" t="n">
         <v>1.5</v>
@@ -3688,10 +3688,10 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX7" t="n">
         <v>1.66</v>
@@ -3706,55 +3706,55 @@
         <v>1.77</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="DE7" t="n">
         <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DG7" t="n">
         <v>1.92</v>
       </c>
       <c r="DH7" t="n">
-        <v>73.70999999999999</v>
+        <v>74</v>
       </c>
       <c r="DI7" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.83</v>
+        <v>30.76</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.75</v>
+        <v>15.56</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.12</v>
+        <v>13.96</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.210000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>42.96</v>
+        <v>42.68</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.42</v>
+        <v>8.44</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.62</v>
+        <v>5.68</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="EA7" t="n">
         <v>17.2</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="H8" t="n">
-        <v>85.83</v>
+        <v>83.77</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>35</v>
+        <v>33.54</v>
       </c>
       <c r="N8" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>13.75</v>
+        <v>13.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.83</v>
+        <v>15.92</v>
       </c>
       <c r="R8" t="n">
-        <v>7.58</v>
+        <v>7.69</v>
       </c>
       <c r="S8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="U8" t="n">
         <v>0.08</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.17</v>
+        <v>52.69</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.75</v>
+        <v>13.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.92</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.92</v>
+        <v>20.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AF8" t="n">
         <v>0.17</v>
@@ -3968,70 +3968,70 @@
         <v>2.42</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.880000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU8" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BY8" t="n">
         <v>3.72</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="CC8" t="n">
         <v>7.29</v>
@@ -4043,7 +4043,7 @@
         <v>1.43</v>
       </c>
       <c r="CF8" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG8" t="n">
         <v>2.77</v>
@@ -4058,10 +4058,10 @@
         <v>2.03</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
         <v>2.25</v>
@@ -4073,7 +4073,7 @@
         <v>1.35</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ8" t="n">
         <v>3.83</v>
@@ -4082,7 +4082,7 @@
         <v>1.47</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CT8" t="n">
         <v>2.77</v>
@@ -4094,19 +4094,19 @@
         <v>1.82</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY8" t="n">
         <v>2.08</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB8" t="n">
         <v>1.38</v>
@@ -4115,49 +4115,49 @@
         <v>2.19</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="DH8" t="n">
-        <v>76.38</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM8" t="n">
-        <v>30.08</v>
+        <v>29.52</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.71</v>
+        <v>14.76</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.08</v>
+        <v>15.16</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.33</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS8" t="n">
         <v>0.16</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.17</v>
+        <v>48.12</v>
       </c>
       <c r="DW8" t="n">
         <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.79</v>
+        <v>10.72</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.21</v>
+        <v>7.08</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.62</v>
+        <v>18.56</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="9">
@@ -4296,7 +4296,7 @@
         <v>1.69</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" t="n">
         <v>85.23</v>
@@ -4311,7 +4311,7 @@
         <v>3.08</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AN9" t="n">
         <v>36.23</v>
@@ -4320,7 +4320,7 @@
         <v>0.62</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9" t="n">
         <v>13.31</v>
@@ -4398,10 +4398,10 @@
         <v>1.64</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.08</v>
+        <v>4.28</v>
       </c>
       <c r="BR9" t="n">
         <v>96</v>
@@ -4527,7 +4527,7 @@
         <v>2.04</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="DH9" t="n">
         <v>84</v>
@@ -4542,7 +4542,7 @@
         <v>3.6</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
         <v>33.96</v>
@@ -4551,7 +4551,7 @@
         <v>0.8</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="DP9" t="n">
         <v>13.8</v>
@@ -4618,7 +4618,7 @@
         <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="n">
         <v>93.62</v>
@@ -4633,7 +4633,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
         <v>46.69</v>
@@ -4642,7 +4642,7 @@
         <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="P10" t="n">
         <v>15.77</v>
@@ -4801,10 +4801,10 @@
         <v>0.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.24</v>
+        <v>5.44</v>
       </c>
       <c r="BR10" t="n">
         <v>88</v>
@@ -4930,7 +4930,7 @@
         <v>1.68</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="DH10" t="n">
         <v>89.52</v>
@@ -4945,7 +4945,7 @@
         <v>4.96</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
         <v>46.36</v>
@@ -4954,7 +4954,7 @@
         <v>0.92</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="DP10" t="n">
         <v>16.76</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
@@ -5018,49 +5018,49 @@
         <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
-        <v>107.08</v>
+        <v>107.46</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="K11" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="L11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>44.5</v>
+        <v>43.62</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O11" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="P11" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="Q11" t="n">
         <v>12.08</v>
       </c>
       <c r="R11" t="n">
-        <v>8.67</v>
+        <v>8.77</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>0.08</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>52.5</v>
+        <v>53.38</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.42</v>
+        <v>12.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.42</v>
+        <v>7.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>4.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.33</v>
+        <v>20.77</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5177,70 +5177,70 @@
         <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="BH11" t="n">
         <v>9.08</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.